--- a/research/traditional_assets/database/data/slovenia/slovenia_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_chemical_basic.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ljse_cicg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0536</v>
+        <v>-0.00514</v>
       </c>
       <c r="E2">
-        <v>0.125</v>
+        <v>-0.188</v>
       </c>
       <c r="G2">
-        <v>0.2494651262302097</v>
+        <v>0.3712</v>
       </c>
       <c r="H2">
-        <v>0.2494651262302097</v>
+        <v>0.3712</v>
       </c>
       <c r="I2">
-        <v>0.2362002567394095</v>
+        <v>0.06986666666666666</v>
       </c>
       <c r="J2">
-        <v>0.1949291649481192</v>
+        <v>0.0620860606060606</v>
       </c>
       <c r="K2">
-        <v>45.7</v>
+        <v>11.7</v>
       </c>
       <c r="L2">
-        <v>0.1955498502353445</v>
+        <v>0.0624</v>
       </c>
       <c r="M2">
-        <v>24.5</v>
+        <v>22.9908</v>
       </c>
       <c r="N2">
-        <v>0.1275377407600208</v>
+        <v>0.1298181818181818</v>
       </c>
       <c r="O2">
-        <v>0.5361050328227571</v>
+        <v>1.965025641025641</v>
       </c>
       <c r="P2">
-        <v>24.5</v>
+        <v>22.9908</v>
       </c>
       <c r="Q2">
-        <v>0.1275377407600208</v>
+        <v>0.1298181818181818</v>
       </c>
       <c r="R2">
-        <v>0.5361050328227571</v>
+        <v>1.965025641025641</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +638,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>54.6</v>
+        <v>19.3</v>
       </c>
       <c r="V2">
-        <v>0.2842269651223321</v>
+        <v>0.1089779785431959</v>
       </c>
       <c r="W2">
-        <v>0.2156677678150071</v>
+        <v>0.05826693227091632</v>
       </c>
       <c r="X2">
-        <v>0.1179787585474963</v>
+        <v>0.09632333459684404</v>
       </c>
       <c r="Y2">
-        <v>0.09768900926751084</v>
+        <v>-0.03805640232592772</v>
       </c>
       <c r="Z2">
-        <v>1.449751861042184</v>
+        <v>1.282489740082079</v>
       </c>
       <c r="AA2">
-        <v>0.2825989196549346</v>
+        <v>0.07962473572938689</v>
       </c>
       <c r="AB2">
-        <v>0.1179787585474963</v>
+        <v>0.09632333459684404</v>
       </c>
       <c r="AC2">
-        <v>0.1646201611074384</v>
+        <v>-0.01669859886745716</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-54.6</v>
+        <v>-19.3</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +683,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.3970909090909091</v>
+        <v>-0.1223067173637516</v>
       </c>
       <c r="AK2">
-        <v>-0.3734610123119015</v>
+        <v>-0.09212410501193317</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM2">
-        <v>-0.008</v>
+        <v>-0.296</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>13100</v>
+      </c>
       <c r="AP2">
-        <v>-0.8222891566265059</v>
+        <v>-0.748062015503876</v>
       </c>
       <c r="AQ2">
-        <v>-6900</v>
+        <v>-44.25675675675676</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0536</v>
+        <v>-0.00514</v>
       </c>
       <c r="E3">
-        <v>0.125</v>
+        <v>-0.188</v>
       </c>
       <c r="G3">
-        <v>0.2494651262302097</v>
+        <v>0.3712</v>
       </c>
       <c r="H3">
-        <v>0.2494651262302097</v>
+        <v>0.3712</v>
       </c>
       <c r="I3">
-        <v>0.2362002567394095</v>
+        <v>0.06986666666666666</v>
       </c>
       <c r="J3">
-        <v>0.1949291649481192</v>
+        <v>0.0620860606060606</v>
       </c>
       <c r="K3">
-        <v>45.7</v>
+        <v>11.7</v>
       </c>
       <c r="L3">
-        <v>0.1955498502353445</v>
+        <v>0.0624</v>
       </c>
       <c r="M3">
-        <v>24.5</v>
+        <v>22.9908</v>
       </c>
       <c r="N3">
-        <v>0.1275377407600208</v>
+        <v>0.1298181818181818</v>
       </c>
       <c r="O3">
-        <v>0.5361050328227571</v>
+        <v>1.965025641025641</v>
       </c>
       <c r="P3">
-        <v>24.5</v>
+        <v>22.9908</v>
       </c>
       <c r="Q3">
-        <v>0.1275377407600208</v>
+        <v>0.1298181818181818</v>
       </c>
       <c r="R3">
-        <v>0.5361050328227571</v>
+        <v>1.965025641025641</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +772,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>54.6</v>
+        <v>19.3</v>
       </c>
       <c r="V3">
-        <v>0.2842269651223321</v>
+        <v>0.1089779785431959</v>
       </c>
       <c r="W3">
-        <v>0.2156677678150071</v>
+        <v>0.05826693227091632</v>
       </c>
       <c r="X3">
-        <v>0.1179787585474963</v>
+        <v>0.09632333459684404</v>
       </c>
       <c r="Y3">
-        <v>0.09768900926751084</v>
+        <v>-0.03805640232592772</v>
       </c>
       <c r="Z3">
-        <v>1.449751861042184</v>
+        <v>1.282489740082079</v>
       </c>
       <c r="AA3">
-        <v>0.2825989196549346</v>
+        <v>0.07962473572938689</v>
       </c>
       <c r="AB3">
-        <v>0.1179787585474963</v>
+        <v>0.09632333459684404</v>
       </c>
       <c r="AC3">
-        <v>0.1646201611074384</v>
+        <v>-0.01669859886745716</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-54.6</v>
+        <v>-19.3</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +817,8800 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3970909090909091</v>
+        <v>-0.1223067173637516</v>
       </c>
       <c r="AK3">
-        <v>-0.3734610123119015</v>
+        <v>-0.09212410501193317</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>-0.008</v>
+        <v>-0.296</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>13100</v>
+      </c>
       <c r="AP3">
-        <v>-0.8222891566265059</v>
+        <v>-0.748062015503876</v>
       </c>
       <c r="AQ3">
-        <v>-6900</v>
+        <v>-44.25675675675676</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cinkarna Celje, d. d. (LJSE:CICG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LJSE:CICG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chemical (Basic)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>13100</v>
+      </c>
+      <c r="F2">
+        <v>4.54134999706026</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>2.19658914728682</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.32</v>
+      </c>
+      <c r="K2">
+        <v>177.1</v>
+      </c>
+      <c r="L2">
+        <v>127.782471091756</v>
+      </c>
+      <c r="M2">
+        <v>157.8</v>
+      </c>
+      <c r="N2">
+        <v>165.154471091756</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>56.672</v>
+      </c>
+      <c r="Q2">
+        <v>0.096323334596844</v>
+      </c>
+      <c r="R2">
+        <v>0.0936031958533559</v>
+      </c>
+      <c r="S2">
+        <v>0.0470638808926358</v>
+      </c>
+      <c r="T2">
+        <v>0.041229</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.096323334596844</v>
+      </c>
+      <c r="X2">
+        <v>0.118249876254935</v>
+      </c>
+      <c r="Y2">
+        <v>0.9054086395470869</v>
+      </c>
+      <c r="Z2">
+        <v>1.25052910920974</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.05810355665757501</v>
+      </c>
+      <c r="AC2">
+        <v>13100</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0.001</v>
+      </c>
+      <c r="AF2">
+        <v>12.7</v>
+      </c>
+      <c r="AG2">
+        <v>25.8</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>177.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.06353300828410362</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.19</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>14</v>
+      </c>
+      <c r="AR2">
+        <v>0.001</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>19.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09632333459684404</v>
+      </c>
+      <c r="C2">
+        <v>177.1</v>
+      </c>
+      <c r="D2">
+        <v>157.8</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>19.3</v>
+      </c>
+      <c r="H2">
+        <v>177.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>25.8</v>
+      </c>
+      <c r="K2">
+        <v>12.7</v>
+      </c>
+      <c r="L2">
+        <v>13.1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>13.1</v>
+      </c>
+      <c r="O2">
+        <v>2.489</v>
+      </c>
+      <c r="P2">
+        <v>10.611</v>
+      </c>
+      <c r="Q2">
+        <v>23.311</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09632333459684404</v>
+      </c>
+      <c r="T2">
+        <v>0.9054086395470866</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.19</v>
+      </c>
+      <c r="W2">
+        <v>0.036207</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09618811026111006</v>
+      </c>
+      <c r="C3">
+        <v>175.6791018342483</v>
+      </c>
+      <c r="D3">
+        <v>158.1501018342482</v>
+      </c>
+      <c r="E3">
+        <v>1.771</v>
+      </c>
+      <c r="F3">
+        <v>1.771</v>
+      </c>
+      <c r="G3">
+        <v>19.3</v>
+      </c>
+      <c r="H3">
+        <v>177.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>25.8</v>
+      </c>
+      <c r="K3">
+        <v>12.7</v>
+      </c>
+      <c r="L3">
+        <v>13.1</v>
+      </c>
+      <c r="M3">
+        <v>0.0791637</v>
+      </c>
+      <c r="N3">
+        <v>13.0208363</v>
+      </c>
+      <c r="O3">
+        <v>2.473958897</v>
+      </c>
+      <c r="P3">
+        <v>10.546877403</v>
+      </c>
+      <c r="Q3">
+        <v>23.246877403</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09679398006172732</v>
+      </c>
+      <c r="T3">
+        <v>0.9128165284161083</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.19</v>
+      </c>
+      <c r="W3">
+        <v>0.036207</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>165.4798853514932</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09605288592537603</v>
+      </c>
+      <c r="C4">
+        <v>174.2597606246556</v>
+      </c>
+      <c r="D4">
+        <v>158.5017606246556</v>
+      </c>
+      <c r="E4">
+        <v>3.542</v>
+      </c>
+      <c r="F4">
+        <v>3.542</v>
+      </c>
+      <c r="G4">
+        <v>19.3</v>
+      </c>
+      <c r="H4">
+        <v>177.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>25.8</v>
+      </c>
+      <c r="K4">
+        <v>12.7</v>
+      </c>
+      <c r="L4">
+        <v>13.1</v>
+      </c>
+      <c r="M4">
+        <v>0.1583274</v>
+      </c>
+      <c r="N4">
+        <v>12.9416726</v>
+      </c>
+      <c r="O4">
+        <v>2.458917794</v>
+      </c>
+      <c r="P4">
+        <v>10.482754806</v>
+      </c>
+      <c r="Q4">
+        <v>23.182754806</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09727423053609799</v>
+      </c>
+      <c r="T4">
+        <v>0.9203755986906201</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.19</v>
+      </c>
+      <c r="W4">
+        <v>0.036207</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>82.73994267574659</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09591766158964204</v>
+      </c>
+      <c r="C5">
+        <v>172.8419867803992</v>
+      </c>
+      <c r="D5">
+        <v>158.8549867803991</v>
+      </c>
+      <c r="E5">
+        <v>5.313</v>
+      </c>
+      <c r="F5">
+        <v>5.313</v>
+      </c>
+      <c r="G5">
+        <v>19.3</v>
+      </c>
+      <c r="H5">
+        <v>177.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>25.8</v>
+      </c>
+      <c r="K5">
+        <v>12.7</v>
+      </c>
+      <c r="L5">
+        <v>13.1</v>
+      </c>
+      <c r="M5">
+        <v>0.2374911</v>
+      </c>
+      <c r="N5">
+        <v>12.8625089</v>
+      </c>
+      <c r="O5">
+        <v>2.443876691</v>
+      </c>
+      <c r="P5">
+        <v>10.418632209</v>
+      </c>
+      <c r="Q5">
+        <v>23.118632209</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09776438308210519</v>
+      </c>
+      <c r="T5">
+        <v>0.9280905260841941</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.19</v>
+      </c>
+      <c r="W5">
+        <v>0.036207</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>55.15996178383106</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.095782437253908</v>
+      </c>
+      <c r="C6">
+        <v>171.4257908036523</v>
+      </c>
+      <c r="D6">
+        <v>159.2097908036523</v>
+      </c>
+      <c r="E6">
+        <v>7.084</v>
+      </c>
+      <c r="F6">
+        <v>7.084</v>
+      </c>
+      <c r="G6">
+        <v>19.3</v>
+      </c>
+      <c r="H6">
+        <v>177.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>25.8</v>
+      </c>
+      <c r="K6">
+        <v>12.7</v>
+      </c>
+      <c r="L6">
+        <v>13.1</v>
+      </c>
+      <c r="M6">
+        <v>0.3166548</v>
+      </c>
+      <c r="N6">
+        <v>12.7833452</v>
+      </c>
+      <c r="O6">
+        <v>2.428835588</v>
+      </c>
+      <c r="P6">
+        <v>10.354509612</v>
+      </c>
+      <c r="Q6">
+        <v>23.054509612</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09826474713948752</v>
+      </c>
+      <c r="T6">
+        <v>0.9359661811318007</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.19</v>
+      </c>
+      <c r="W6">
+        <v>0.036207</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>41.3699713378733</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09564721291817402</v>
+      </c>
+      <c r="C7">
+        <v>170.0111832906247</v>
+      </c>
+      <c r="D7">
+        <v>159.5661832906247</v>
+      </c>
+      <c r="E7">
+        <v>8.855</v>
+      </c>
+      <c r="F7">
+        <v>8.855</v>
+      </c>
+      <c r="G7">
+        <v>19.3</v>
+      </c>
+      <c r="H7">
+        <v>177.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>25.8</v>
+      </c>
+      <c r="K7">
+        <v>12.7</v>
+      </c>
+      <c r="L7">
+        <v>13.1</v>
+      </c>
+      <c r="M7">
+        <v>0.3958185000000001</v>
+      </c>
+      <c r="N7">
+        <v>12.7041815</v>
+      </c>
+      <c r="O7">
+        <v>2.413794485</v>
+      </c>
+      <c r="P7">
+        <v>10.290387015</v>
+      </c>
+      <c r="Q7">
+        <v>22.990387015</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09877564517702528</v>
+      </c>
+      <c r="T7">
+        <v>0.9440076394435676</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.19</v>
+      </c>
+      <c r="W7">
+        <v>0.036207</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>33.09597707029863</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09551198858244001</v>
+      </c>
+      <c r="C8">
+        <v>168.5981749326182</v>
+      </c>
+      <c r="D8">
+        <v>159.9241749326182</v>
+      </c>
+      <c r="E8">
+        <v>10.626</v>
+      </c>
+      <c r="F8">
+        <v>10.626</v>
+      </c>
+      <c r="G8">
+        <v>19.3</v>
+      </c>
+      <c r="H8">
+        <v>177.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>25.8</v>
+      </c>
+      <c r="K8">
+        <v>12.7</v>
+      </c>
+      <c r="L8">
+        <v>13.1</v>
+      </c>
+      <c r="M8">
+        <v>0.4749822</v>
+      </c>
+      <c r="N8">
+        <v>12.6250178</v>
+      </c>
+      <c r="O8">
+        <v>2.398753382</v>
+      </c>
+      <c r="P8">
+        <v>10.226264418</v>
+      </c>
+      <c r="Q8">
+        <v>22.926264418</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09929741338557449</v>
+      </c>
+      <c r="T8">
+        <v>0.9522201926130317</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.19</v>
+      </c>
+      <c r="W8">
+        <v>0.036207</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>27.57998089191553</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09537676424670602</v>
+      </c>
+      <c r="C9">
+        <v>167.1867765170954</v>
+      </c>
+      <c r="D9">
+        <v>160.2837765170954</v>
+      </c>
+      <c r="E9">
+        <v>12.397</v>
+      </c>
+      <c r="F9">
+        <v>12.397</v>
+      </c>
+      <c r="G9">
+        <v>19.3</v>
+      </c>
+      <c r="H9">
+        <v>177.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>25.8</v>
+      </c>
+      <c r="K9">
+        <v>12.7</v>
+      </c>
+      <c r="L9">
+        <v>13.1</v>
+      </c>
+      <c r="M9">
+        <v>0.5541459000000001</v>
+      </c>
+      <c r="N9">
+        <v>12.5458541</v>
+      </c>
+      <c r="O9">
+        <v>2.383712279</v>
+      </c>
+      <c r="P9">
+        <v>10.162141821</v>
+      </c>
+      <c r="Q9">
+        <v>22.862141821</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09983040241581292</v>
+      </c>
+      <c r="T9">
+        <v>0.960609359829151</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.19</v>
+      </c>
+      <c r="W9">
+        <v>0.036207</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>23.63998362164188</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09524153991097202</v>
+      </c>
+      <c r="C10">
+        <v>165.776998928763</v>
+      </c>
+      <c r="D10">
+        <v>160.644998928763</v>
+      </c>
+      <c r="E10">
+        <v>14.168</v>
+      </c>
+      <c r="F10">
+        <v>14.168</v>
+      </c>
+      <c r="G10">
+        <v>19.3</v>
+      </c>
+      <c r="H10">
+        <v>177.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>25.8</v>
+      </c>
+      <c r="K10">
+        <v>12.7</v>
+      </c>
+      <c r="L10">
+        <v>13.1</v>
+      </c>
+      <c r="M10">
+        <v>0.6333096</v>
+      </c>
+      <c r="N10">
+        <v>12.4666904</v>
+      </c>
+      <c r="O10">
+        <v>2.368671176</v>
+      </c>
+      <c r="P10">
+        <v>10.098019224</v>
+      </c>
+      <c r="Q10">
+        <v>22.798019224</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1003749781641</v>
+      </c>
+      <c r="T10">
+        <v>0.9691809002456206</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.19</v>
+      </c>
+      <c r="W10">
+        <v>0.036207</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>20.68498566893665</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09510631557523801</v>
+      </c>
+      <c r="C11">
+        <v>164.3688531506706</v>
+      </c>
+      <c r="D11">
+        <v>161.0078531506706</v>
+      </c>
+      <c r="E11">
+        <v>15.939</v>
+      </c>
+      <c r="F11">
+        <v>15.939</v>
+      </c>
+      <c r="G11">
+        <v>19.3</v>
+      </c>
+      <c r="H11">
+        <v>177.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>25.8</v>
+      </c>
+      <c r="K11">
+        <v>12.7</v>
+      </c>
+      <c r="L11">
+        <v>13.1</v>
+      </c>
+      <c r="M11">
+        <v>0.7124733</v>
+      </c>
+      <c r="N11">
+        <v>12.3875267</v>
+      </c>
+      <c r="O11">
+        <v>2.353630073000001</v>
+      </c>
+      <c r="P11">
+        <v>10.033896627</v>
+      </c>
+      <c r="Q11">
+        <v>22.733896627</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1009315226101516</v>
+      </c>
+      <c r="T11">
+        <v>0.9779408261657487</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.19</v>
+      </c>
+      <c r="W11">
+        <v>0.036207</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>18.38665392794369</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09497109123950402</v>
+      </c>
+      <c r="C12">
+        <v>162.9623502653232</v>
+      </c>
+      <c r="D12">
+        <v>161.3723502653232</v>
+      </c>
+      <c r="E12">
+        <v>17.71</v>
+      </c>
+      <c r="F12">
+        <v>17.71</v>
+      </c>
+      <c r="G12">
+        <v>19.3</v>
+      </c>
+      <c r="H12">
+        <v>177.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>25.8</v>
+      </c>
+      <c r="K12">
+        <v>12.7</v>
+      </c>
+      <c r="L12">
+        <v>13.1</v>
+      </c>
+      <c r="M12">
+        <v>0.7916370000000001</v>
+      </c>
+      <c r="N12">
+        <v>12.308363</v>
+      </c>
+      <c r="O12">
+        <v>2.33858897</v>
+      </c>
+      <c r="P12">
+        <v>9.969774030000002</v>
+      </c>
+      <c r="Q12">
+        <v>22.66977403</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.10150043471056</v>
+      </c>
+      <c r="T12">
+        <v>0.9868954171063244</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.19</v>
+      </c>
+      <c r="W12">
+        <v>0.036207</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>16.54798853514932</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09483586690376999</v>
+      </c>
+      <c r="C13">
+        <v>161.5575014558104</v>
+      </c>
+      <c r="D13">
+        <v>161.7385014558104</v>
+      </c>
+      <c r="E13">
+        <v>19.481</v>
+      </c>
+      <c r="F13">
+        <v>19.481</v>
+      </c>
+      <c r="G13">
+        <v>19.3</v>
+      </c>
+      <c r="H13">
+        <v>177.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>25.8</v>
+      </c>
+      <c r="K13">
+        <v>12.7</v>
+      </c>
+      <c r="L13">
+        <v>13.1</v>
+      </c>
+      <c r="M13">
+        <v>0.8708007</v>
+      </c>
+      <c r="N13">
+        <v>12.2291993</v>
+      </c>
+      <c r="O13">
+        <v>2.323547867</v>
+      </c>
+      <c r="P13">
+        <v>9.905651433000001</v>
+      </c>
+      <c r="Q13">
+        <v>22.605651433</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1020821313525506</v>
+      </c>
+      <c r="T13">
+        <v>0.9960512348096096</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.19</v>
+      </c>
+      <c r="W13">
+        <v>0.036207</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>15.04362594104484</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09470064256803599</v>
+      </c>
+      <c r="C14">
+        <v>160.154318006949</v>
+      </c>
+      <c r="D14">
+        <v>162.106318006949</v>
+      </c>
+      <c r="E14">
+        <v>21.252</v>
+      </c>
+      <c r="F14">
+        <v>21.252</v>
+      </c>
+      <c r="G14">
+        <v>19.3</v>
+      </c>
+      <c r="H14">
+        <v>177.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>25.8</v>
+      </c>
+      <c r="K14">
+        <v>12.7</v>
+      </c>
+      <c r="L14">
+        <v>13.1</v>
+      </c>
+      <c r="M14">
+        <v>0.9499644</v>
+      </c>
+      <c r="N14">
+        <v>12.1500356</v>
+      </c>
+      <c r="O14">
+        <v>2.308506764</v>
+      </c>
+      <c r="P14">
+        <v>9.841528836</v>
+      </c>
+      <c r="Q14">
+        <v>22.541528836</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1026770483727682</v>
+      </c>
+      <c r="T14">
+        <v>1.005415139278878</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.19</v>
+      </c>
+      <c r="W14">
+        <v>0.036207</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>13.78999044595776</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09468124823230199</v>
+      </c>
+      <c r="C15">
+        <v>158.4362087321857</v>
+      </c>
+      <c r="D15">
+        <v>162.1592087321857</v>
+      </c>
+      <c r="E15">
+        <v>23.023</v>
+      </c>
+      <c r="F15">
+        <v>23.023</v>
+      </c>
+      <c r="G15">
+        <v>19.3</v>
+      </c>
+      <c r="H15">
+        <v>177.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>25.8</v>
+      </c>
+      <c r="K15">
+        <v>12.7</v>
+      </c>
+      <c r="L15">
+        <v>13.1</v>
+      </c>
+      <c r="M15">
+        <v>1.0544534</v>
+      </c>
+      <c r="N15">
+        <v>12.0455466</v>
+      </c>
+      <c r="O15">
+        <v>2.288653854000001</v>
+      </c>
+      <c r="P15">
+        <v>9.756892746000002</v>
+      </c>
+      <c r="Q15">
+        <v>22.456892746</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1032856416463241</v>
+      </c>
+      <c r="T15">
+        <v>1.014994305919855</v>
+      </c>
+      <c r="U15">
+        <v>0.0458</v>
+      </c>
+      <c r="V15">
+        <v>0.19</v>
+      </c>
+      <c r="W15">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>12.42349827882389</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09455493389656799</v>
+      </c>
+      <c r="C16">
+        <v>157.0105295688417</v>
+      </c>
+      <c r="D16">
+        <v>162.5045295688417</v>
+      </c>
+      <c r="E16">
+        <v>24.794</v>
+      </c>
+      <c r="F16">
+        <v>24.794</v>
+      </c>
+      <c r="G16">
+        <v>19.3</v>
+      </c>
+      <c r="H16">
+        <v>177.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>25.8</v>
+      </c>
+      <c r="K16">
+        <v>12.7</v>
+      </c>
+      <c r="L16">
+        <v>13.1</v>
+      </c>
+      <c r="M16">
+        <v>1.1355652</v>
+      </c>
+      <c r="N16">
+        <v>11.9644348</v>
+      </c>
+      <c r="O16">
+        <v>2.273242612</v>
+      </c>
+      <c r="P16">
+        <v>9.691192188</v>
+      </c>
+      <c r="Q16">
+        <v>22.391192188</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1039083882518232</v>
+      </c>
+      <c r="T16">
+        <v>1.024796243878063</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.19</v>
+      </c>
+      <c r="W16">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>11.53610554462218</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.094428619560834</v>
+      </c>
+      <c r="C17">
+        <v>155.5863242775094</v>
+      </c>
+      <c r="D17">
+        <v>162.8513242775093</v>
+      </c>
+      <c r="E17">
+        <v>26.565</v>
+      </c>
+      <c r="F17">
+        <v>26.565</v>
+      </c>
+      <c r="G17">
+        <v>19.3</v>
+      </c>
+      <c r="H17">
+        <v>177.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>25.8</v>
+      </c>
+      <c r="K17">
+        <v>12.7</v>
+      </c>
+      <c r="L17">
+        <v>13.1</v>
+      </c>
+      <c r="M17">
+        <v>1.216677</v>
+      </c>
+      <c r="N17">
+        <v>11.883323</v>
+      </c>
+      <c r="O17">
+        <v>2.25783137</v>
+      </c>
+      <c r="P17">
+        <v>9.625491630000001</v>
+      </c>
+      <c r="Q17">
+        <v>22.32549163</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1045457877186282</v>
+      </c>
+      <c r="T17">
+        <v>1.034828815670582</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.19</v>
+      </c>
+      <c r="W17">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>10.76703184164737</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09430230522509998</v>
+      </c>
+      <c r="C18">
+        <v>154.1636023143706</v>
+      </c>
+      <c r="D18">
+        <v>163.1996023143706</v>
+      </c>
+      <c r="E18">
+        <v>28.336</v>
+      </c>
+      <c r="F18">
+        <v>28.336</v>
+      </c>
+      <c r="G18">
+        <v>19.3</v>
+      </c>
+      <c r="H18">
+        <v>177.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>25.8</v>
+      </c>
+      <c r="K18">
+        <v>12.7</v>
+      </c>
+      <c r="L18">
+        <v>13.1</v>
+      </c>
+      <c r="M18">
+        <v>1.2977888</v>
+      </c>
+      <c r="N18">
+        <v>11.8022112</v>
+      </c>
+      <c r="O18">
+        <v>2.242420128</v>
+      </c>
+      <c r="P18">
+        <v>9.559791072000001</v>
+      </c>
+      <c r="Q18">
+        <v>22.259791072</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1051983633632143</v>
+      </c>
+      <c r="T18">
+        <v>1.045100258220066</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.19</v>
+      </c>
+      <c r="W18">
+        <v>0.03709800000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.09409235154441</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09447893088936599</v>
+      </c>
+      <c r="C19">
+        <v>151.906017827341</v>
+      </c>
+      <c r="D19">
+        <v>162.713017827341</v>
+      </c>
+      <c r="E19">
+        <v>30.107</v>
+      </c>
+      <c r="F19">
+        <v>30.107</v>
+      </c>
+      <c r="G19">
+        <v>19.3</v>
+      </c>
+      <c r="H19">
+        <v>177.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>25.8</v>
+      </c>
+      <c r="K19">
+        <v>12.7</v>
+      </c>
+      <c r="L19">
+        <v>13.1</v>
+      </c>
+      <c r="M19">
+        <v>1.445136</v>
+      </c>
+      <c r="N19">
+        <v>11.654864</v>
+      </c>
+      <c r="O19">
+        <v>2.214424160000001</v>
+      </c>
+      <c r="P19">
+        <v>9.440439840000002</v>
+      </c>
+      <c r="Q19">
+        <v>22.14043984</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1058666637221277</v>
+      </c>
+      <c r="T19">
+        <v>1.055619205409296</v>
+      </c>
+      <c r="U19">
+        <v>0.048</v>
+      </c>
+      <c r="V19">
+        <v>0.19</v>
+      </c>
+      <c r="W19">
+        <v>0.03888</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>9.064890778445765</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09437043655363199</v>
+      </c>
+      <c r="C20">
+        <v>150.4335635358754</v>
+      </c>
+      <c r="D20">
+        <v>163.0115635358754</v>
+      </c>
+      <c r="E20">
+        <v>31.878</v>
+      </c>
+      <c r="F20">
+        <v>31.878</v>
+      </c>
+      <c r="G20">
+        <v>19.3</v>
+      </c>
+      <c r="H20">
+        <v>177.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>25.8</v>
+      </c>
+      <c r="K20">
+        <v>12.7</v>
+      </c>
+      <c r="L20">
+        <v>13.1</v>
+      </c>
+      <c r="M20">
+        <v>1.530144</v>
+      </c>
+      <c r="N20">
+        <v>11.569856</v>
+      </c>
+      <c r="O20">
+        <v>2.19827264</v>
+      </c>
+      <c r="P20">
+        <v>9.371583360000001</v>
+      </c>
+      <c r="Q20">
+        <v>22.07158336</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1065512640897951</v>
+      </c>
+      <c r="T20">
+        <v>1.066394712286069</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.19</v>
+      </c>
+      <c r="W20">
+        <v>0.03888</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>8.56128573519878</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09426194221789796</v>
+      </c>
+      <c r="C21">
+        <v>148.9622068010368</v>
+      </c>
+      <c r="D21">
+        <v>163.3112068010367</v>
+      </c>
+      <c r="E21">
+        <v>33.649</v>
+      </c>
+      <c r="F21">
+        <v>33.649</v>
+      </c>
+      <c r="G21">
+        <v>19.3</v>
+      </c>
+      <c r="H21">
+        <v>177.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>25.8</v>
+      </c>
+      <c r="K21">
+        <v>12.7</v>
+      </c>
+      <c r="L21">
+        <v>13.1</v>
+      </c>
+      <c r="M21">
+        <v>1.615152</v>
+      </c>
+      <c r="N21">
+        <v>11.484848</v>
+      </c>
+      <c r="O21">
+        <v>2.18212112</v>
+      </c>
+      <c r="P21">
+        <v>9.302726880000002</v>
+      </c>
+      <c r="Q21">
+        <v>22.00272688</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1072527681702444</v>
+      </c>
+      <c r="T21">
+        <v>1.077436281061033</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.19</v>
+      </c>
+      <c r="W21">
+        <v>0.03888</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.110691749135686</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09439644788216399</v>
+      </c>
+      <c r="C22">
+        <v>146.8198879229772</v>
+      </c>
+      <c r="D22">
+        <v>162.9398879229771</v>
+      </c>
+      <c r="E22">
+        <v>35.42</v>
+      </c>
+      <c r="F22">
+        <v>35.42</v>
+      </c>
+      <c r="G22">
+        <v>19.3</v>
+      </c>
+      <c r="H22">
+        <v>177.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>25.8</v>
+      </c>
+      <c r="K22">
+        <v>12.7</v>
+      </c>
+      <c r="L22">
+        <v>13.1</v>
+      </c>
+      <c r="M22">
+        <v>1.75329</v>
+      </c>
+      <c r="N22">
+        <v>11.34671</v>
+      </c>
+      <c r="O22">
+        <v>2.1558749</v>
+      </c>
+      <c r="P22">
+        <v>9.190835100000001</v>
+      </c>
+      <c r="Q22">
+        <v>21.8908351</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.107971809852705</v>
+      </c>
+      <c r="T22">
+        <v>1.088753889055372</v>
+      </c>
+      <c r="U22">
+        <v>0.0495</v>
+      </c>
+      <c r="V22">
+        <v>0.19</v>
+      </c>
+      <c r="W22">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>7.471667550718935</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09430010354642997</v>
+      </c>
+      <c r="C23">
+        <v>145.3146860645375</v>
+      </c>
+      <c r="D23">
+        <v>163.2056860645375</v>
+      </c>
+      <c r="E23">
+        <v>37.191</v>
+      </c>
+      <c r="F23">
+        <v>37.191</v>
+      </c>
+      <c r="G23">
+        <v>19.3</v>
+      </c>
+      <c r="H23">
+        <v>177.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>25.8</v>
+      </c>
+      <c r="K23">
+        <v>12.7</v>
+      </c>
+      <c r="L23">
+        <v>13.1</v>
+      </c>
+      <c r="M23">
+        <v>1.8409545</v>
+      </c>
+      <c r="N23">
+        <v>11.2590455</v>
+      </c>
+      <c r="O23">
+        <v>2.139218645</v>
+      </c>
+      <c r="P23">
+        <v>9.119826855000001</v>
+      </c>
+      <c r="Q23">
+        <v>21.819826855</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1087090551220632</v>
+      </c>
+      <c r="T23">
+        <v>1.100358018771086</v>
+      </c>
+      <c r="U23">
+        <v>0.0495</v>
+      </c>
+      <c r="V23">
+        <v>0.19</v>
+      </c>
+      <c r="W23">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.115873857827557</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09420375921069597</v>
+      </c>
+      <c r="C24">
+        <v>143.8103527974285</v>
+      </c>
+      <c r="D24">
+        <v>163.4723527974285</v>
+      </c>
+      <c r="E24">
+        <v>38.962</v>
+      </c>
+      <c r="F24">
+        <v>38.962</v>
+      </c>
+      <c r="G24">
+        <v>19.3</v>
+      </c>
+      <c r="H24">
+        <v>177.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>25.8</v>
+      </c>
+      <c r="K24">
+        <v>12.7</v>
+      </c>
+      <c r="L24">
+        <v>13.1</v>
+      </c>
+      <c r="M24">
+        <v>1.928619</v>
+      </c>
+      <c r="N24">
+        <v>11.171381</v>
+      </c>
+      <c r="O24">
+        <v>2.122562390000001</v>
+      </c>
+      <c r="P24">
+        <v>9.048818610000001</v>
+      </c>
+      <c r="Q24">
+        <v>21.74881861</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1094652041162769</v>
+      </c>
+      <c r="T24">
+        <v>1.112259690274383</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.19</v>
+      </c>
+      <c r="W24">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>6.792425046108123</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09410741487496196</v>
+      </c>
+      <c r="C25">
+        <v>142.3068923862717</v>
+      </c>
+      <c r="D25">
+        <v>163.7398923862717</v>
+      </c>
+      <c r="E25">
+        <v>40.733</v>
+      </c>
+      <c r="F25">
+        <v>40.733</v>
+      </c>
+      <c r="G25">
+        <v>19.3</v>
+      </c>
+      <c r="H25">
+        <v>177.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>25.8</v>
+      </c>
+      <c r="K25">
+        <v>12.7</v>
+      </c>
+      <c r="L25">
+        <v>13.1</v>
+      </c>
+      <c r="M25">
+        <v>2.0162835</v>
+      </c>
+      <c r="N25">
+        <v>11.0837165</v>
+      </c>
+      <c r="O25">
+        <v>2.105906135</v>
+      </c>
+      <c r="P25">
+        <v>8.977810365000002</v>
+      </c>
+      <c r="Q25">
+        <v>21.677810365</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1102409933441064</v>
+      </c>
+      <c r="T25">
+        <v>1.12447049610244</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.19</v>
+      </c>
+      <c r="W25">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>6.497102218016464</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09401107053922796</v>
+      </c>
+      <c r="C26">
+        <v>140.8043091236522</v>
+      </c>
+      <c r="D26">
+        <v>164.0083091236522</v>
+      </c>
+      <c r="E26">
+        <v>42.504</v>
+      </c>
+      <c r="F26">
+        <v>42.504</v>
+      </c>
+      <c r="G26">
+        <v>19.3</v>
+      </c>
+      <c r="H26">
+        <v>177.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>25.8</v>
+      </c>
+      <c r="K26">
+        <v>12.7</v>
+      </c>
+      <c r="L26">
+        <v>13.1</v>
+      </c>
+      <c r="M26">
+        <v>2.103948</v>
+      </c>
+      <c r="N26">
+        <v>10.996052</v>
+      </c>
+      <c r="O26">
+        <v>2.089249880000001</v>
+      </c>
+      <c r="P26">
+        <v>8.906802120000002</v>
+      </c>
+      <c r="Q26">
+        <v>21.60680212</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1110371980779315</v>
+      </c>
+      <c r="T26">
+        <v>1.137002638925973</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.19</v>
+      </c>
+      <c r="W26">
+        <v>0.04009500000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.226389625599113</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09419822620349395</v>
+      </c>
+      <c r="C27">
+        <v>138.5126937974676</v>
+      </c>
+      <c r="D27">
+        <v>163.4876937974676</v>
+      </c>
+      <c r="E27">
+        <v>44.275</v>
+      </c>
+      <c r="F27">
+        <v>44.275</v>
+      </c>
+      <c r="G27">
+        <v>19.3</v>
+      </c>
+      <c r="H27">
+        <v>177.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>25.8</v>
+      </c>
+      <c r="K27">
+        <v>12.7</v>
+      </c>
+      <c r="L27">
+        <v>13.1</v>
+      </c>
+      <c r="M27">
+        <v>2.2535975</v>
+      </c>
+      <c r="N27">
+        <v>10.8464025</v>
+      </c>
+      <c r="O27">
+        <v>2.060816475</v>
+      </c>
+      <c r="P27">
+        <v>8.785586025000001</v>
+      </c>
+      <c r="Q27">
+        <v>21.485586025</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1118546349379919</v>
+      </c>
+      <c r="T27">
+        <v>1.1498689722248</v>
+      </c>
+      <c r="U27">
+        <v>0.0509</v>
+      </c>
+      <c r="V27">
+        <v>0.19</v>
+      </c>
+      <c r="W27">
+        <v>0.041229</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>5.812927996237128</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09411322186775996</v>
+      </c>
+      <c r="C28">
+        <v>136.9777420895795</v>
+      </c>
+      <c r="D28">
+        <v>163.7237420895794</v>
+      </c>
+      <c r="E28">
+        <v>46.046</v>
+      </c>
+      <c r="F28">
+        <v>46.046</v>
+      </c>
+      <c r="G28">
+        <v>19.3</v>
+      </c>
+      <c r="H28">
+        <v>177.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>25.8</v>
+      </c>
+      <c r="K28">
+        <v>12.7</v>
+      </c>
+      <c r="L28">
+        <v>13.1</v>
+      </c>
+      <c r="M28">
+        <v>2.3437414</v>
+      </c>
+      <c r="N28">
+        <v>10.7562586</v>
+      </c>
+      <c r="O28">
+        <v>2.043689134000001</v>
+      </c>
+      <c r="P28">
+        <v>8.712569466000001</v>
+      </c>
+      <c r="Q28">
+        <v>21.412569466</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1126941646861621</v>
+      </c>
+      <c r="T28">
+        <v>1.163083044261433</v>
+      </c>
+      <c r="U28">
+        <v>0.0509</v>
+      </c>
+      <c r="V28">
+        <v>0.19</v>
+      </c>
+      <c r="W28">
+        <v>0.041229</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>5.589353842535701</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09402821753202593</v>
+      </c>
+      <c r="C29">
+        <v>135.4434729940599</v>
+      </c>
+      <c r="D29">
+        <v>163.9604729940599</v>
+      </c>
+      <c r="E29">
+        <v>47.817</v>
+      </c>
+      <c r="F29">
+        <v>47.817</v>
+      </c>
+      <c r="G29">
+        <v>19.3</v>
+      </c>
+      <c r="H29">
+        <v>177.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>25.8</v>
+      </c>
+      <c r="K29">
+        <v>12.7</v>
+      </c>
+      <c r="L29">
+        <v>13.1</v>
+      </c>
+      <c r="M29">
+        <v>2.4338853</v>
+      </c>
+      <c r="N29">
+        <v>10.6661147</v>
+      </c>
+      <c r="O29">
+        <v>2.026561793</v>
+      </c>
+      <c r="P29">
+        <v>8.639552907000001</v>
+      </c>
+      <c r="Q29">
+        <v>21.339552907</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1135566952493506</v>
+      </c>
+      <c r="T29">
+        <v>1.176659145668933</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.19</v>
+      </c>
+      <c r="W29">
+        <v>0.041229</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.3823407372566</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09394321319629194</v>
+      </c>
+      <c r="C30">
+        <v>133.9098894761985</v>
+      </c>
+      <c r="D30">
+        <v>164.1978894761985</v>
+      </c>
+      <c r="E30">
+        <v>49.588</v>
+      </c>
+      <c r="F30">
+        <v>49.588</v>
+      </c>
+      <c r="G30">
+        <v>19.3</v>
+      </c>
+      <c r="H30">
+        <v>177.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>25.8</v>
+      </c>
+      <c r="K30">
+        <v>12.7</v>
+      </c>
+      <c r="L30">
+        <v>13.1</v>
+      </c>
+      <c r="M30">
+        <v>2.5240292</v>
+      </c>
+      <c r="N30">
+        <v>10.5759708</v>
+      </c>
+      <c r="O30">
+        <v>2.009434452</v>
+      </c>
+      <c r="P30">
+        <v>8.566536348</v>
+      </c>
+      <c r="Q30">
+        <v>21.266536348</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1144431849948499</v>
+      </c>
+      <c r="T30">
+        <v>1.190612361004419</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.19</v>
+      </c>
+      <c r="W30">
+        <v>0.041229</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.190114282354578</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09385820886055793</v>
+      </c>
+      <c r="C31">
+        <v>132.3769945184849</v>
+      </c>
+      <c r="D31">
+        <v>164.4359945184849</v>
+      </c>
+      <c r="E31">
+        <v>51.35899999999999</v>
+      </c>
+      <c r="F31">
+        <v>51.35899999999999</v>
+      </c>
+      <c r="G31">
+        <v>19.3</v>
+      </c>
+      <c r="H31">
+        <v>177.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>25.8</v>
+      </c>
+      <c r="K31">
+        <v>12.7</v>
+      </c>
+      <c r="L31">
+        <v>13.1</v>
+      </c>
+      <c r="M31">
+        <v>2.6141731</v>
+      </c>
+      <c r="N31">
+        <v>10.4858269</v>
+      </c>
+      <c r="O31">
+        <v>1.992307111</v>
+      </c>
+      <c r="P31">
+        <v>8.493519789</v>
+      </c>
+      <c r="Q31">
+        <v>21.193519789</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.115354646282476</v>
+      </c>
+      <c r="T31">
+        <v>1.204958624659214</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.19</v>
+      </c>
+      <c r="W31">
+        <v>0.041229</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.011144824342352</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09377320452482393</v>
+      </c>
+      <c r="C32">
+        <v>130.8447911207334</v>
+      </c>
+      <c r="D32">
+        <v>164.6747911207334</v>
+      </c>
+      <c r="E32">
+        <v>53.13</v>
+      </c>
+      <c r="F32">
+        <v>53.13</v>
+      </c>
+      <c r="G32">
+        <v>19.3</v>
+      </c>
+      <c r="H32">
+        <v>177.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>25.8</v>
+      </c>
+      <c r="K32">
+        <v>12.7</v>
+      </c>
+      <c r="L32">
+        <v>13.1</v>
+      </c>
+      <c r="M32">
+        <v>2.704317</v>
+      </c>
+      <c r="N32">
+        <v>10.395683</v>
+      </c>
+      <c r="O32">
+        <v>1.97517977</v>
+      </c>
+      <c r="P32">
+        <v>8.420503230000001</v>
+      </c>
+      <c r="Q32">
+        <v>21.12050323</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1162921493211771</v>
+      </c>
+      <c r="T32">
+        <v>1.21971478156129</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.19</v>
+      </c>
+      <c r="W32">
+        <v>0.041229</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>4.84410666353094</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09368820018908992</v>
+      </c>
+      <c r="C33">
+        <v>129.3132823002095</v>
+      </c>
+      <c r="D33">
+        <v>164.9142823002095</v>
+      </c>
+      <c r="E33">
+        <v>54.901</v>
+      </c>
+      <c r="F33">
+        <v>54.901</v>
+      </c>
+      <c r="G33">
+        <v>19.3</v>
+      </c>
+      <c r="H33">
+        <v>177.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>25.8</v>
+      </c>
+      <c r="K33">
+        <v>12.7</v>
+      </c>
+      <c r="L33">
+        <v>13.1</v>
+      </c>
+      <c r="M33">
+        <v>2.7944609</v>
+      </c>
+      <c r="N33">
+        <v>10.3055391</v>
+      </c>
+      <c r="O33">
+        <v>1.958052429</v>
+      </c>
+      <c r="P33">
+        <v>8.347486671</v>
+      </c>
+      <c r="Q33">
+        <v>21.047486671</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1172568263609999</v>
+      </c>
+      <c r="T33">
+        <v>1.234898653156179</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.19</v>
+      </c>
+      <c r="W33">
+        <v>0.041229</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>4.687845158255748</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09360319585335593</v>
+      </c>
+      <c r="C34">
+        <v>127.7824710917562</v>
+      </c>
+      <c r="D34">
+        <v>165.1544710917562</v>
+      </c>
+      <c r="E34">
+        <v>56.672</v>
+      </c>
+      <c r="F34">
+        <v>56.672</v>
+      </c>
+      <c r="G34">
+        <v>19.3</v>
+      </c>
+      <c r="H34">
+        <v>177.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>25.8</v>
+      </c>
+      <c r="K34">
+        <v>12.7</v>
+      </c>
+      <c r="L34">
+        <v>13.1</v>
+      </c>
+      <c r="M34">
+        <v>2.8846048</v>
+      </c>
+      <c r="N34">
+        <v>10.2153952</v>
+      </c>
+      <c r="O34">
+        <v>1.940925088</v>
+      </c>
+      <c r="P34">
+        <v>8.274470112000001</v>
+      </c>
+      <c r="Q34">
+        <v>20.974470112</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1182498762549352</v>
+      </c>
+      <c r="T34">
+        <v>1.250529109209741</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.19</v>
+      </c>
+      <c r="W34">
+        <v>0.041229</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.541349997060257</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0942131715176219</v>
+      </c>
+      <c r="C35">
+        <v>124.3032625352828</v>
+      </c>
+      <c r="D35">
+        <v>163.4462625352828</v>
+      </c>
+      <c r="E35">
+        <v>58.443</v>
+      </c>
+      <c r="F35">
+        <v>58.443</v>
+      </c>
+      <c r="G35">
+        <v>19.3</v>
+      </c>
+      <c r="H35">
+        <v>177.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>25.8</v>
+      </c>
+      <c r="K35">
+        <v>12.7</v>
+      </c>
+      <c r="L35">
+        <v>13.1</v>
+      </c>
+      <c r="M35">
+        <v>3.1267005</v>
+      </c>
+      <c r="N35">
+        <v>9.973299500000001</v>
+      </c>
+      <c r="O35">
+        <v>1.894926905</v>
+      </c>
+      <c r="P35">
+        <v>8.078372595000001</v>
+      </c>
+      <c r="Q35">
+        <v>20.778372595</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1192725694292864</v>
+      </c>
+      <c r="T35">
+        <v>1.266626146041021</v>
+      </c>
+      <c r="U35">
+        <v>0.0535</v>
+      </c>
+      <c r="V35">
+        <v>0.19</v>
+      </c>
+      <c r="W35">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.189720121898469</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09414922718188792</v>
+      </c>
+      <c r="C36">
+        <v>122.7096758761024</v>
+      </c>
+      <c r="D36">
+        <v>163.6236758761024</v>
+      </c>
+      <c r="E36">
+        <v>60.21400000000001</v>
+      </c>
+      <c r="F36">
+        <v>60.21400000000001</v>
+      </c>
+      <c r="G36">
+        <v>19.3</v>
+      </c>
+      <c r="H36">
+        <v>177.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>25.8</v>
+      </c>
+      <c r="K36">
+        <v>12.7</v>
+      </c>
+      <c r="L36">
+        <v>13.1</v>
+      </c>
+      <c r="M36">
+        <v>3.221449</v>
+      </c>
+      <c r="N36">
+        <v>9.878551000000002</v>
+      </c>
+      <c r="O36">
+        <v>1.87692469</v>
+      </c>
+      <c r="P36">
+        <v>8.001626310000001</v>
+      </c>
+      <c r="Q36">
+        <v>20.70162631</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1203262533058908</v>
+      </c>
+      <c r="T36">
+        <v>1.283210971867189</v>
+      </c>
+      <c r="U36">
+        <v>0.0535</v>
+      </c>
+      <c r="V36">
+        <v>0.19</v>
+      </c>
+      <c r="W36">
+        <v>0.04333500000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.066493059489689</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09485073284615392</v>
+      </c>
+      <c r="C37">
+        <v>119.01316720336</v>
+      </c>
+      <c r="D37">
+        <v>161.69816720336</v>
+      </c>
+      <c r="E37">
+        <v>61.98500000000001</v>
+      </c>
+      <c r="F37">
+        <v>61.98500000000001</v>
+      </c>
+      <c r="G37">
+        <v>19.3</v>
+      </c>
+      <c r="H37">
+        <v>177.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>25.8</v>
+      </c>
+      <c r="K37">
+        <v>12.7</v>
+      </c>
+      <c r="L37">
+        <v>13.1</v>
+      </c>
+      <c r="M37">
+        <v>3.483557</v>
+      </c>
+      <c r="N37">
+        <v>9.616443</v>
+      </c>
+      <c r="O37">
+        <v>1.82712417</v>
+      </c>
+      <c r="P37">
+        <v>7.78931883</v>
+      </c>
+      <c r="Q37">
+        <v>20.48931883</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1214123582248522</v>
+      </c>
+      <c r="T37">
+        <v>1.30030610002647</v>
+      </c>
+      <c r="U37">
+        <v>0.0562</v>
+      </c>
+      <c r="V37">
+        <v>0.19</v>
+      </c>
+      <c r="W37">
+        <v>0.045522</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>3.760524085008513</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.0948086585104199</v>
+      </c>
+      <c r="C38">
+        <v>117.3563753682629</v>
+      </c>
+      <c r="D38">
+        <v>161.8123753682628</v>
+      </c>
+      <c r="E38">
+        <v>63.75599999999999</v>
+      </c>
+      <c r="F38">
+        <v>63.75599999999999</v>
+      </c>
+      <c r="G38">
+        <v>19.3</v>
+      </c>
+      <c r="H38">
+        <v>177.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>25.8</v>
+      </c>
+      <c r="K38">
+        <v>12.7</v>
+      </c>
+      <c r="L38">
+        <v>13.1</v>
+      </c>
+      <c r="M38">
+        <v>3.5830872</v>
+      </c>
+      <c r="N38">
+        <v>9.516912800000002</v>
+      </c>
+      <c r="O38">
+        <v>1.808213432</v>
+      </c>
+      <c r="P38">
+        <v>7.708699368000001</v>
+      </c>
+      <c r="Q38">
+        <v>20.408699368</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1225324039225311</v>
+      </c>
+      <c r="T38">
+        <v>1.317935450940728</v>
+      </c>
+      <c r="U38">
+        <v>0.0562</v>
+      </c>
+      <c r="V38">
+        <v>0.19</v>
+      </c>
+      <c r="W38">
+        <v>0.045522</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>3.656065082647166</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09476658417468589</v>
+      </c>
+      <c r="C39">
+        <v>115.6997449787078</v>
+      </c>
+      <c r="D39">
+        <v>161.9267449787078</v>
+      </c>
+      <c r="E39">
+        <v>65.527</v>
+      </c>
+      <c r="F39">
+        <v>65.527</v>
+      </c>
+      <c r="G39">
+        <v>19.3</v>
+      </c>
+      <c r="H39">
+        <v>177.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>25.8</v>
+      </c>
+      <c r="K39">
+        <v>12.7</v>
+      </c>
+      <c r="L39">
+        <v>13.1</v>
+      </c>
+      <c r="M39">
+        <v>3.6826174</v>
+      </c>
+      <c r="N39">
+        <v>9.417382600000002</v>
+      </c>
+      <c r="O39">
+        <v>1.789302694</v>
+      </c>
+      <c r="P39">
+        <v>7.628079906000002</v>
+      </c>
+      <c r="Q39">
+        <v>20.328079906</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1236880066264856</v>
+      </c>
+      <c r="T39">
+        <v>1.336124463788772</v>
+      </c>
+      <c r="U39">
+        <v>0.0562</v>
+      </c>
+      <c r="V39">
+        <v>0.19</v>
+      </c>
+      <c r="W39">
+        <v>0.045522</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.557252512845891</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09617116983895191</v>
+      </c>
+      <c r="C40">
+        <v>110.1960708720087</v>
+      </c>
+      <c r="D40">
+        <v>158.1940708720087</v>
+      </c>
+      <c r="E40">
+        <v>67.298</v>
+      </c>
+      <c r="F40">
+        <v>67.298</v>
+      </c>
+      <c r="G40">
+        <v>19.3</v>
+      </c>
+      <c r="H40">
+        <v>177.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>25.8</v>
+      </c>
+      <c r="K40">
+        <v>12.7</v>
+      </c>
+      <c r="L40">
+        <v>13.1</v>
+      </c>
+      <c r="M40">
+        <v>4.0984482</v>
+      </c>
+      <c r="N40">
+        <v>9.001551800000001</v>
+      </c>
+      <c r="O40">
+        <v>1.710294842</v>
+      </c>
+      <c r="P40">
+        <v>7.291256958000001</v>
+      </c>
+      <c r="Q40">
+        <v>19.991256958</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1248808868370192</v>
+      </c>
+      <c r="T40">
+        <v>1.354900218986753</v>
+      </c>
+      <c r="U40">
+        <v>0.0609</v>
+      </c>
+      <c r="V40">
+        <v>0.19</v>
+      </c>
+      <c r="W40">
+        <v>0.049329</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.196331723797315</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09616716550321788</v>
+      </c>
+      <c r="C41">
+        <v>108.4354677388884</v>
+      </c>
+      <c r="D41">
+        <v>158.2044677388884</v>
+      </c>
+      <c r="E41">
+        <v>69.069</v>
+      </c>
+      <c r="F41">
+        <v>69.069</v>
+      </c>
+      <c r="G41">
+        <v>19.3</v>
+      </c>
+      <c r="H41">
+        <v>177.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>25.8</v>
+      </c>
+      <c r="K41">
+        <v>12.7</v>
+      </c>
+      <c r="L41">
+        <v>13.1</v>
+      </c>
+      <c r="M41">
+        <v>4.2063021</v>
+      </c>
+      <c r="N41">
+        <v>8.893697900000001</v>
+      </c>
+      <c r="O41">
+        <v>1.689802601</v>
+      </c>
+      <c r="P41">
+        <v>7.203895299000001</v>
+      </c>
+      <c r="Q41">
+        <v>19.903895299</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1261128778741277</v>
+      </c>
+      <c r="T41">
+        <v>1.374291572715816</v>
+      </c>
+      <c r="U41">
+        <v>0.0609</v>
+      </c>
+      <c r="V41">
+        <v>0.19</v>
+      </c>
+      <c r="W41">
+        <v>0.049329</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.114374500110204</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.0961631611674839</v>
+      </c>
+      <c r="C42">
+        <v>106.6748659724685</v>
+      </c>
+      <c r="D42">
+        <v>158.2148659724685</v>
+      </c>
+      <c r="E42">
+        <v>70.84</v>
+      </c>
+      <c r="F42">
+        <v>70.84</v>
+      </c>
+      <c r="G42">
+        <v>19.3</v>
+      </c>
+      <c r="H42">
+        <v>177.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>25.8</v>
+      </c>
+      <c r="K42">
+        <v>12.7</v>
+      </c>
+      <c r="L42">
+        <v>13.1</v>
+      </c>
+      <c r="M42">
+        <v>4.314156000000001</v>
+      </c>
+      <c r="N42">
+        <v>8.785844000000001</v>
+      </c>
+      <c r="O42">
+        <v>1.66931036</v>
+      </c>
+      <c r="P42">
+        <v>7.116533640000001</v>
+      </c>
+      <c r="Q42">
+        <v>19.81653364</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1273859352791398</v>
+      </c>
+      <c r="T42">
+        <v>1.394329304902513</v>
+      </c>
+      <c r="U42">
+        <v>0.0609</v>
+      </c>
+      <c r="V42">
+        <v>0.19</v>
+      </c>
+      <c r="W42">
+        <v>0.049329</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.036515137607449</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09924768683174988</v>
+      </c>
+      <c r="C43">
+        <v>97.27962413233833</v>
+      </c>
+      <c r="D43">
+        <v>150.5906241323383</v>
+      </c>
+      <c r="E43">
+        <v>72.611</v>
+      </c>
+      <c r="F43">
+        <v>72.611</v>
+      </c>
+      <c r="G43">
+        <v>19.3</v>
+      </c>
+      <c r="H43">
+        <v>177.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>25.8</v>
+      </c>
+      <c r="K43">
+        <v>12.7</v>
+      </c>
+      <c r="L43">
+        <v>13.1</v>
+      </c>
+      <c r="M43">
+        <v>5.0972922</v>
+      </c>
+      <c r="N43">
+        <v>8.002707800000001</v>
+      </c>
+      <c r="O43">
+        <v>1.520514482</v>
+      </c>
+      <c r="P43">
+        <v>6.482193318000001</v>
+      </c>
+      <c r="Q43">
+        <v>19.182193318</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1287021471724574</v>
+      </c>
+      <c r="T43">
+        <v>1.415046282248082</v>
+      </c>
+      <c r="U43">
+        <v>0.0702</v>
+      </c>
+      <c r="V43">
+        <v>0.19</v>
+      </c>
+      <c r="W43">
+        <v>0.056862</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.569991965538095</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09931901249601588</v>
+      </c>
+      <c r="C44">
+        <v>95.3410059696164</v>
+      </c>
+      <c r="D44">
+        <v>150.4230059696164</v>
+      </c>
+      <c r="E44">
+        <v>74.38199999999999</v>
+      </c>
+      <c r="F44">
+        <v>74.38199999999999</v>
+      </c>
+      <c r="G44">
+        <v>19.3</v>
+      </c>
+      <c r="H44">
+        <v>177.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>25.8</v>
+      </c>
+      <c r="K44">
+        <v>12.7</v>
+      </c>
+      <c r="L44">
+        <v>13.1</v>
+      </c>
+      <c r="M44">
+        <v>5.221616399999999</v>
+      </c>
+      <c r="N44">
+        <v>7.878383600000002</v>
+      </c>
+      <c r="O44">
+        <v>1.496892884</v>
+      </c>
+      <c r="P44">
+        <v>6.381490716000002</v>
+      </c>
+      <c r="Q44">
+        <v>19.081490716</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.130063745682786</v>
+      </c>
+      <c r="T44">
+        <v>1.436477638122809</v>
+      </c>
+      <c r="U44">
+        <v>0.0702</v>
+      </c>
+      <c r="V44">
+        <v>0.19</v>
+      </c>
+      <c r="W44">
+        <v>0.056862</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.508801680644331</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1010273481602819</v>
+      </c>
+      <c r="C45">
+        <v>89.66395058811642</v>
+      </c>
+      <c r="D45">
+        <v>146.5169505881164</v>
+      </c>
+      <c r="E45">
+        <v>76.15299999999999</v>
+      </c>
+      <c r="F45">
+        <v>76.15299999999999</v>
+      </c>
+      <c r="G45">
+        <v>19.3</v>
+      </c>
+      <c r="H45">
+        <v>177.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>25.8</v>
+      </c>
+      <c r="K45">
+        <v>12.7</v>
+      </c>
+      <c r="L45">
+        <v>13.1</v>
+      </c>
+      <c r="M45">
+        <v>5.703859699999999</v>
+      </c>
+      <c r="N45">
+        <v>7.396140300000003</v>
+      </c>
+      <c r="O45">
+        <v>1.405266657000001</v>
+      </c>
+      <c r="P45">
+        <v>5.990873643000002</v>
+      </c>
+      <c r="Q45">
+        <v>18.690873643</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1314731195794419</v>
+      </c>
+      <c r="T45">
+        <v>1.458660971396649</v>
+      </c>
+      <c r="U45">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V45">
+        <v>0.19</v>
+      </c>
+      <c r="W45">
+        <v>0.060669</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.296690432269925</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1011367438245479</v>
+      </c>
+      <c r="C46">
+        <v>87.649720474082</v>
+      </c>
+      <c r="D46">
+        <v>146.273720474082</v>
+      </c>
+      <c r="E46">
+        <v>77.92399999999999</v>
+      </c>
+      <c r="F46">
+        <v>77.92399999999999</v>
+      </c>
+      <c r="G46">
+        <v>19.3</v>
+      </c>
+      <c r="H46">
+        <v>177.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>25.8</v>
+      </c>
+      <c r="K46">
+        <v>12.7</v>
+      </c>
+      <c r="L46">
+        <v>13.1</v>
+      </c>
+      <c r="M46">
+        <v>5.836507599999999</v>
+      </c>
+      <c r="N46">
+        <v>7.263492400000002</v>
+      </c>
+      <c r="O46">
+        <v>1.380063556000001</v>
+      </c>
+      <c r="P46">
+        <v>5.883428844000002</v>
+      </c>
+      <c r="Q46">
+        <v>18.583428844</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1329328282581212</v>
+      </c>
+      <c r="T46">
+        <v>1.481636566573125</v>
+      </c>
+      <c r="U46">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V46">
+        <v>0.19</v>
+      </c>
+      <c r="W46">
+        <v>0.060669</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.244492922445608</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1012461394888139</v>
+      </c>
+      <c r="C47">
+        <v>85.63629658538872</v>
+      </c>
+      <c r="D47">
+        <v>146.0312965853887</v>
+      </c>
+      <c r="E47">
+        <v>79.69499999999999</v>
+      </c>
+      <c r="F47">
+        <v>79.69499999999999</v>
+      </c>
+      <c r="G47">
+        <v>19.3</v>
+      </c>
+      <c r="H47">
+        <v>177.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>25.8</v>
+      </c>
+      <c r="K47">
+        <v>12.7</v>
+      </c>
+      <c r="L47">
+        <v>13.1</v>
+      </c>
+      <c r="M47">
+        <v>5.969155499999999</v>
+      </c>
+      <c r="N47">
+        <v>7.130844500000002</v>
+      </c>
+      <c r="O47">
+        <v>1.354860455</v>
+      </c>
+      <c r="P47">
+        <v>5.775984045000001</v>
+      </c>
+      <c r="Q47">
+        <v>18.475984045</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1344456172523888</v>
+      </c>
+      <c r="T47">
+        <v>1.505447637937838</v>
+      </c>
+      <c r="U47">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V47">
+        <v>0.19</v>
+      </c>
+      <c r="W47">
+        <v>0.060669</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.194615301946817</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1013555351530799</v>
+      </c>
+      <c r="C48">
+        <v>83.62367492012358</v>
+      </c>
+      <c r="D48">
+        <v>145.7896749201236</v>
+      </c>
+      <c r="E48">
+        <v>81.46599999999999</v>
+      </c>
+      <c r="F48">
+        <v>81.46599999999999</v>
+      </c>
+      <c r="G48">
+        <v>19.3</v>
+      </c>
+      <c r="H48">
+        <v>177.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>25.8</v>
+      </c>
+      <c r="K48">
+        <v>12.7</v>
+      </c>
+      <c r="L48">
+        <v>13.1</v>
+      </c>
+      <c r="M48">
+        <v>6.101803399999999</v>
+      </c>
+      <c r="N48">
+        <v>6.998196600000003</v>
+      </c>
+      <c r="O48">
+        <v>1.329657354000001</v>
+      </c>
+      <c r="P48">
+        <v>5.668539246000002</v>
+      </c>
+      <c r="Q48">
+        <v>18.368539246</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1360144354686664</v>
+      </c>
+      <c r="T48">
+        <v>1.530140600834576</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.19</v>
+      </c>
+      <c r="W48">
+        <v>0.060669</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.146906273643626</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1014649308173459</v>
+      </c>
+      <c r="C49">
+        <v>81.61185150281609</v>
+      </c>
+      <c r="D49">
+        <v>145.5488515028161</v>
+      </c>
+      <c r="E49">
+        <v>83.23700000000001</v>
+      </c>
+      <c r="F49">
+        <v>83.23700000000001</v>
+      </c>
+      <c r="G49">
+        <v>19.3</v>
+      </c>
+      <c r="H49">
+        <v>177.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>25.8</v>
+      </c>
+      <c r="K49">
+        <v>12.7</v>
+      </c>
+      <c r="L49">
+        <v>13.1</v>
+      </c>
+      <c r="M49">
+        <v>6.2344513</v>
+      </c>
+      <c r="N49">
+        <v>6.865548700000002</v>
+      </c>
+      <c r="O49">
+        <v>1.304454253</v>
+      </c>
+      <c r="P49">
+        <v>5.561094447000001</v>
+      </c>
+      <c r="Q49">
+        <v>18.261094447</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1376424543723507</v>
+      </c>
+      <c r="T49">
+        <v>1.555765373651947</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.19</v>
+      </c>
+      <c r="W49">
+        <v>0.060669</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.10122741675759</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1015743264816119</v>
+      </c>
+      <c r="C50">
+        <v>79.60082238422002</v>
+      </c>
+      <c r="D50">
+        <v>145.30882238422</v>
+      </c>
+      <c r="E50">
+        <v>85.008</v>
+      </c>
+      <c r="F50">
+        <v>85.008</v>
+      </c>
+      <c r="G50">
+        <v>19.3</v>
+      </c>
+      <c r="H50">
+        <v>177.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>25.8</v>
+      </c>
+      <c r="K50">
+        <v>12.7</v>
+      </c>
+      <c r="L50">
+        <v>13.1</v>
+      </c>
+      <c r="M50">
+        <v>6.367099199999999</v>
+      </c>
+      <c r="N50">
+        <v>6.732900800000002</v>
+      </c>
+      <c r="O50">
+        <v>1.279251152000001</v>
+      </c>
+      <c r="P50">
+        <v>5.453649648000002</v>
+      </c>
+      <c r="Q50">
+        <v>18.153649648</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1393330893877151</v>
+      </c>
+      <c r="T50">
+        <v>1.5823757146546</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.19</v>
+      </c>
+      <c r="W50">
+        <v>0.060669</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.057451845575141</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1016837221458779</v>
+      </c>
+      <c r="C51">
+        <v>77.59058364109734</v>
+      </c>
+      <c r="D51">
+        <v>145.0695836410973</v>
+      </c>
+      <c r="E51">
+        <v>86.779</v>
+      </c>
+      <c r="F51">
+        <v>86.779</v>
+      </c>
+      <c r="G51">
+        <v>19.3</v>
+      </c>
+      <c r="H51">
+        <v>177.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>25.8</v>
+      </c>
+      <c r="K51">
+        <v>12.7</v>
+      </c>
+      <c r="L51">
+        <v>13.1</v>
+      </c>
+      <c r="M51">
+        <v>6.4997471</v>
+      </c>
+      <c r="N51">
+        <v>6.600252900000002</v>
+      </c>
+      <c r="O51">
+        <v>1.254048051</v>
+      </c>
+      <c r="P51">
+        <v>5.346204849000001</v>
+      </c>
+      <c r="Q51">
+        <v>18.046204849</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1410900238154468</v>
+      </c>
+      <c r="T51">
+        <v>1.610029598441672</v>
+      </c>
+      <c r="U51">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V51">
+        <v>0.19</v>
+      </c>
+      <c r="W51">
+        <v>0.060669</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.015463032400138</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1083946178101439</v>
+      </c>
+      <c r="C52">
+        <v>62.51169719987637</v>
+      </c>
+      <c r="D52">
+        <v>131.7616971998764</v>
+      </c>
+      <c r="E52">
+        <v>88.55</v>
+      </c>
+      <c r="F52">
+        <v>88.55</v>
+      </c>
+      <c r="G52">
+        <v>19.3</v>
+      </c>
+      <c r="H52">
+        <v>177.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>25.8</v>
+      </c>
+      <c r="K52">
+        <v>12.7</v>
+      </c>
+      <c r="L52">
+        <v>13.1</v>
+      </c>
+      <c r="M52">
+        <v>8.075760000000001</v>
+      </c>
+      <c r="N52">
+        <v>5.024240000000001</v>
+      </c>
+      <c r="O52">
+        <v>0.9546056000000002</v>
+      </c>
+      <c r="P52">
+        <v>4.069634400000001</v>
+      </c>
+      <c r="Q52">
+        <v>16.7696344</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1429172356202877</v>
+      </c>
+      <c r="T52">
+        <v>1.638789637580227</v>
+      </c>
+      <c r="U52">
+        <v>0.0912</v>
+      </c>
+      <c r="V52">
+        <v>0.19</v>
+      </c>
+      <c r="W52">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.622138349827137</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1086360434744099</v>
+      </c>
+      <c r="C53">
+        <v>60.30729215079583</v>
+      </c>
+      <c r="D53">
+        <v>131.3282921507958</v>
+      </c>
+      <c r="E53">
+        <v>90.321</v>
+      </c>
+      <c r="F53">
+        <v>90.321</v>
+      </c>
+      <c r="G53">
+        <v>19.3</v>
+      </c>
+      <c r="H53">
+        <v>177.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>25.8</v>
+      </c>
+      <c r="K53">
+        <v>12.7</v>
+      </c>
+      <c r="L53">
+        <v>13.1</v>
+      </c>
+      <c r="M53">
+        <v>8.237275200000001</v>
+      </c>
+      <c r="N53">
+        <v>4.862724800000001</v>
+      </c>
+      <c r="O53">
+        <v>0.9239177120000001</v>
+      </c>
+      <c r="P53">
+        <v>3.938807088</v>
+      </c>
+      <c r="Q53">
+        <v>16.638807088</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1448190274987956</v>
+      </c>
+      <c r="T53">
+        <v>1.668723555867294</v>
+      </c>
+      <c r="U53">
+        <v>0.0912</v>
+      </c>
+      <c r="V53">
+        <v>0.19</v>
+      </c>
+      <c r="W53">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>1.590331715516801</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1088774691386759</v>
+      </c>
+      <c r="C54">
+        <v>58.10572896095773</v>
+      </c>
+      <c r="D54">
+        <v>130.8977289609577</v>
+      </c>
+      <c r="E54">
+        <v>92.092</v>
+      </c>
+      <c r="F54">
+        <v>92.092</v>
+      </c>
+      <c r="G54">
+        <v>19.3</v>
+      </c>
+      <c r="H54">
+        <v>177.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>25.8</v>
+      </c>
+      <c r="K54">
+        <v>12.7</v>
+      </c>
+      <c r="L54">
+        <v>13.1</v>
+      </c>
+      <c r="M54">
+        <v>8.398790399999999</v>
+      </c>
+      <c r="N54">
+        <v>4.701209600000002</v>
+      </c>
+      <c r="O54">
+        <v>0.8932298240000004</v>
+      </c>
+      <c r="P54">
+        <v>3.807979776000002</v>
+      </c>
+      <c r="Q54">
+        <v>16.507979776</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1468000607055747</v>
+      </c>
+      <c r="T54">
+        <v>1.699904720749655</v>
+      </c>
+      <c r="U54">
+        <v>0.0912</v>
+      </c>
+      <c r="V54">
+        <v>0.19</v>
+      </c>
+      <c r="W54">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>1.559748413295324</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1091188948029418</v>
+      </c>
+      <c r="C55">
+        <v>55.90697977037561</v>
+      </c>
+      <c r="D55">
+        <v>130.4699797703756</v>
+      </c>
+      <c r="E55">
+        <v>93.863</v>
+      </c>
+      <c r="F55">
+        <v>93.863</v>
+      </c>
+      <c r="G55">
+        <v>19.3</v>
+      </c>
+      <c r="H55">
+        <v>177.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>25.8</v>
+      </c>
+      <c r="K55">
+        <v>12.7</v>
+      </c>
+      <c r="L55">
+        <v>13.1</v>
+      </c>
+      <c r="M55">
+        <v>8.5603056</v>
+      </c>
+      <c r="N55">
+        <v>4.539694400000002</v>
+      </c>
+      <c r="O55">
+        <v>0.8625419360000004</v>
+      </c>
+      <c r="P55">
+        <v>3.677152464000002</v>
+      </c>
+      <c r="Q55">
+        <v>16.377152464</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1488653931977486</v>
+      </c>
+      <c r="T55">
+        <v>1.732412743712117</v>
+      </c>
+      <c r="U55">
+        <v>0.0912</v>
+      </c>
+      <c r="V55">
+        <v>0.19</v>
+      </c>
+      <c r="W55">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>1.53031919795013</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1093603204672078</v>
+      </c>
+      <c r="C56">
+        <v>53.71101708204144</v>
+      </c>
+      <c r="D56">
+        <v>130.0450170820414</v>
+      </c>
+      <c r="E56">
+        <v>95.634</v>
+      </c>
+      <c r="F56">
+        <v>95.634</v>
+      </c>
+      <c r="G56">
+        <v>19.3</v>
+      </c>
+      <c r="H56">
+        <v>177.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>25.8</v>
+      </c>
+      <c r="K56">
+        <v>12.7</v>
+      </c>
+      <c r="L56">
+        <v>13.1</v>
+      </c>
+      <c r="M56">
+        <v>8.7218208</v>
+      </c>
+      <c r="N56">
+        <v>4.378179200000002</v>
+      </c>
+      <c r="O56">
+        <v>0.8318540480000003</v>
+      </c>
+      <c r="P56">
+        <v>3.546325152000001</v>
+      </c>
+      <c r="Q56">
+        <v>16.246325152</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1510205227547997</v>
+      </c>
+      <c r="T56">
+        <v>1.766334158977295</v>
+      </c>
+      <c r="U56">
+        <v>0.0912</v>
+      </c>
+      <c r="V56">
+        <v>0.19</v>
+      </c>
+      <c r="W56">
+        <v>0.07387200000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>1.501979953543646</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1418966449686587</v>
+      </c>
+      <c r="C57">
+        <v>12.26929002079898</v>
+      </c>
+      <c r="D57">
+        <v>90.37429002079898</v>
+      </c>
+      <c r="E57">
+        <v>97.405</v>
+      </c>
+      <c r="F57">
+        <v>97.405</v>
+      </c>
+      <c r="G57">
+        <v>19.3</v>
+      </c>
+      <c r="H57">
+        <v>177.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>25.8</v>
+      </c>
+      <c r="K57">
+        <v>12.7</v>
+      </c>
+      <c r="L57">
+        <v>13.1</v>
+      </c>
+      <c r="M57">
+        <v>15.253623</v>
+      </c>
+      <c r="N57">
+        <v>-2.153623</v>
+      </c>
+      <c r="O57">
+        <v>-0.4091883699999999</v>
+      </c>
+      <c r="P57">
+        <v>-1.74443463</v>
+      </c>
+      <c r="Q57">
+        <v>10.95556537</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1551574480701355</v>
+      </c>
+      <c r="T57">
+        <v>1.831448741570906</v>
+      </c>
+      <c r="U57">
+        <v>0.1566</v>
+      </c>
+      <c r="V57">
+        <v>0.1631743488088043</v>
+      </c>
+      <c r="W57">
+        <v>0.1310468969765413</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.8588123621516016</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1430746449686587</v>
+      </c>
+      <c r="C58">
+        <v>9.51103854274993</v>
+      </c>
+      <c r="D58">
+        <v>89.38703854274993</v>
+      </c>
+      <c r="E58">
+        <v>99.176</v>
+      </c>
+      <c r="F58">
+        <v>99.176</v>
+      </c>
+      <c r="G58">
+        <v>19.3</v>
+      </c>
+      <c r="H58">
+        <v>177.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>25.8</v>
+      </c>
+      <c r="K58">
+        <v>12.7</v>
+      </c>
+      <c r="L58">
+        <v>13.1</v>
+      </c>
+      <c r="M58">
+        <v>15.5309616</v>
+      </c>
+      <c r="N58">
+        <v>-2.4309616</v>
+      </c>
+      <c r="O58">
+        <v>-0.461882704</v>
+      </c>
+      <c r="P58">
+        <v>-1.969078896</v>
+      </c>
+      <c r="Q58">
+        <v>10.730921104</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.157801935526275</v>
+      </c>
+      <c r="T58">
+        <v>1.873072576606609</v>
+      </c>
+      <c r="U58">
+        <v>0.1566</v>
+      </c>
+      <c r="V58">
+        <v>0.1602605211515042</v>
+      </c>
+      <c r="W58">
+        <v>0.1315032023876745</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.8434764271131802</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1442526449686587</v>
+      </c>
+      <c r="C59">
+        <v>6.774123514697678</v>
+      </c>
+      <c r="D59">
+        <v>88.42112351469768</v>
+      </c>
+      <c r="E59">
+        <v>100.947</v>
+      </c>
+      <c r="F59">
+        <v>100.947</v>
+      </c>
+      <c r="G59">
+        <v>19.3</v>
+      </c>
+      <c r="H59">
+        <v>177.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>25.8</v>
+      </c>
+      <c r="K59">
+        <v>12.7</v>
+      </c>
+      <c r="L59">
+        <v>13.1</v>
+      </c>
+      <c r="M59">
+        <v>15.8083002</v>
+      </c>
+      <c r="N59">
+        <v>-2.7083002</v>
+      </c>
+      <c r="O59">
+        <v>-0.514577038</v>
+      </c>
+      <c r="P59">
+        <v>-2.193723162</v>
+      </c>
+      <c r="Q59">
+        <v>10.506276838</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1605694223989791</v>
+      </c>
+      <c r="T59">
+        <v>1.916632403969553</v>
+      </c>
+      <c r="U59">
+        <v>0.1566</v>
+      </c>
+      <c r="V59">
+        <v>0.157448933061127</v>
+      </c>
+      <c r="W59">
+        <v>0.1319434970826275</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.828678595058563</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1454306449686587</v>
+      </c>
+      <c r="C60">
+        <v>4.05786064696882</v>
+      </c>
+      <c r="D60">
+        <v>87.47586064696881</v>
+      </c>
+      <c r="E60">
+        <v>102.718</v>
+      </c>
+      <c r="F60">
+        <v>102.718</v>
+      </c>
+      <c r="G60">
+        <v>19.3</v>
+      </c>
+      <c r="H60">
+        <v>177.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>25.8</v>
+      </c>
+      <c r="K60">
+        <v>12.7</v>
+      </c>
+      <c r="L60">
+        <v>13.1</v>
+      </c>
+      <c r="M60">
+        <v>16.0856388</v>
+      </c>
+      <c r="N60">
+        <v>-2.9856388</v>
+      </c>
+      <c r="O60">
+        <v>-0.5672713720000001</v>
+      </c>
+      <c r="P60">
+        <v>-2.418367428</v>
+      </c>
+      <c r="Q60">
+        <v>10.281632572</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1634686943608595</v>
+      </c>
+      <c r="T60">
+        <v>1.962266508825971</v>
+      </c>
+      <c r="U60">
+        <v>0.1566</v>
+      </c>
+      <c r="V60">
+        <v>0.154734296284211</v>
+      </c>
+      <c r="W60">
+        <v>0.1323686092018926</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.8143910330747947</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1466086449686587</v>
+      </c>
+      <c r="C61">
+        <v>1.361594601877101</v>
+      </c>
+      <c r="D61">
+        <v>86.55059460187709</v>
+      </c>
+      <c r="E61">
+        <v>104.489</v>
+      </c>
+      <c r="F61">
+        <v>104.489</v>
+      </c>
+      <c r="G61">
+        <v>19.3</v>
+      </c>
+      <c r="H61">
+        <v>177.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>25.8</v>
+      </c>
+      <c r="K61">
+        <v>12.7</v>
+      </c>
+      <c r="L61">
+        <v>13.1</v>
+      </c>
+      <c r="M61">
+        <v>16.3629774</v>
+      </c>
+      <c r="N61">
+        <v>-3.2629774</v>
+      </c>
+      <c r="O61">
+        <v>-0.6199657060000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.643011694</v>
+      </c>
+      <c r="Q61">
+        <v>10.056988306</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1665093942233195</v>
+      </c>
+      <c r="T61">
+        <v>2.010126667577824</v>
+      </c>
+      <c r="U61">
+        <v>0.1566</v>
+      </c>
+      <c r="V61">
+        <v>0.1521116810929532</v>
+      </c>
+      <c r="W61">
+        <v>0.1327793107408436</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.8005877952260693</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1803972657099794</v>
+      </c>
+      <c r="C62">
+        <v>-20.55586361586543</v>
+      </c>
+      <c r="D62">
+        <v>66.40413638413456</v>
+      </c>
+      <c r="E62">
+        <v>106.26</v>
+      </c>
+      <c r="F62">
+        <v>106.26</v>
+      </c>
+      <c r="G62">
+        <v>19.3</v>
+      </c>
+      <c r="H62">
+        <v>177.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>25.8</v>
+      </c>
+      <c r="K62">
+        <v>12.7</v>
+      </c>
+      <c r="L62">
+        <v>13.1</v>
+      </c>
+      <c r="M62">
+        <v>22.187088</v>
+      </c>
+      <c r="N62">
+        <v>-9.087087999999998</v>
+      </c>
+      <c r="O62">
+        <v>-1.72654672</v>
+      </c>
+      <c r="P62">
+        <v>-7.360541279999998</v>
+      </c>
+      <c r="Q62">
+        <v>5.339458720000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1729286809322044</v>
+      </c>
+      <c r="T62">
+        <v>2.111165275417382</v>
+      </c>
+      <c r="U62">
+        <v>0.2088</v>
+      </c>
+      <c r="V62">
+        <v>0.112182364806053</v>
+      </c>
+      <c r="W62">
+        <v>0.1853763222284961</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5904334989792261</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1820972657099794</v>
+      </c>
+      <c r="C63">
+        <v>-23.09554368022179</v>
+      </c>
+      <c r="D63">
+        <v>65.6354563197782</v>
+      </c>
+      <c r="E63">
+        <v>108.031</v>
+      </c>
+      <c r="F63">
+        <v>108.031</v>
+      </c>
+      <c r="G63">
+        <v>19.3</v>
+      </c>
+      <c r="H63">
+        <v>177.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>25.8</v>
+      </c>
+      <c r="K63">
+        <v>12.7</v>
+      </c>
+      <c r="L63">
+        <v>13.1</v>
+      </c>
+      <c r="M63">
+        <v>22.5568728</v>
+      </c>
+      <c r="N63">
+        <v>-9.456872799999999</v>
+      </c>
+      <c r="O63">
+        <v>-1.796805832</v>
+      </c>
+      <c r="P63">
+        <v>-7.660066967999999</v>
+      </c>
+      <c r="Q63">
+        <v>5.039933032</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.176367877879184</v>
+      </c>
+      <c r="T63">
+        <v>2.165297718376801</v>
+      </c>
+      <c r="U63">
+        <v>0.2088</v>
+      </c>
+      <c r="V63">
+        <v>0.110343309645298</v>
+      </c>
+      <c r="W63">
+        <v>0.1857603169460618</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5807542612910421</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1837972657099795</v>
+      </c>
+      <c r="C64">
+        <v>-25.61763123997352</v>
+      </c>
+      <c r="D64">
+        <v>64.88436876002648</v>
+      </c>
+      <c r="E64">
+        <v>109.802</v>
+      </c>
+      <c r="F64">
+        <v>109.802</v>
+      </c>
+      <c r="G64">
+        <v>19.3</v>
+      </c>
+      <c r="H64">
+        <v>177.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>25.8</v>
+      </c>
+      <c r="K64">
+        <v>12.7</v>
+      </c>
+      <c r="L64">
+        <v>13.1</v>
+      </c>
+      <c r="M64">
+        <v>22.9266576</v>
+      </c>
+      <c r="N64">
+        <v>-9.826657599999997</v>
+      </c>
+      <c r="O64">
+        <v>-1.867064944</v>
+      </c>
+      <c r="P64">
+        <v>-7.959592655999998</v>
+      </c>
+      <c r="Q64">
+        <v>4.740407344000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1799880851917941</v>
+      </c>
+      <c r="T64">
+        <v>2.222279237281454</v>
+      </c>
+      <c r="U64">
+        <v>0.2088</v>
+      </c>
+      <c r="V64">
+        <v>0.1085635788445674</v>
+      </c>
+      <c r="W64">
+        <v>0.1861319247372543</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5713872570766705</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1854972657099794</v>
+      </c>
+      <c r="C65">
+        <v>-28.12272341212265</v>
+      </c>
+      <c r="D65">
+        <v>64.15027658787734</v>
+      </c>
+      <c r="E65">
+        <v>111.573</v>
+      </c>
+      <c r="F65">
+        <v>111.573</v>
+      </c>
+      <c r="G65">
+        <v>19.3</v>
+      </c>
+      <c r="H65">
+        <v>177.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>25.8</v>
+      </c>
+      <c r="K65">
+        <v>12.7</v>
+      </c>
+      <c r="L65">
+        <v>13.1</v>
+      </c>
+      <c r="M65">
+        <v>23.2964424</v>
+      </c>
+      <c r="N65">
+        <v>-10.1964424</v>
+      </c>
+      <c r="O65">
+        <v>-1.937324056</v>
+      </c>
+      <c r="P65">
+        <v>-8.259118343999999</v>
+      </c>
+      <c r="Q65">
+        <v>4.440881656</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1838039793861669</v>
+      </c>
+      <c r="T65">
+        <v>2.282340838289061</v>
+      </c>
+      <c r="U65">
+        <v>0.2088</v>
+      </c>
+      <c r="V65">
+        <v>0.1068403474343362</v>
+      </c>
+      <c r="W65">
+        <v>0.1864917354557106</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.5623176180754534</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1871972657099795</v>
+      </c>
+      <c r="C66">
+        <v>-30.61139059320816</v>
+      </c>
+      <c r="D66">
+        <v>63.43260940679183</v>
+      </c>
+      <c r="E66">
+        <v>113.344</v>
+      </c>
+      <c r="F66">
+        <v>113.344</v>
+      </c>
+      <c r="G66">
+        <v>19.3</v>
+      </c>
+      <c r="H66">
+        <v>177.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>25.8</v>
+      </c>
+      <c r="K66">
+        <v>12.7</v>
+      </c>
+      <c r="L66">
+        <v>13.1</v>
+      </c>
+      <c r="M66">
+        <v>23.6662272</v>
+      </c>
+      <c r="N66">
+        <v>-10.5662272</v>
+      </c>
+      <c r="O66">
+        <v>-2.007583168</v>
+      </c>
+      <c r="P66">
+        <v>-8.558644032</v>
+      </c>
+      <c r="Q66">
+        <v>4.141355967999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1878318677024493</v>
+      </c>
+      <c r="T66">
+        <v>2.345739194908202</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1051709670056746</v>
+      </c>
+      <c r="W66">
+        <v>0.1868403020892151</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5535314052930245</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1888972657099795</v>
+      </c>
+      <c r="C67">
+        <v>-33.0841779374164</v>
+      </c>
+      <c r="D67">
+        <v>62.73082206258359</v>
+      </c>
+      <c r="E67">
+        <v>115.115</v>
+      </c>
+      <c r="F67">
+        <v>115.115</v>
+      </c>
+      <c r="G67">
+        <v>19.3</v>
+      </c>
+      <c r="H67">
+        <v>177.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>25.8</v>
+      </c>
+      <c r="K67">
+        <v>12.7</v>
+      </c>
+      <c r="L67">
+        <v>13.1</v>
+      </c>
+      <c r="M67">
+        <v>24.036012</v>
+      </c>
+      <c r="N67">
+        <v>-10.936012</v>
+      </c>
+      <c r="O67">
+        <v>-2.07784228</v>
+      </c>
+      <c r="P67">
+        <v>-8.858169719999999</v>
+      </c>
+      <c r="Q67">
+        <v>3.84183028</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1920899210653765</v>
+      </c>
+      <c r="T67">
+        <v>2.412760314762722</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1035529521286643</v>
+      </c>
+      <c r="W67">
+        <v>0.1871781435955349</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5450155375192858</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1905972657099794</v>
+      </c>
+      <c r="C68">
+        <v>-35.54160673764694</v>
+      </c>
+      <c r="D68">
+        <v>62.04439326235305</v>
+      </c>
+      <c r="E68">
+        <v>116.886</v>
+      </c>
+      <c r="F68">
+        <v>116.886</v>
+      </c>
+      <c r="G68">
+        <v>19.3</v>
+      </c>
+      <c r="H68">
+        <v>177.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>25.8</v>
+      </c>
+      <c r="K68">
+        <v>12.7</v>
+      </c>
+      <c r="L68">
+        <v>13.1</v>
+      </c>
+      <c r="M68">
+        <v>24.4057968</v>
+      </c>
+      <c r="N68">
+        <v>-11.3057968</v>
+      </c>
+      <c r="O68">
+        <v>-2.148101392</v>
+      </c>
+      <c r="P68">
+        <v>-9.157695407999999</v>
+      </c>
+      <c r="Q68">
+        <v>3.542304592000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1965984481555346</v>
+      </c>
+      <c r="T68">
+        <v>2.483723853432213</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1019839680055027</v>
+      </c>
+      <c r="W68">
+        <v>0.187505747480451</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5367577263447511</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1922972657099794</v>
+      </c>
+      <c r="C69">
+        <v>-37.98417571688636</v>
+      </c>
+      <c r="D69">
+        <v>61.37282428311364</v>
+      </c>
+      <c r="E69">
+        <v>118.657</v>
+      </c>
+      <c r="F69">
+        <v>118.657</v>
+      </c>
+      <c r="G69">
+        <v>19.3</v>
+      </c>
+      <c r="H69">
+        <v>177.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>25.8</v>
+      </c>
+      <c r="K69">
+        <v>12.7</v>
+      </c>
+      <c r="L69">
+        <v>13.1</v>
+      </c>
+      <c r="M69">
+        <v>24.7755816</v>
+      </c>
+      <c r="N69">
+        <v>-11.6755816</v>
+      </c>
+      <c r="O69">
+        <v>-2.218360504</v>
+      </c>
+      <c r="P69">
+        <v>-9.457221096000001</v>
+      </c>
+      <c r="Q69">
+        <v>3.242778903999998</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2013802193117629</v>
+      </c>
+      <c r="T69">
+        <v>2.558988212627129</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1004618192293012</v>
+      </c>
+      <c r="W69">
+        <v>0.1878235721449219</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5287464169963219</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1939972657099795</v>
+      </c>
+      <c r="C70">
+        <v>-40.41236223661291</v>
+      </c>
+      <c r="D70">
+        <v>60.7156377633871</v>
+      </c>
+      <c r="E70">
+        <v>120.428</v>
+      </c>
+      <c r="F70">
+        <v>120.428</v>
+      </c>
+      <c r="G70">
+        <v>19.3</v>
+      </c>
+      <c r="H70">
+        <v>177.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>25.8</v>
+      </c>
+      <c r="K70">
+        <v>12.7</v>
+      </c>
+      <c r="L70">
+        <v>13.1</v>
+      </c>
+      <c r="M70">
+        <v>25.1453664</v>
+      </c>
+      <c r="N70">
+        <v>-12.0453664</v>
+      </c>
+      <c r="O70">
+        <v>-2.288619616000001</v>
+      </c>
+      <c r="P70">
+        <v>-9.756746784000002</v>
+      </c>
+      <c r="Q70">
+        <v>2.943253215999997</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2064608511652555</v>
+      </c>
+      <c r="T70">
+        <v>2.638956594271727</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.09898443953475261</v>
+      </c>
+      <c r="W70">
+        <v>0.1881320490251437</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5209707343934348</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1956972657099795</v>
+      </c>
+      <c r="C71">
+        <v>-42.82662342838537</v>
+      </c>
+      <c r="D71">
+        <v>60.07237657161463</v>
+      </c>
+      <c r="E71">
+        <v>122.199</v>
+      </c>
+      <c r="F71">
+        <v>122.199</v>
+      </c>
+      <c r="G71">
+        <v>19.3</v>
+      </c>
+      <c r="H71">
+        <v>177.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>25.8</v>
+      </c>
+      <c r="K71">
+        <v>12.7</v>
+      </c>
+      <c r="L71">
+        <v>13.1</v>
+      </c>
+      <c r="M71">
+        <v>25.51515120000001</v>
+      </c>
+      <c r="N71">
+        <v>-12.4151512</v>
+      </c>
+      <c r="O71">
+        <v>-2.358878728000001</v>
+      </c>
+      <c r="P71">
+        <v>-10.056272472</v>
+      </c>
+      <c r="Q71">
+        <v>2.643727527999996</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2118692657189734</v>
+      </c>
+      <c r="T71">
+        <v>2.724084226345009</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.09754988244004605</v>
+      </c>
+      <c r="W71">
+        <v>0.1884315845465184</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5134204338949792</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1973972657099795</v>
+      </c>
+      <c r="C72">
+        <v>-45.22739725425376</v>
+      </c>
+      <c r="D72">
+        <v>59.44260274574626</v>
+      </c>
+      <c r="E72">
+        <v>123.97</v>
+      </c>
+      <c r="F72">
+        <v>123.97</v>
+      </c>
+      <c r="G72">
+        <v>19.3</v>
+      </c>
+      <c r="H72">
+        <v>177.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>25.8</v>
+      </c>
+      <c r="K72">
+        <v>12.7</v>
+      </c>
+      <c r="L72">
+        <v>13.1</v>
+      </c>
+      <c r="M72">
+        <v>25.884936</v>
+      </c>
+      <c r="N72">
+        <v>-12.784936</v>
+      </c>
+      <c r="O72">
+        <v>-2.429137840000001</v>
+      </c>
+      <c r="P72">
+        <v>-10.35579816</v>
+      </c>
+      <c r="Q72">
+        <v>2.344201839999998</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2176382412429392</v>
+      </c>
+      <c r="T72">
+        <v>2.814887033889843</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.09615631269090255</v>
+      </c>
+      <c r="W72">
+        <v>0.1887225619101396</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.506085856267908</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.220883680562236</v>
+      </c>
+      <c r="C73">
+        <v>-54.51864248250389</v>
+      </c>
+      <c r="D73">
+        <v>51.92235751749609</v>
+      </c>
+      <c r="E73">
+        <v>125.741</v>
+      </c>
+      <c r="F73">
+        <v>125.741</v>
+      </c>
+      <c r="G73">
+        <v>19.3</v>
+      </c>
+      <c r="H73">
+        <v>177.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>25.8</v>
+      </c>
+      <c r="K73">
+        <v>12.7</v>
+      </c>
+      <c r="L73">
+        <v>13.1</v>
+      </c>
+      <c r="M73">
+        <v>30.0269508</v>
+      </c>
+      <c r="N73">
+        <v>-16.9269508</v>
+      </c>
+      <c r="O73">
+        <v>-3.216120651999999</v>
+      </c>
+      <c r="P73">
+        <v>-13.710830148</v>
+      </c>
+      <c r="Q73">
+        <v>-1.010830147999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2254823697418563</v>
+      </c>
+      <c r="T73">
+        <v>2.938352437319822</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.08289219963020689</v>
+      </c>
+      <c r="W73">
+        <v>0.2190053427283066</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.4362747348958257</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.222883680562236</v>
+      </c>
+      <c r="C74">
+        <v>-56.84305389288329</v>
+      </c>
+      <c r="D74">
+        <v>51.3689461071167</v>
+      </c>
+      <c r="E74">
+        <v>127.512</v>
+      </c>
+      <c r="F74">
+        <v>127.512</v>
+      </c>
+      <c r="G74">
+        <v>19.3</v>
+      </c>
+      <c r="H74">
+        <v>177.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>25.8</v>
+      </c>
+      <c r="K74">
+        <v>12.7</v>
+      </c>
+      <c r="L74">
+        <v>13.1</v>
+      </c>
+      <c r="M74">
+        <v>30.4498656</v>
+      </c>
+      <c r="N74">
+        <v>-17.3498656</v>
+      </c>
+      <c r="O74">
+        <v>-3.296474464</v>
+      </c>
+      <c r="P74">
+        <v>-14.053391136</v>
+      </c>
+      <c r="Q74">
+        <v>-1.353391135999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2321495972326369</v>
+      </c>
+      <c r="T74">
+        <v>3.04329359579553</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08174091907978735</v>
+      </c>
+      <c r="W74">
+        <v>0.2192802685237468</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.4302153635778281</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.224883680562236</v>
+      </c>
+      <c r="C75">
+        <v>-59.1557927086387</v>
+      </c>
+      <c r="D75">
+        <v>50.82720729136128</v>
+      </c>
+      <c r="E75">
+        <v>129.283</v>
+      </c>
+      <c r="F75">
+        <v>129.283</v>
+      </c>
+      <c r="G75">
+        <v>19.3</v>
+      </c>
+      <c r="H75">
+        <v>177.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>25.8</v>
+      </c>
+      <c r="K75">
+        <v>12.7</v>
+      </c>
+      <c r="L75">
+        <v>13.1</v>
+      </c>
+      <c r="M75">
+        <v>30.8727804</v>
+      </c>
+      <c r="N75">
+        <v>-17.7727804</v>
+      </c>
+      <c r="O75">
+        <v>-3.376828276</v>
+      </c>
+      <c r="P75">
+        <v>-14.395952124</v>
+      </c>
+      <c r="Q75">
+        <v>-1.695952124</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2393106934264382</v>
+      </c>
+      <c r="T75">
+        <v>3.156008173417586</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.08062118046225601</v>
+      </c>
+      <c r="W75">
+        <v>0.2195476621056133</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.4243220024329264</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.226883680562236</v>
+      </c>
+      <c r="C76">
+        <v>-61.45722437462595</v>
+      </c>
+      <c r="D76">
+        <v>50.29677562537405</v>
+      </c>
+      <c r="E76">
+        <v>131.054</v>
+      </c>
+      <c r="F76">
+        <v>131.054</v>
+      </c>
+      <c r="G76">
+        <v>19.3</v>
+      </c>
+      <c r="H76">
+        <v>177.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>25.8</v>
+      </c>
+      <c r="K76">
+        <v>12.7</v>
+      </c>
+      <c r="L76">
+        <v>13.1</v>
+      </c>
+      <c r="M76">
+        <v>31.2956952</v>
+      </c>
+      <c r="N76">
+        <v>-18.1956952</v>
+      </c>
+      <c r="O76">
+        <v>-3.457182088</v>
+      </c>
+      <c r="P76">
+        <v>-14.738513112</v>
+      </c>
+      <c r="Q76">
+        <v>-2.038513112</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2470226431736089</v>
+      </c>
+      <c r="T76">
+        <v>3.277393103164416</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0795317050506039</v>
+      </c>
+      <c r="W76">
+        <v>0.2198078288339158</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.4185879213189679</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.228883680562236</v>
+      </c>
+      <c r="C77">
+        <v>-63.74769923815907</v>
+      </c>
+      <c r="D77">
+        <v>49.77730076184091</v>
+      </c>
+      <c r="E77">
+        <v>132.825</v>
+      </c>
+      <c r="F77">
+        <v>132.825</v>
+      </c>
+      <c r="G77">
+        <v>19.3</v>
+      </c>
+      <c r="H77">
+        <v>177.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>25.8</v>
+      </c>
+      <c r="K77">
+        <v>12.7</v>
+      </c>
+      <c r="L77">
+        <v>13.1</v>
+      </c>
+      <c r="M77">
+        <v>31.71861</v>
+      </c>
+      <c r="N77">
+        <v>-18.61861</v>
+      </c>
+      <c r="O77">
+        <v>-3.5375359</v>
+      </c>
+      <c r="P77">
+        <v>-15.0810741</v>
+      </c>
+      <c r="Q77">
+        <v>-2.381074099999998</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2553515489005533</v>
+      </c>
+      <c r="T77">
+        <v>3.408488827290993</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07847128231659585</v>
+      </c>
+      <c r="W77">
+        <v>0.2200610577827969</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.413006749034715</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.230883680562236</v>
+      </c>
+      <c r="C78">
+        <v>-66.02755332069219</v>
+      </c>
+      <c r="D78">
+        <v>49.26844667930781</v>
+      </c>
+      <c r="E78">
+        <v>134.596</v>
+      </c>
+      <c r="F78">
+        <v>134.596</v>
+      </c>
+      <c r="G78">
+        <v>19.3</v>
+      </c>
+      <c r="H78">
+        <v>177.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>25.8</v>
+      </c>
+      <c r="K78">
+        <v>12.7</v>
+      </c>
+      <c r="L78">
+        <v>13.1</v>
+      </c>
+      <c r="M78">
+        <v>32.1415248</v>
+      </c>
+      <c r="N78">
+        <v>-19.0415248</v>
+      </c>
+      <c r="O78">
+        <v>-3.617889712</v>
+      </c>
+      <c r="P78">
+        <v>-15.423635088</v>
+      </c>
+      <c r="Q78">
+        <v>-2.723635087999998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.264374530104743</v>
+      </c>
+      <c r="T78">
+        <v>3.550509195094785</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07743876544400907</v>
+      </c>
+      <c r="W78">
+        <v>0.2203076228119706</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.4075724497053108</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.232883680562236</v>
+      </c>
+      <c r="C79">
+        <v>-68.29710904264824</v>
+      </c>
+      <c r="D79">
+        <v>48.76989095735174</v>
+      </c>
+      <c r="E79">
+        <v>136.367</v>
+      </c>
+      <c r="F79">
+        <v>136.367</v>
+      </c>
+      <c r="G79">
+        <v>19.3</v>
+      </c>
+      <c r="H79">
+        <v>177.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>25.8</v>
+      </c>
+      <c r="K79">
+        <v>12.7</v>
+      </c>
+      <c r="L79">
+        <v>13.1</v>
+      </c>
+      <c r="M79">
+        <v>32.5644396</v>
+      </c>
+      <c r="N79">
+        <v>-19.4644396</v>
+      </c>
+      <c r="O79">
+        <v>-3.698243524</v>
+      </c>
+      <c r="P79">
+        <v>-15.766196076</v>
+      </c>
+      <c r="Q79">
+        <v>-3.066196076000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2741821183701666</v>
+      </c>
+      <c r="T79">
+        <v>3.704879160098906</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07643306719148946</v>
+      </c>
+      <c r="W79">
+        <v>0.2205477835546723</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4022793010078393</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.234883680562236</v>
+      </c>
+      <c r="C80">
+        <v>-70.55667590468097</v>
+      </c>
+      <c r="D80">
+        <v>48.28132409531903</v>
+      </c>
+      <c r="E80">
+        <v>138.138</v>
+      </c>
+      <c r="F80">
+        <v>138.138</v>
+      </c>
+      <c r="G80">
+        <v>19.3</v>
+      </c>
+      <c r="H80">
+        <v>177.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>25.8</v>
+      </c>
+      <c r="K80">
+        <v>12.7</v>
+      </c>
+      <c r="L80">
+        <v>13.1</v>
+      </c>
+      <c r="M80">
+        <v>32.9873544</v>
+      </c>
+      <c r="N80">
+        <v>-19.8873544</v>
+      </c>
+      <c r="O80">
+        <v>-3.778597336</v>
+      </c>
+      <c r="P80">
+        <v>-16.108757064</v>
+      </c>
+      <c r="Q80">
+        <v>-3.408757064</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2848813055688106</v>
+      </c>
+      <c r="T80">
+        <v>3.87328275828522</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07545315607364986</v>
+      </c>
+      <c r="W80">
+        <v>0.2207817863296124</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3971218740718413</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.236883680562236</v>
+      </c>
+      <c r="C81">
+        <v>-72.80655112839437</v>
+      </c>
+      <c r="D81">
+        <v>47.80244887160561</v>
+      </c>
+      <c r="E81">
+        <v>139.909</v>
+      </c>
+      <c r="F81">
+        <v>139.909</v>
+      </c>
+      <c r="G81">
+        <v>19.3</v>
+      </c>
+      <c r="H81">
+        <v>177.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>25.8</v>
+      </c>
+      <c r="K81">
+        <v>12.7</v>
+      </c>
+      <c r="L81">
+        <v>13.1</v>
+      </c>
+      <c r="M81">
+        <v>33.4102692</v>
+      </c>
+      <c r="N81">
+        <v>-20.3102692</v>
+      </c>
+      <c r="O81">
+        <v>-3.858951148</v>
+      </c>
+      <c r="P81">
+        <v>-16.451318052</v>
+      </c>
+      <c r="Q81">
+        <v>-3.751318052000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2965994629768492</v>
+      </c>
+      <c r="T81">
+        <v>4.057724794394041</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07449805283221125</v>
+      </c>
+      <c r="W81">
+        <v>0.221009864983668</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.392095014906375</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.238883680562236</v>
+      </c>
+      <c r="C82">
+        <v>-75.04702025930712</v>
+      </c>
+      <c r="D82">
+        <v>47.33297974069288</v>
+      </c>
+      <c r="E82">
+        <v>141.68</v>
+      </c>
+      <c r="F82">
+        <v>141.68</v>
+      </c>
+      <c r="G82">
+        <v>19.3</v>
+      </c>
+      <c r="H82">
+        <v>177.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>25.8</v>
+      </c>
+      <c r="K82">
+        <v>12.7</v>
+      </c>
+      <c r="L82">
+        <v>13.1</v>
+      </c>
+      <c r="M82">
+        <v>33.833184</v>
+      </c>
+      <c r="N82">
+        <v>-20.733184</v>
+      </c>
+      <c r="O82">
+        <v>-3.93930496</v>
+      </c>
+      <c r="P82">
+        <v>-16.79387904</v>
+      </c>
+      <c r="Q82">
+        <v>-4.093879040000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3094894361256916</v>
+      </c>
+      <c r="T82">
+        <v>4.260611034113742</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0735668271718086</v>
+      </c>
+      <c r="W82">
+        <v>0.2212322416713721</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3871938272200453</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.240883680562236</v>
+      </c>
+      <c r="C83">
+        <v>-77.27835773463208</v>
+      </c>
+      <c r="D83">
+        <v>46.87264226536791</v>
+      </c>
+      <c r="E83">
+        <v>143.451</v>
+      </c>
+      <c r="F83">
+        <v>143.451</v>
+      </c>
+      <c r="G83">
+        <v>19.3</v>
+      </c>
+      <c r="H83">
+        <v>177.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>25.8</v>
+      </c>
+      <c r="K83">
+        <v>12.7</v>
+      </c>
+      <c r="L83">
+        <v>13.1</v>
+      </c>
+      <c r="M83">
+        <v>34.2560988</v>
+      </c>
+      <c r="N83">
+        <v>-21.1560988</v>
+      </c>
+      <c r="O83">
+        <v>-4.019658772000001</v>
+      </c>
+      <c r="P83">
+        <v>-17.136440028</v>
+      </c>
+      <c r="Q83">
+        <v>-4.436440028000003</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3237362485533596</v>
+      </c>
+      <c r="T83">
+        <v>4.484853720119728</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07265859473758875</v>
+      </c>
+      <c r="W83">
+        <v>0.2214491275766638</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3824136565136249</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.242883680562236</v>
+      </c>
+      <c r="C84">
+        <v>-79.50082741824342</v>
+      </c>
+      <c r="D84">
+        <v>46.42117258175659</v>
+      </c>
+      <c r="E84">
+        <v>145.222</v>
+      </c>
+      <c r="F84">
+        <v>145.222</v>
+      </c>
+      <c r="G84">
+        <v>19.3</v>
+      </c>
+      <c r="H84">
+        <v>177.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>25.8</v>
+      </c>
+      <c r="K84">
+        <v>12.7</v>
+      </c>
+      <c r="L84">
+        <v>13.1</v>
+      </c>
+      <c r="M84">
+        <v>34.6790136</v>
+      </c>
+      <c r="N84">
+        <v>-21.5790136</v>
+      </c>
+      <c r="O84">
+        <v>-4.100012584000001</v>
+      </c>
+      <c r="P84">
+        <v>-17.479001016</v>
+      </c>
+      <c r="Q84">
+        <v>-4.779001016000002</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3395660401396575</v>
+      </c>
+      <c r="T84">
+        <v>4.734012260126381</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0717725143139596</v>
+      </c>
+      <c r="W84">
+        <v>0.2216607235818265</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3777500753366295</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.244883680562236</v>
+      </c>
+      <c r="C85">
+        <v>-81.71468310502198</v>
+      </c>
+      <c r="D85">
+        <v>45.97831689497801</v>
+      </c>
+      <c r="E85">
+        <v>146.993</v>
+      </c>
+      <c r="F85">
+        <v>146.993</v>
+      </c>
+      <c r="G85">
+        <v>19.3</v>
+      </c>
+      <c r="H85">
+        <v>177.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>25.8</v>
+      </c>
+      <c r="K85">
+        <v>12.7</v>
+      </c>
+      <c r="L85">
+        <v>13.1</v>
+      </c>
+      <c r="M85">
+        <v>35.1019284</v>
+      </c>
+      <c r="N85">
+        <v>-22.0019284</v>
+      </c>
+      <c r="O85">
+        <v>-4.180366395999999</v>
+      </c>
+      <c r="P85">
+        <v>-17.821562004</v>
+      </c>
+      <c r="Q85">
+        <v>-5.121562003999998</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3572581601478726</v>
+      </c>
+      <c r="T85">
+        <v>5.01248356954558</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07090778522583963</v>
+      </c>
+      <c r="W85">
+        <v>0.2218672208880695</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3731988696096823</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.246883680562236</v>
+      </c>
+      <c r="C86">
+        <v>-83.92016899660544</v>
+      </c>
+      <c r="D86">
+        <v>45.54383100339454</v>
+      </c>
+      <c r="E86">
+        <v>148.764</v>
+      </c>
+      <c r="F86">
+        <v>148.764</v>
+      </c>
+      <c r="G86">
+        <v>19.3</v>
+      </c>
+      <c r="H86">
+        <v>177.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>25.8</v>
+      </c>
+      <c r="K86">
+        <v>12.7</v>
+      </c>
+      <c r="L86">
+        <v>13.1</v>
+      </c>
+      <c r="M86">
+        <v>35.5248432</v>
+      </c>
+      <c r="N86">
+        <v>-22.4248432</v>
+      </c>
+      <c r="O86">
+        <v>-4.260720208</v>
+      </c>
+      <c r="P86">
+        <v>-18.164122992</v>
+      </c>
+      <c r="Q86">
+        <v>-5.464122992</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3771617951571145</v>
+      </c>
+      <c r="T86">
+        <v>5.325763792642176</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07006364492553202</v>
+      </c>
+      <c r="W86">
+        <v>0.2220688015917829</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3687560259238527</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.248883680562236</v>
+      </c>
+      <c r="C87">
+        <v>-86.11752015041614</v>
+      </c>
+      <c r="D87">
+        <v>45.11747984958385</v>
+      </c>
+      <c r="E87">
+        <v>150.535</v>
+      </c>
+      <c r="F87">
+        <v>150.535</v>
+      </c>
+      <c r="G87">
+        <v>19.3</v>
+      </c>
+      <c r="H87">
+        <v>177.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>25.8</v>
+      </c>
+      <c r="K87">
+        <v>12.7</v>
+      </c>
+      <c r="L87">
+        <v>13.1</v>
+      </c>
+      <c r="M87">
+        <v>35.947758</v>
+      </c>
+      <c r="N87">
+        <v>-22.847758</v>
+      </c>
+      <c r="O87">
+        <v>-4.34107402</v>
+      </c>
+      <c r="P87">
+        <v>-18.50668398</v>
+      </c>
+      <c r="Q87">
+        <v>-5.806683979999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3997192481675889</v>
+      </c>
+      <c r="T87">
+        <v>5.680814712151656</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06923936674993751</v>
+      </c>
+      <c r="W87">
+        <v>0.2222656392201149</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3644177197365133</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.250883680562236</v>
+      </c>
+      <c r="C88">
+        <v>-88.3069629037017</v>
+      </c>
+      <c r="D88">
+        <v>44.69903709629828</v>
+      </c>
+      <c r="E88">
+        <v>152.306</v>
+      </c>
+      <c r="F88">
+        <v>152.306</v>
+      </c>
+      <c r="G88">
+        <v>19.3</v>
+      </c>
+      <c r="H88">
+        <v>177.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>25.8</v>
+      </c>
+      <c r="K88">
+        <v>12.7</v>
+      </c>
+      <c r="L88">
+        <v>13.1</v>
+      </c>
+      <c r="M88">
+        <v>36.3706728</v>
+      </c>
+      <c r="N88">
+        <v>-23.2706728</v>
+      </c>
+      <c r="O88">
+        <v>-4.421427832</v>
+      </c>
+      <c r="P88">
+        <v>-18.849244968</v>
+      </c>
+      <c r="Q88">
+        <v>-6.149244968000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4254991944652737</v>
+      </c>
+      <c r="T88">
+        <v>6.086587191591059</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06843425783424056</v>
+      </c>
+      <c r="W88">
+        <v>0.2224578992291834</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3601803043907398</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.252883680562236</v>
+      </c>
+      <c r="C89">
+        <v>-90.48871527419635</v>
+      </c>
+      <c r="D89">
+        <v>44.28828472580365</v>
+      </c>
+      <c r="E89">
+        <v>154.077</v>
+      </c>
+      <c r="F89">
+        <v>154.077</v>
+      </c>
+      <c r="G89">
+        <v>19.3</v>
+      </c>
+      <c r="H89">
+        <v>177.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>25.8</v>
+      </c>
+      <c r="K89">
+        <v>12.7</v>
+      </c>
+      <c r="L89">
+        <v>13.1</v>
+      </c>
+      <c r="M89">
+        <v>36.7935876</v>
+      </c>
+      <c r="N89">
+        <v>-23.6935876</v>
+      </c>
+      <c r="O89">
+        <v>-4.501781644</v>
+      </c>
+      <c r="P89">
+        <v>-19.191805956</v>
+      </c>
+      <c r="Q89">
+        <v>-6.491805956</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4552452863472178</v>
+      </c>
+      <c r="T89">
+        <v>6.554786206328832</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06764765716947918</v>
+      </c>
+      <c r="W89">
+        <v>0.2226457394679284</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3560403008919957</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.254883680562236</v>
+      </c>
+      <c r="C90">
+        <v>-92.66298733889211</v>
+      </c>
+      <c r="D90">
+        <v>43.88501266110788</v>
+      </c>
+      <c r="E90">
+        <v>155.848</v>
+      </c>
+      <c r="F90">
+        <v>155.848</v>
+      </c>
+      <c r="G90">
+        <v>19.3</v>
+      </c>
+      <c r="H90">
+        <v>177.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>25.8</v>
+      </c>
+      <c r="K90">
+        <v>12.7</v>
+      </c>
+      <c r="L90">
+        <v>13.1</v>
+      </c>
+      <c r="M90">
+        <v>37.2165024</v>
+      </c>
+      <c r="N90">
+        <v>-24.11650239999999</v>
+      </c>
+      <c r="O90">
+        <v>-4.582135455999999</v>
+      </c>
+      <c r="P90">
+        <v>-19.53436694399999</v>
+      </c>
+      <c r="Q90">
+        <v>-6.834366943999996</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4899490602094861</v>
+      </c>
+      <c r="T90">
+        <v>7.10101839018957</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06687893379255329</v>
+      </c>
+      <c r="W90">
+        <v>0.2228293106103383</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3519943883818594</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.256883680562236</v>
+      </c>
+      <c r="C91">
+        <v>-94.82998159230347</v>
+      </c>
+      <c r="D91">
+        <v>43.48901840769653</v>
+      </c>
+      <c r="E91">
+        <v>157.619</v>
+      </c>
+      <c r="F91">
+        <v>157.619</v>
+      </c>
+      <c r="G91">
+        <v>19.3</v>
+      </c>
+      <c r="H91">
+        <v>177.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>25.8</v>
+      </c>
+      <c r="K91">
+        <v>12.7</v>
+      </c>
+      <c r="L91">
+        <v>13.1</v>
+      </c>
+      <c r="M91">
+        <v>37.6394172</v>
+      </c>
+      <c r="N91">
+        <v>-24.5394172</v>
+      </c>
+      <c r="O91">
+        <v>-4.662489268000001</v>
+      </c>
+      <c r="P91">
+        <v>-19.876927932</v>
+      </c>
+      <c r="Q91">
+        <v>-7.176927932000002</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5309626111376211</v>
+      </c>
+      <c r="T91">
+        <v>7.74656551657044</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06612748509825492</v>
+      </c>
+      <c r="W91">
+        <v>0.2230087565585367</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3480393952539733</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.258883680562236</v>
+      </c>
+      <c r="C92">
+        <v>-96.98989328550847</v>
+      </c>
+      <c r="D92">
+        <v>43.10010671449152</v>
+      </c>
+      <c r="E92">
+        <v>159.39</v>
+      </c>
+      <c r="F92">
+        <v>159.39</v>
+      </c>
+      <c r="G92">
+        <v>19.3</v>
+      </c>
+      <c r="H92">
+        <v>177.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>25.8</v>
+      </c>
+      <c r="K92">
+        <v>12.7</v>
+      </c>
+      <c r="L92">
+        <v>13.1</v>
+      </c>
+      <c r="M92">
+        <v>38.062332</v>
+      </c>
+      <c r="N92">
+        <v>-24.962332</v>
+      </c>
+      <c r="O92">
+        <v>-4.742843079999999</v>
+      </c>
+      <c r="P92">
+        <v>-20.21948892</v>
+      </c>
+      <c r="Q92">
+        <v>-7.519488919999997</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5801788722513832</v>
+      </c>
+      <c r="T92">
+        <v>8.521222068227484</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06539273526382988</v>
+      </c>
+      <c r="W92">
+        <v>0.2231842148189974</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3441722908622625</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.260883680562236</v>
+      </c>
+      <c r="C93">
+        <v>-99.14291074715955</v>
+      </c>
+      <c r="D93">
+        <v>42.71808925284045</v>
+      </c>
+      <c r="E93">
+        <v>161.161</v>
+      </c>
+      <c r="F93">
+        <v>161.161</v>
+      </c>
+      <c r="G93">
+        <v>19.3</v>
+      </c>
+      <c r="H93">
+        <v>177.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>25.8</v>
+      </c>
+      <c r="K93">
+        <v>12.7</v>
+      </c>
+      <c r="L93">
+        <v>13.1</v>
+      </c>
+      <c r="M93">
+        <v>38.4852468</v>
+      </c>
+      <c r="N93">
+        <v>-25.3852468</v>
+      </c>
+      <c r="O93">
+        <v>-4.823196891999999</v>
+      </c>
+      <c r="P93">
+        <v>-20.562049908</v>
+      </c>
+      <c r="Q93">
+        <v>-7.862049907999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6403320802793149</v>
+      </c>
+      <c r="T93">
+        <v>9.468024520252762</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06467413377741416</v>
+      </c>
+      <c r="W93">
+        <v>0.2233558168539535</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.340390177775864</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.262883680562236</v>
+      </c>
+      <c r="C94">
+        <v>-101.2892156875725</v>
+      </c>
+      <c r="D94">
+        <v>42.34278431242752</v>
+      </c>
+      <c r="E94">
+        <v>162.932</v>
+      </c>
+      <c r="F94">
+        <v>162.932</v>
+      </c>
+      <c r="G94">
+        <v>19.3</v>
+      </c>
+      <c r="H94">
+        <v>177.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>25.8</v>
+      </c>
+      <c r="K94">
+        <v>12.7</v>
+      </c>
+      <c r="L94">
+        <v>13.1</v>
+      </c>
+      <c r="M94">
+        <v>38.9081616</v>
+      </c>
+      <c r="N94">
+        <v>-25.8081616</v>
+      </c>
+      <c r="O94">
+        <v>-4.903550704</v>
+      </c>
+      <c r="P94">
+        <v>-20.904610896</v>
+      </c>
+      <c r="Q94">
+        <v>-8.204610895999998</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7155235903142294</v>
+      </c>
+      <c r="T94">
+        <v>10.65152758528436</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06397115406244226</v>
+      </c>
+      <c r="W94">
+        <v>0.2235236884098888</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3366902845391698</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.264883680562236</v>
+      </c>
+      <c r="C95">
+        <v>-103.4289834869253</v>
+      </c>
+      <c r="D95">
+        <v>41.97401651307465</v>
+      </c>
+      <c r="E95">
+        <v>164.703</v>
+      </c>
+      <c r="F95">
+        <v>164.703</v>
+      </c>
+      <c r="G95">
+        <v>19.3</v>
+      </c>
+      <c r="H95">
+        <v>177.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>25.8</v>
+      </c>
+      <c r="K95">
+        <v>12.7</v>
+      </c>
+      <c r="L95">
+        <v>13.1</v>
+      </c>
+      <c r="M95">
+        <v>39.3310764</v>
+      </c>
+      <c r="N95">
+        <v>-26.2310764</v>
+      </c>
+      <c r="O95">
+        <v>-4.983904516</v>
+      </c>
+      <c r="P95">
+        <v>-21.247171884</v>
+      </c>
+      <c r="Q95">
+        <v>-8.547171884000001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.812198388930548</v>
+      </c>
+      <c r="T95">
+        <v>12.17317438318213</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0632832921908031</v>
+      </c>
+      <c r="W95">
+        <v>0.2236879498248362</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3330699588989637</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.266883680562236</v>
+      </c>
+      <c r="C96">
+        <v>-105.562383468528</v>
+      </c>
+      <c r="D96">
+        <v>41.61161653147204</v>
+      </c>
+      <c r="E96">
+        <v>166.474</v>
+      </c>
+      <c r="F96">
+        <v>166.474</v>
+      </c>
+      <c r="G96">
+        <v>19.3</v>
+      </c>
+      <c r="H96">
+        <v>177.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>25.8</v>
+      </c>
+      <c r="K96">
+        <v>12.7</v>
+      </c>
+      <c r="L96">
+        <v>13.1</v>
+      </c>
+      <c r="M96">
+        <v>39.75399120000001</v>
+      </c>
+      <c r="N96">
+        <v>-26.65399120000001</v>
+      </c>
+      <c r="O96">
+        <v>-5.064258328000001</v>
+      </c>
+      <c r="P96">
+        <v>-21.58973287200001</v>
+      </c>
+      <c r="Q96">
+        <v>-8.889732872000007</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9410981204189728</v>
+      </c>
+      <c r="T96">
+        <v>14.20203678037915</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06261006567813497</v>
+      </c>
+      <c r="W96">
+        <v>0.2238487163160614</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3295266614638683</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.268883680562236</v>
+      </c>
+      <c r="C97">
+        <v>-107.6895791580558</v>
+      </c>
+      <c r="D97">
+        <v>41.25542084194418</v>
+      </c>
+      <c r="E97">
+        <v>168.245</v>
+      </c>
+      <c r="F97">
+        <v>168.245</v>
+      </c>
+      <c r="G97">
+        <v>19.3</v>
+      </c>
+      <c r="H97">
+        <v>177.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>25.8</v>
+      </c>
+      <c r="K97">
+        <v>12.7</v>
+      </c>
+      <c r="L97">
+        <v>13.1</v>
+      </c>
+      <c r="M97">
+        <v>40.176906</v>
+      </c>
+      <c r="N97">
+        <v>-27.076906</v>
+      </c>
+      <c r="O97">
+        <v>-5.14461214</v>
+      </c>
+      <c r="P97">
+        <v>-21.93229386</v>
+      </c>
+      <c r="Q97">
+        <v>-9.232293860000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.121557744502768</v>
+      </c>
+      <c r="T97">
+        <v>17.04244413645499</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.06195101235520725</v>
+      </c>
+      <c r="W97">
+        <v>0.2240060982495765</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3260579597642487</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.270883680562236</v>
+      </c>
+      <c r="C98">
+        <v>-109.8107285295831</v>
+      </c>
+      <c r="D98">
+        <v>40.90527147041688</v>
+      </c>
+      <c r="E98">
+        <v>170.016</v>
+      </c>
+      <c r="F98">
+        <v>170.016</v>
+      </c>
+      <c r="G98">
+        <v>19.3</v>
+      </c>
+      <c r="H98">
+        <v>177.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>25.8</v>
+      </c>
+      <c r="K98">
+        <v>12.7</v>
+      </c>
+      <c r="L98">
+        <v>13.1</v>
+      </c>
+      <c r="M98">
+        <v>40.5998208</v>
+      </c>
+      <c r="N98">
+        <v>-27.4998208</v>
+      </c>
+      <c r="O98">
+        <v>-5.224965952000001</v>
+      </c>
+      <c r="P98">
+        <v>-22.274854848</v>
+      </c>
+      <c r="Q98">
+        <v>-9.574854848000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.392247180628457</v>
+      </c>
+      <c r="T98">
+        <v>21.30305517056869</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0613056893098405</v>
+      </c>
+      <c r="W98">
+        <v>0.2241602013928101</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3226615226833711</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.272883680562236</v>
+      </c>
+      <c r="C99">
+        <v>-111.9259842391919</v>
+      </c>
+      <c r="D99">
+        <v>40.56101576080803</v>
+      </c>
+      <c r="E99">
+        <v>171.787</v>
+      </c>
+      <c r="F99">
+        <v>171.787</v>
+      </c>
+      <c r="G99">
+        <v>19.3</v>
+      </c>
+      <c r="H99">
+        <v>177.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>25.8</v>
+      </c>
+      <c r="K99">
+        <v>12.7</v>
+      </c>
+      <c r="L99">
+        <v>13.1</v>
+      </c>
+      <c r="M99">
+        <v>41.0227356</v>
+      </c>
+      <c r="N99">
+        <v>-27.9227356</v>
+      </c>
+      <c r="O99">
+        <v>-5.305319763999999</v>
+      </c>
+      <c r="P99">
+        <v>-22.617415836</v>
+      </c>
+      <c r="Q99">
+        <v>-9.917415835999996</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.843396240837943</v>
+      </c>
+      <c r="T99">
+        <v>28.40407356075825</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06067367189427515</v>
+      </c>
+      <c r="W99">
+        <v>0.2243111271516471</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.319335115233027</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.274883680562236</v>
+      </c>
+      <c r="C100">
+        <v>-114.035493846884</v>
+      </c>
+      <c r="D100">
+        <v>40.22250615311599</v>
+      </c>
+      <c r="E100">
+        <v>173.558</v>
+      </c>
+      <c r="F100">
+        <v>173.558</v>
+      </c>
+      <c r="G100">
+        <v>19.3</v>
+      </c>
+      <c r="H100">
+        <v>177.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>25.8</v>
+      </c>
+      <c r="K100">
+        <v>12.7</v>
+      </c>
+      <c r="L100">
+        <v>13.1</v>
+      </c>
+      <c r="M100">
+        <v>41.4456504</v>
+      </c>
+      <c r="N100">
+        <v>-28.3456504</v>
+      </c>
+      <c r="O100">
+        <v>-5.385673575999999</v>
+      </c>
+      <c r="P100">
+        <v>-22.959976824</v>
+      </c>
+      <c r="Q100">
+        <v>-10.259976824</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.745694361256914</v>
+      </c>
+      <c r="T100">
+        <v>42.60611034113738</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06005455279331315</v>
+      </c>
+      <c r="W100">
+        <v>0.2244589727929568</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3160765936490166</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2768836805622361</v>
+      </c>
+      <c r="C101">
+        <v>-116.1394000274718</v>
+      </c>
+      <c r="D101">
+        <v>39.88959997252814</v>
+      </c>
+      <c r="E101">
+        <v>175.329</v>
+      </c>
+      <c r="F101">
+        <v>175.329</v>
+      </c>
+      <c r="G101">
+        <v>19.3</v>
+      </c>
+      <c r="H101">
+        <v>177.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>25.8</v>
+      </c>
+      <c r="K101">
+        <v>12.7</v>
+      </c>
+      <c r="L101">
+        <v>13.1</v>
+      </c>
+      <c r="M101">
+        <v>41.8685652</v>
+      </c>
+      <c r="N101">
+        <v>-28.7685652</v>
+      </c>
+      <c r="O101">
+        <v>-5.466027388</v>
+      </c>
+      <c r="P101">
+        <v>-23.302537812</v>
+      </c>
+      <c r="Q101">
+        <v>-10.602537812</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.452588722513828</v>
+      </c>
+      <c r="T101">
+        <v>85.21222068227476</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05944794114893626</v>
+      </c>
+      <c r="W101">
+        <v>0.224603831653634</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.312883900783875</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/slovenia/slovenia_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_chemical_basic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.099497004583035</v>
+        <v>0.09934441027432724</v>
       </c>
       <c r="C2">
-        <v>223.2</v>
+        <v>221.4780643486775</v>
       </c>
       <c r="D2">
-        <v>212.5</v>
+        <v>213.0100643486775</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2.232</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.232</v>
       </c>
       <c r="G2">
         <v>10.7</v>
@@ -1451,28 +1451,28 @@
         <v>25.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1122696</v>
       </c>
       <c r="N2">
-        <v>25.4</v>
+        <v>25.2877304</v>
       </c>
       <c r="O2">
-        <v>4.826</v>
+        <v>4.804668776</v>
       </c>
       <c r="P2">
-        <v>20.574</v>
+        <v>20.483061624</v>
       </c>
       <c r="Q2">
-        <v>34.574</v>
+        <v>34.483061624</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.099497004583035</v>
+        <v>0.09993634371144165</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9128165284161083</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>226.2411195906996</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09934441027432724</v>
+        <v>0.09919181596561946</v>
       </c>
       <c r="C3">
-        <v>221.4780643486775</v>
+        <v>219.7585832067071</v>
       </c>
       <c r="D3">
-        <v>213.0100643486775</v>
+        <v>213.5225832067071</v>
       </c>
       <c r="E3">
-        <v>2.232</v>
+        <v>4.464</v>
       </c>
       <c r="F3">
-        <v>2.232</v>
+        <v>4.464</v>
       </c>
       <c r="G3">
         <v>10.7</v>
@@ -1533,28 +1533,28 @@
         <v>25.4</v>
       </c>
       <c r="M3">
-        <v>0.1122696</v>
+        <v>0.2245392</v>
       </c>
       <c r="N3">
-        <v>25.2877304</v>
+        <v>25.1754608</v>
       </c>
       <c r="O3">
-        <v>4.804668776</v>
+        <v>4.783337552</v>
       </c>
       <c r="P3">
-        <v>20.483061624</v>
+        <v>20.392123248</v>
       </c>
       <c r="Q3">
-        <v>34.483061624</v>
+        <v>34.392123248</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09993634371144165</v>
+        <v>0.1003846489445097</v>
       </c>
       <c r="T3">
-        <v>0.9128165284161083</v>
+        <v>0.9203755986906201</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>226.2411195906996</v>
+        <v>113.1205597953498</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09919181596561946</v>
+        <v>0.09903922165691169</v>
       </c>
       <c r="C4">
-        <v>219.7585832067071</v>
+        <v>218.0415743340444</v>
       </c>
       <c r="D4">
-        <v>213.5225832067071</v>
+        <v>214.0375743340444</v>
       </c>
       <c r="E4">
-        <v>4.464</v>
+        <v>6.696</v>
       </c>
       <c r="F4">
-        <v>4.464</v>
+        <v>6.696</v>
       </c>
       <c r="G4">
         <v>10.7</v>
@@ -1615,28 +1615,28 @@
         <v>25.4</v>
       </c>
       <c r="M4">
-        <v>0.2245392</v>
+        <v>0.3368088</v>
       </c>
       <c r="N4">
-        <v>25.1754608</v>
+        <v>25.0631912</v>
       </c>
       <c r="O4">
-        <v>4.783337552</v>
+        <v>4.762006328</v>
       </c>
       <c r="P4">
-        <v>20.392123248</v>
+        <v>20.301184872</v>
       </c>
       <c r="Q4">
-        <v>34.392123248</v>
+        <v>34.301184872</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1003846489445097</v>
+        <v>0.100842197584445</v>
       </c>
       <c r="T4">
-        <v>0.9203755986906201</v>
+        <v>0.9280905260841941</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>113.1205597953498</v>
+        <v>75.41370653023318</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09903922165691169</v>
+        <v>0.09888662734820393</v>
       </c>
       <c r="C5">
-        <v>218.0415743340444</v>
+        <v>216.3270556623987</v>
       </c>
       <c r="D5">
-        <v>214.0375743340444</v>
+        <v>214.5550556623988</v>
       </c>
       <c r="E5">
-        <v>6.696</v>
+        <v>8.927999999999999</v>
       </c>
       <c r="F5">
-        <v>6.696</v>
+        <v>8.927999999999999</v>
       </c>
       <c r="G5">
         <v>10.7</v>
@@ -1697,28 +1697,28 @@
         <v>25.4</v>
       </c>
       <c r="M5">
-        <v>0.3368088</v>
+        <v>0.4490783999999999</v>
       </c>
       <c r="N5">
-        <v>25.0631912</v>
+        <v>24.9509216</v>
       </c>
       <c r="O5">
-        <v>4.762006328</v>
+        <v>4.740675103999999</v>
       </c>
       <c r="P5">
-        <v>20.301184872</v>
+        <v>20.210246496</v>
       </c>
       <c r="Q5">
-        <v>34.301184872</v>
+        <v>34.210246496</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.100842197584445</v>
+        <v>0.1013092784877124</v>
       </c>
       <c r="T5">
-        <v>0.9280905260841941</v>
+        <v>0.9359661811318007</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.41370653023318</v>
+        <v>56.56027989767488</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09888662734820393</v>
+        <v>0.09873403303949616</v>
       </c>
       <c r="C6">
-        <v>216.3270556623987</v>
+        <v>214.6150452973151</v>
       </c>
       <c r="D6">
-        <v>214.5550556623988</v>
+        <v>215.0750452973151</v>
       </c>
       <c r="E6">
-        <v>8.927999999999999</v>
+        <v>11.16</v>
       </c>
       <c r="F6">
-        <v>8.927999999999999</v>
+        <v>11.16</v>
       </c>
       <c r="G6">
         <v>10.7</v>
@@ -1779,28 +1779,28 @@
         <v>25.4</v>
       </c>
       <c r="M6">
-        <v>0.4490783999999999</v>
+        <v>0.561348</v>
       </c>
       <c r="N6">
-        <v>24.9509216</v>
+        <v>24.838652</v>
       </c>
       <c r="O6">
-        <v>4.740675103999999</v>
+        <v>4.71934388</v>
       </c>
       <c r="P6">
-        <v>20.210246496</v>
+        <v>20.11930812</v>
       </c>
       <c r="Q6">
-        <v>34.210246496</v>
+        <v>34.11930812</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1013092784877124</v>
+        <v>0.1017861926731538</v>
       </c>
       <c r="T6">
-        <v>0.9359661811318007</v>
+        <v>0.9440076394435676</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.56027989767488</v>
+        <v>45.24822391813991</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09873403303949616</v>
+        <v>0.0985814387307884</v>
       </c>
       <c r="C7">
-        <v>214.6150452973151</v>
+        <v>212.9055615202849</v>
       </c>
       <c r="D7">
-        <v>215.0750452973151</v>
+        <v>215.5975615202849</v>
       </c>
       <c r="E7">
-        <v>11.16</v>
+        <v>13.392</v>
       </c>
       <c r="F7">
-        <v>11.16</v>
+        <v>13.392</v>
       </c>
       <c r="G7">
         <v>10.7</v>
@@ -1861,28 +1861,28 @@
         <v>25.4</v>
       </c>
       <c r="M7">
-        <v>0.561348</v>
+        <v>0.6736176</v>
       </c>
       <c r="N7">
-        <v>24.838652</v>
+        <v>24.7263824</v>
       </c>
       <c r="O7">
-        <v>4.71934388</v>
+        <v>4.698012656</v>
       </c>
       <c r="P7">
-        <v>20.11930812</v>
+        <v>20.028369744</v>
       </c>
       <c r="Q7">
-        <v>34.11930812</v>
+        <v>34.028369744</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1017861926731538</v>
+        <v>0.1022732539689238</v>
       </c>
       <c r="T7">
-        <v>0.9440076394435676</v>
+        <v>0.9522201926130317</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.24822391813991</v>
+        <v>37.70685326511659</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0985814387307884</v>
+        <v>0.09842884442208064</v>
       </c>
       <c r="C8">
-        <v>212.9055615202849</v>
+        <v>211.1986227908889</v>
       </c>
       <c r="D8">
-        <v>215.5975615202849</v>
+        <v>216.1226227908889</v>
       </c>
       <c r="E8">
-        <v>13.392</v>
+        <v>15.624</v>
       </c>
       <c r="F8">
-        <v>13.392</v>
+        <v>15.624</v>
       </c>
       <c r="G8">
         <v>10.7</v>
@@ -1943,28 +1943,28 @@
         <v>25.4</v>
       </c>
       <c r="M8">
-        <v>0.6736175999999999</v>
+        <v>0.7858871999999998</v>
       </c>
       <c r="N8">
-        <v>24.7263824</v>
+        <v>24.6141128</v>
       </c>
       <c r="O8">
-        <v>4.698012656</v>
+        <v>4.676681432</v>
       </c>
       <c r="P8">
-        <v>20.028369744</v>
+        <v>19.937431368</v>
       </c>
       <c r="Q8">
-        <v>34.028369744</v>
+        <v>33.937431368</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1022732539689238</v>
+        <v>0.102770789701162</v>
       </c>
       <c r="T8">
-        <v>0.9522201926130317</v>
+        <v>0.960609359829151</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.70685326511659</v>
+        <v>32.32015994152851</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09842884442208062</v>
+        <v>0.09827625011337288</v>
       </c>
       <c r="C9">
-        <v>211.1986227908889</v>
+        <v>209.494247748971</v>
       </c>
       <c r="D9">
-        <v>216.122622790889</v>
+        <v>216.650247748971</v>
       </c>
       <c r="E9">
-        <v>15.624</v>
+        <v>17.856</v>
       </c>
       <c r="F9">
-        <v>15.624</v>
+        <v>17.856</v>
       </c>
       <c r="G9">
         <v>10.7</v>
@@ -2025,28 +2025,28 @@
         <v>25.4</v>
       </c>
       <c r="M9">
-        <v>0.7858872</v>
+        <v>0.8981567999999999</v>
       </c>
       <c r="N9">
-        <v>24.6141128</v>
+        <v>24.5018432</v>
       </c>
       <c r="O9">
-        <v>4.676681432</v>
+        <v>4.655350208</v>
       </c>
       <c r="P9">
-        <v>19.937431368</v>
+        <v>19.846492992</v>
       </c>
       <c r="Q9">
-        <v>33.937431368</v>
+        <v>33.846492992</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.102770789701162</v>
+        <v>0.1032791414275792</v>
       </c>
       <c r="T9">
-        <v>0.960609359829151</v>
+        <v>0.9691809002456206</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.3201599415285</v>
+        <v>28.28013994883744</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09827625011337288</v>
+        <v>0.0981236558046651</v>
       </c>
       <c r="C10">
-        <v>209.494247748971</v>
+        <v>207.7924552168441</v>
       </c>
       <c r="D10">
-        <v>216.650247748971</v>
+        <v>217.1804552168441</v>
       </c>
       <c r="E10">
-        <v>17.856</v>
+        <v>20.088</v>
       </c>
       <c r="F10">
-        <v>17.856</v>
+        <v>20.088</v>
       </c>
       <c r="G10">
         <v>10.7</v>
@@ -2107,28 +2107,28 @@
         <v>25.4</v>
       </c>
       <c r="M10">
-        <v>0.8981567999999999</v>
+        <v>1.0104264</v>
       </c>
       <c r="N10">
-        <v>24.5018432</v>
+        <v>24.3895736</v>
       </c>
       <c r="O10">
-        <v>4.655350208</v>
+        <v>4.634018984</v>
       </c>
       <c r="P10">
-        <v>19.846492992</v>
+        <v>19.755554616</v>
       </c>
       <c r="Q10">
-        <v>33.846492992</v>
+        <v>33.755554616</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1032791414275792</v>
+        <v>0.1037986657194122</v>
       </c>
       <c r="T10">
-        <v>0.9691809002456206</v>
+        <v>0.9779408261657487</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.28013994883744</v>
+        <v>25.13790217674439</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0981236558046651</v>
+        <v>0.09797106149595734</v>
       </c>
       <c r="C11">
-        <v>207.7924552168441</v>
+        <v>206.0932642015281</v>
       </c>
       <c r="D11">
-        <v>217.1804552168441</v>
+        <v>217.7132642015281</v>
       </c>
       <c r="E11">
-        <v>20.088</v>
+        <v>22.32</v>
       </c>
       <c r="F11">
-        <v>20.088</v>
+        <v>22.32</v>
       </c>
       <c r="G11">
         <v>10.7</v>
@@ -2189,28 +2189,28 @@
         <v>25.4</v>
       </c>
       <c r="M11">
-        <v>1.0104264</v>
+        <v>1.122696</v>
       </c>
       <c r="N11">
-        <v>24.3895736</v>
+        <v>24.277304</v>
       </c>
       <c r="O11">
-        <v>4.634018984</v>
+        <v>4.612687759999999</v>
       </c>
       <c r="P11">
-        <v>19.755554616</v>
+        <v>19.66461624</v>
       </c>
       <c r="Q11">
-        <v>33.755554616</v>
+        <v>33.66461624</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1037986657194122</v>
+        <v>0.1043297349955082</v>
       </c>
       <c r="T11">
-        <v>0.9779408261657487</v>
+        <v>0.9868954171063244</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.13790217674439</v>
+        <v>22.62411195906996</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09797106149595734</v>
+        <v>0.09781846718724958</v>
       </c>
       <c r="C12">
-        <v>206.0932642015281</v>
+        <v>204.3966938970215</v>
       </c>
       <c r="D12">
-        <v>217.7132642015281</v>
+        <v>218.2486938970216</v>
       </c>
       <c r="E12">
-        <v>22.32</v>
+        <v>24.552</v>
       </c>
       <c r="F12">
-        <v>22.32</v>
+        <v>24.552</v>
       </c>
       <c r="G12">
         <v>10.7</v>
@@ -2271,28 +2271,28 @@
         <v>25.4</v>
       </c>
       <c r="M12">
-        <v>1.122696</v>
+        <v>1.2349656</v>
       </c>
       <c r="N12">
-        <v>24.277304</v>
+        <v>24.1650344</v>
       </c>
       <c r="O12">
-        <v>4.612687759999999</v>
+        <v>4.591356536</v>
       </c>
       <c r="P12">
-        <v>19.66461624</v>
+        <v>19.573677864</v>
       </c>
       <c r="Q12">
-        <v>33.66461624</v>
+        <v>33.573677864</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1043297349955082</v>
+        <v>0.10487273841264</v>
       </c>
       <c r="T12">
-        <v>0.9868954171063244</v>
+        <v>0.9960512348096096</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.62411195906995</v>
+        <v>20.56737450824541</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09781846718724958</v>
+        <v>0.0976658728785418</v>
       </c>
       <c r="C13">
-        <v>204.3966938970215</v>
+        <v>202.7027636866064</v>
       </c>
       <c r="D13">
-        <v>218.2486938970216</v>
+        <v>218.7867636866064</v>
       </c>
       <c r="E13">
-        <v>24.552</v>
+        <v>26.784</v>
       </c>
       <c r="F13">
-        <v>24.552</v>
+        <v>26.784</v>
       </c>
       <c r="G13">
         <v>10.7</v>
@@ -2353,28 +2353,28 @@
         <v>25.4</v>
       </c>
       <c r="M13">
-        <v>1.2349656</v>
+        <v>1.3472352</v>
       </c>
       <c r="N13">
-        <v>24.1650344</v>
+        <v>24.0527648</v>
       </c>
       <c r="O13">
-        <v>4.591356536</v>
+        <v>4.570025311999999</v>
       </c>
       <c r="P13">
-        <v>19.573677864</v>
+        <v>19.482739488</v>
       </c>
       <c r="Q13">
-        <v>33.573677864</v>
+        <v>33.482739488</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.10487273841264</v>
+        <v>0.1054280828165248</v>
       </c>
       <c r="T13">
-        <v>0.9960512348096096</v>
+        <v>1.005415139278878</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.56737450824541</v>
+        <v>18.8534266325583</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0976658728785418</v>
+        <v>0.09751327856983404</v>
       </c>
       <c r="C14">
-        <v>202.7027636866064</v>
+        <v>201.0114931451866</v>
       </c>
       <c r="D14">
-        <v>218.7867636866064</v>
+        <v>219.3274931451866</v>
       </c>
       <c r="E14">
-        <v>26.784</v>
+        <v>29.016</v>
       </c>
       <c r="F14">
-        <v>26.784</v>
+        <v>29.016</v>
       </c>
       <c r="G14">
         <v>10.7</v>
@@ -2435,28 +2435,28 @@
         <v>25.4</v>
       </c>
       <c r="M14">
-        <v>1.3472352</v>
+        <v>1.4595048</v>
       </c>
       <c r="N14">
-        <v>24.0527648</v>
+        <v>23.9404952</v>
       </c>
       <c r="O14">
-        <v>4.570025311999999</v>
+        <v>4.548694088</v>
       </c>
       <c r="P14">
-        <v>19.482739488</v>
+        <v>19.391801112</v>
       </c>
       <c r="Q14">
-        <v>33.482739488</v>
+        <v>33.391801112</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1054280828165248</v>
+        <v>0.1059961937584299</v>
       </c>
       <c r="T14">
-        <v>1.005415139278878</v>
+        <v>1.014994305919855</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.8534266325583</v>
+        <v>17.40316304543843</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09751327856983404</v>
+        <v>0.09736068426112626</v>
       </c>
       <c r="C15">
-        <v>201.0114931451866</v>
+        <v>199.3229020416627</v>
       </c>
       <c r="D15">
-        <v>219.3274931451866</v>
+        <v>219.8709020416627</v>
       </c>
       <c r="E15">
-        <v>29.016</v>
+        <v>31.248</v>
       </c>
       <c r="F15">
-        <v>29.016</v>
+        <v>31.248</v>
       </c>
       <c r="G15">
         <v>10.7</v>
@@ -2517,28 +2517,28 @@
         <v>25.4</v>
       </c>
       <c r="M15">
-        <v>1.4595048</v>
+        <v>1.5717744</v>
       </c>
       <c r="N15">
-        <v>23.9404952</v>
+        <v>23.8282256</v>
       </c>
       <c r="O15">
-        <v>4.548694088</v>
+        <v>4.527362864</v>
       </c>
       <c r="P15">
-        <v>19.391801112</v>
+        <v>19.300862736</v>
       </c>
       <c r="Q15">
-        <v>33.391801112</v>
+        <v>33.300862736</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1059961937584299</v>
+        <v>0.106577516582705</v>
       </c>
       <c r="T15">
-        <v>1.014994305919855</v>
+        <v>1.024796243878063</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.40316304543843</v>
+        <v>16.16007997076425</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09736068426112626</v>
+        <v>0.0972080899524185</v>
       </c>
       <c r="C16">
-        <v>199.3229020416627</v>
+        <v>197.6370103413408</v>
       </c>
       <c r="D16">
-        <v>219.8709020416627</v>
+        <v>220.4170103413408</v>
       </c>
       <c r="E16">
-        <v>31.248</v>
+        <v>33.48</v>
       </c>
       <c r="F16">
-        <v>31.248</v>
+        <v>33.48</v>
       </c>
       <c r="G16">
         <v>10.7</v>
@@ -2599,28 +2599,28 @@
         <v>25.4</v>
       </c>
       <c r="M16">
-        <v>1.5717744</v>
+        <v>1.684044</v>
       </c>
       <c r="N16">
-        <v>23.8282256</v>
+        <v>23.715956</v>
       </c>
       <c r="O16">
-        <v>4.527362864</v>
+        <v>4.50603164</v>
       </c>
       <c r="P16">
-        <v>19.300862736</v>
+        <v>19.20992436</v>
       </c>
       <c r="Q16">
-        <v>33.300862736</v>
+        <v>33.20992436</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.106577516582705</v>
+        <v>0.1071725175910806</v>
       </c>
       <c r="T16">
-        <v>1.024796243878063</v>
+        <v>1.034828815670582</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.16007997076425</v>
+        <v>15.08274130604663</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0972080899524185</v>
+        <v>0.09705549564371073</v>
       </c>
       <c r="C17">
-        <v>197.6370103413408</v>
+        <v>195.9538382083773</v>
       </c>
       <c r="D17">
-        <v>220.4170103413408</v>
+        <v>220.9658382083773</v>
       </c>
       <c r="E17">
-        <v>33.48</v>
+        <v>35.712</v>
       </c>
       <c r="F17">
-        <v>33.48</v>
+        <v>35.712</v>
       </c>
       <c r="G17">
         <v>10.7</v>
@@ -2681,28 +2681,28 @@
         <v>25.4</v>
       </c>
       <c r="M17">
-        <v>1.684044</v>
+        <v>1.7963136</v>
       </c>
       <c r="N17">
-        <v>23.715956</v>
+        <v>23.6036864</v>
       </c>
       <c r="O17">
-        <v>4.50603164</v>
+        <v>4.484700416</v>
       </c>
       <c r="P17">
-        <v>19.20992436</v>
+        <v>19.118985984</v>
       </c>
       <c r="Q17">
-        <v>33.20992436</v>
+        <v>33.118985984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1071725175910806</v>
+        <v>0.1077816852901318</v>
       </c>
       <c r="T17">
-        <v>1.034828815670582</v>
+        <v>1.045100258220066</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.08274130604664</v>
+        <v>14.14006997441872</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09705549564371073</v>
+        <v>0.09690290133500296</v>
       </c>
       <c r="C18">
-        <v>195.9538382083773</v>
+        <v>194.2734060082612</v>
       </c>
       <c r="D18">
-        <v>220.9658382083773</v>
+        <v>221.5174060082613</v>
       </c>
       <c r="E18">
-        <v>35.712</v>
+        <v>37.944</v>
       </c>
       <c r="F18">
-        <v>35.712</v>
+        <v>37.944</v>
       </c>
       <c r="G18">
         <v>10.7</v>
@@ -2763,28 +2763,28 @@
         <v>25.4</v>
       </c>
       <c r="M18">
-        <v>1.7963136</v>
+        <v>1.9085832</v>
       </c>
       <c r="N18">
-        <v>23.6036864</v>
+        <v>23.4914168</v>
       </c>
       <c r="O18">
-        <v>4.484700416</v>
+        <v>4.463369192</v>
       </c>
       <c r="P18">
-        <v>19.118985984</v>
+        <v>19.028047608</v>
       </c>
       <c r="Q18">
-        <v>33.118985984</v>
+        <v>33.028047608</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1077816852901318</v>
+        <v>0.1084055317289192</v>
       </c>
       <c r="T18">
-        <v>1.045100258220066</v>
+        <v>1.055619205409296</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.14006997441872</v>
+        <v>13.30830115239409</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09690290133500296</v>
+        <v>0.09696900702629521</v>
       </c>
       <c r="C19">
-        <v>194.2734060082612</v>
+        <v>191.8021225033516</v>
       </c>
       <c r="D19">
-        <v>221.5174060082613</v>
+        <v>221.2781225033516</v>
       </c>
       <c r="E19">
-        <v>37.944</v>
+        <v>40.176</v>
       </c>
       <c r="F19">
-        <v>37.944</v>
+        <v>40.176</v>
       </c>
       <c r="G19">
         <v>10.7</v>
@@ -2845,45 +2845,45 @@
         <v>25.4</v>
       </c>
       <c r="M19">
-        <v>1.9085832</v>
+        <v>2.0811168</v>
       </c>
       <c r="N19">
-        <v>23.4914168</v>
+        <v>23.3188832</v>
       </c>
       <c r="O19">
-        <v>4.463369192</v>
+        <v>4.430587807999999</v>
       </c>
       <c r="P19">
-        <v>19.028047608</v>
+        <v>18.888295392</v>
       </c>
       <c r="Q19">
-        <v>33.028047608</v>
+        <v>32.888295392</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1084055317289192</v>
+        <v>0.1090445939345064</v>
       </c>
       <c r="T19">
-        <v>1.055619205409296</v>
+        <v>1.066394712286069</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.30830115239409</v>
+        <v>12.20498532326489</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09696900702629521</v>
+        <v>0.09682856271758743</v>
       </c>
       <c r="C20">
-        <v>191.8021225033516</v>
+        <v>190.0791092784918</v>
       </c>
       <c r="D20">
-        <v>221.2781225033516</v>
+        <v>221.7871092784918</v>
       </c>
       <c r="E20">
-        <v>40.17599999999999</v>
+        <v>42.408</v>
       </c>
       <c r="F20">
-        <v>40.17599999999999</v>
+        <v>42.408</v>
       </c>
       <c r="G20">
         <v>10.7</v>
@@ -2927,28 +2927,28 @@
         <v>25.4</v>
       </c>
       <c r="M20">
-        <v>2.0811168</v>
+        <v>2.1967344</v>
       </c>
       <c r="N20">
-        <v>23.3188832</v>
+        <v>23.2032656</v>
       </c>
       <c r="O20">
-        <v>4.430587807999999</v>
+        <v>4.408620463999999</v>
       </c>
       <c r="P20">
-        <v>18.888295392</v>
+        <v>18.794645136</v>
       </c>
       <c r="Q20">
-        <v>32.888295392</v>
+        <v>32.794645136</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1090445939345064</v>
+        <v>0.1096994354538116</v>
       </c>
       <c r="T20">
-        <v>1.066394712286069</v>
+        <v>1.077436281061033</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.20498532326489</v>
+        <v>11.562617674672</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09682856271758743</v>
+        <v>0.0966881184088797</v>
       </c>
       <c r="C21">
-        <v>190.0791092784918</v>
+        <v>188.3584430079413</v>
       </c>
       <c r="D21">
-        <v>221.7871092784918</v>
+        <v>222.2984430079414</v>
       </c>
       <c r="E21">
-        <v>42.408</v>
+        <v>44.64</v>
       </c>
       <c r="F21">
-        <v>42.408</v>
+        <v>44.64</v>
       </c>
       <c r="G21">
         <v>10.7</v>
@@ -3009,28 +3009,28 @@
         <v>25.4</v>
       </c>
       <c r="M21">
-        <v>2.1967344</v>
+        <v>2.312352</v>
       </c>
       <c r="N21">
-        <v>23.2032656</v>
+        <v>23.087648</v>
       </c>
       <c r="O21">
-        <v>4.408620463999999</v>
+        <v>4.38665312</v>
       </c>
       <c r="P21">
-        <v>18.794645136</v>
+        <v>18.70099488</v>
       </c>
       <c r="Q21">
-        <v>32.794645136</v>
+        <v>32.70099488</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1096994354538116</v>
+        <v>0.1103706480110996</v>
       </c>
       <c r="T21">
-        <v>1.077436281061033</v>
+        <v>1.088753889055372</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.562617674672</v>
+        <v>10.9844867909384</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0966881184088797</v>
+        <v>0.09654767410017191</v>
       </c>
       <c r="C22">
-        <v>188.3584430079413</v>
+        <v>186.6401399620345</v>
       </c>
       <c r="D22">
-        <v>222.2984430079414</v>
+        <v>222.8121399620345</v>
       </c>
       <c r="E22">
-        <v>44.64</v>
+        <v>46.872</v>
       </c>
       <c r="F22">
-        <v>44.64</v>
+        <v>46.872</v>
       </c>
       <c r="G22">
         <v>10.7</v>
@@ -3091,28 +3091,28 @@
         <v>25.4</v>
       </c>
       <c r="M22">
-        <v>2.312352</v>
+        <v>2.4279696</v>
       </c>
       <c r="N22">
-        <v>23.087648</v>
+        <v>22.9720304</v>
       </c>
       <c r="O22">
-        <v>4.38665312</v>
+        <v>4.364685776</v>
       </c>
       <c r="P22">
-        <v>18.70099488</v>
+        <v>18.607344624</v>
       </c>
       <c r="Q22">
-        <v>32.70099488</v>
+        <v>32.607344624</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1103706480110996</v>
+        <v>0.1110588532913568</v>
       </c>
       <c r="T22">
-        <v>1.088753889055372</v>
+        <v>1.100358018771086</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.9844867909384</v>
+        <v>10.46141599136991</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09654767410017191</v>
+        <v>0.09640722979146416</v>
       </c>
       <c r="C23">
-        <v>186.6401399620345</v>
+        <v>184.9242165618456</v>
       </c>
       <c r="D23">
-        <v>222.8121399620345</v>
+        <v>223.3282165618457</v>
       </c>
       <c r="E23">
-        <v>46.87199999999999</v>
+        <v>49.104</v>
       </c>
       <c r="F23">
-        <v>46.87199999999999</v>
+        <v>49.104</v>
       </c>
       <c r="G23">
         <v>10.7</v>
@@ -3173,28 +3173,28 @@
         <v>25.4</v>
       </c>
       <c r="M23">
-        <v>2.4279696</v>
+        <v>2.5435872</v>
       </c>
       <c r="N23">
-        <v>22.9720304</v>
+        <v>22.8564128</v>
       </c>
       <c r="O23">
-        <v>4.364685776</v>
+        <v>4.342718432</v>
       </c>
       <c r="P23">
-        <v>18.607344624</v>
+        <v>18.513694368</v>
       </c>
       <c r="Q23">
-        <v>32.607344624</v>
+        <v>32.513694368</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1110588532913568</v>
+        <v>0.1117647048608515</v>
       </c>
       <c r="T23">
-        <v>1.100358018771086</v>
+        <v>1.112259690274383</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.46141599136991</v>
+        <v>9.985897082671276</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09640722979146416</v>
+        <v>0.09658349548275637</v>
       </c>
       <c r="C24">
-        <v>184.9242165618456</v>
+        <v>182.0448922558684</v>
       </c>
       <c r="D24">
-        <v>223.3282165618457</v>
+        <v>222.6808922558684</v>
       </c>
       <c r="E24">
-        <v>49.104</v>
+        <v>51.336</v>
       </c>
       <c r="F24">
-        <v>49.104</v>
+        <v>51.336</v>
       </c>
       <c r="G24">
         <v>10.7</v>
@@ -3255,45 +3255,45 @@
         <v>25.4</v>
       </c>
       <c r="M24">
-        <v>2.5435872</v>
+        <v>2.746476</v>
       </c>
       <c r="N24">
-        <v>22.8564128</v>
+        <v>22.653524</v>
       </c>
       <c r="O24">
-        <v>4.342718432</v>
+        <v>4.304169559999999</v>
       </c>
       <c r="P24">
-        <v>18.513694368</v>
+        <v>18.34935444</v>
       </c>
       <c r="Q24">
-        <v>32.513694368</v>
+        <v>32.34935444</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1117647048608515</v>
+        <v>0.1124888902373459</v>
       </c>
       <c r="T24">
-        <v>1.112259690274383</v>
+        <v>1.12447049610244</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.985897082671276</v>
+        <v>9.248214803260614</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09658349548275637</v>
+        <v>0.09645682117404861</v>
       </c>
       <c r="C25">
-        <v>182.0448922558684</v>
+        <v>180.2777152706057</v>
       </c>
       <c r="D25">
-        <v>222.6808922558684</v>
+        <v>223.1457152706058</v>
       </c>
       <c r="E25">
-        <v>51.336</v>
+        <v>53.568</v>
       </c>
       <c r="F25">
-        <v>51.336</v>
+        <v>53.568</v>
       </c>
       <c r="G25">
         <v>10.7</v>
@@ -3337,28 +3337,28 @@
         <v>25.4</v>
       </c>
       <c r="M25">
-        <v>2.746476</v>
+        <v>2.865888</v>
       </c>
       <c r="N25">
-        <v>22.653524</v>
+        <v>22.534112</v>
       </c>
       <c r="O25">
-        <v>4.304169559999999</v>
+        <v>4.28148128</v>
       </c>
       <c r="P25">
-        <v>18.34935444</v>
+        <v>18.25263072</v>
       </c>
       <c r="Q25">
-        <v>32.34935444</v>
+        <v>32.25263072</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1124888902373459</v>
+        <v>0.1132321331237482</v>
       </c>
       <c r="T25">
-        <v>1.12447049610244</v>
+        <v>1.137002638925973</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.248214803260614</v>
+        <v>8.862872519791424</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09645682117404861</v>
+        <v>0.09633014686534083</v>
       </c>
       <c r="C26">
-        <v>180.2777152706058</v>
+        <v>178.5124828831012</v>
       </c>
       <c r="D26">
-        <v>223.1457152706058</v>
+        <v>223.6124828831012</v>
       </c>
       <c r="E26">
-        <v>53.568</v>
+        <v>55.8</v>
       </c>
       <c r="F26">
-        <v>53.568</v>
+        <v>55.8</v>
       </c>
       <c r="G26">
         <v>10.7</v>
@@ -3419,28 +3419,28 @@
         <v>25.4</v>
       </c>
       <c r="M26">
-        <v>2.865888</v>
+        <v>2.9853</v>
       </c>
       <c r="N26">
-        <v>22.534112</v>
+        <v>22.4147</v>
       </c>
       <c r="O26">
-        <v>4.28148128</v>
+        <v>4.258793</v>
       </c>
       <c r="P26">
-        <v>18.25263072</v>
+        <v>18.155907</v>
       </c>
       <c r="Q26">
-        <v>32.25263072</v>
+        <v>32.155907</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132321331237482</v>
+        <v>0.1139951958204544</v>
       </c>
       <c r="T26">
-        <v>1.137002638925973</v>
+        <v>1.1498689722248</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.862872519791424</v>
+        <v>8.508357618999767</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09633014686534083</v>
+        <v>0.09620347255663307</v>
       </c>
       <c r="C27">
-        <v>178.5124828831012</v>
+        <v>176.7492073218379</v>
       </c>
       <c r="D27">
-        <v>223.6124828831012</v>
+        <v>224.0812073218379</v>
       </c>
       <c r="E27">
-        <v>55.8</v>
+        <v>58.032</v>
       </c>
       <c r="F27">
-        <v>55.8</v>
+        <v>58.032</v>
       </c>
       <c r="G27">
         <v>10.7</v>
@@ -3501,28 +3501,28 @@
         <v>25.4</v>
       </c>
       <c r="M27">
-        <v>2.9853</v>
+        <v>3.104712</v>
       </c>
       <c r="N27">
-        <v>22.4147</v>
+        <v>22.295288</v>
       </c>
       <c r="O27">
-        <v>4.258793</v>
+        <v>4.23610472</v>
       </c>
       <c r="P27">
-        <v>18.155907</v>
+        <v>18.05918328</v>
       </c>
       <c r="Q27">
-        <v>32.155907</v>
+        <v>32.05918328</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1139951958204544</v>
+        <v>0.1147788818332879</v>
       </c>
       <c r="T27">
-        <v>1.1498689722248</v>
+        <v>1.163083044261433</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.508357618999767</v>
+        <v>8.181113095192082</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09620347255663307</v>
+        <v>0.09607679824792528</v>
       </c>
       <c r="C28">
-        <v>176.7492073218379</v>
+        <v>174.9879009180451</v>
       </c>
       <c r="D28">
-        <v>224.0812073218379</v>
+        <v>224.5519009180451</v>
       </c>
       <c r="E28">
-        <v>58.032</v>
+        <v>60.264</v>
       </c>
       <c r="F28">
-        <v>58.032</v>
+        <v>60.264</v>
       </c>
       <c r="G28">
         <v>10.7</v>
@@ -3583,28 +3583,28 @@
         <v>25.4</v>
       </c>
       <c r="M28">
-        <v>3.104712</v>
+        <v>3.224124</v>
       </c>
       <c r="N28">
-        <v>22.295288</v>
+        <v>22.175876</v>
       </c>
       <c r="O28">
-        <v>4.23610472</v>
+        <v>4.21341644</v>
       </c>
       <c r="P28">
-        <v>18.05918328</v>
+        <v>17.96245956</v>
       </c>
       <c r="Q28">
-        <v>32.05918328</v>
+        <v>31.96245956</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1147788818332879</v>
+        <v>0.1155840386957881</v>
       </c>
       <c r="T28">
-        <v>1.163083044261433</v>
+        <v>1.176659145668933</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.181113095192082</v>
+        <v>7.878108906481263</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09607679824792528</v>
+        <v>0.09613156393921753</v>
       </c>
       <c r="C29">
-        <v>174.9879009180451</v>
+        <v>172.552161341249</v>
       </c>
       <c r="D29">
-        <v>224.5519009180451</v>
+        <v>224.3481613412491</v>
       </c>
       <c r="E29">
-        <v>60.264</v>
+        <v>62.496</v>
       </c>
       <c r="F29">
-        <v>60.264</v>
+        <v>62.496</v>
       </c>
       <c r="G29">
         <v>10.7</v>
@@ -3665,45 +3665,45 @@
         <v>25.4</v>
       </c>
       <c r="M29">
-        <v>3.224124</v>
+        <v>3.3935328</v>
       </c>
       <c r="N29">
-        <v>22.175876</v>
+        <v>22.0064672</v>
       </c>
       <c r="O29">
-        <v>4.21341644</v>
+        <v>4.181228768</v>
       </c>
       <c r="P29">
-        <v>17.96245956</v>
+        <v>17.825238432</v>
       </c>
       <c r="Q29">
-        <v>31.96245956</v>
+        <v>31.825238432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1155840386957881</v>
+        <v>0.116411561026691</v>
       </c>
       <c r="T29">
-        <v>1.176659145668933</v>
+        <v>1.190612361004419</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.19</v>
       </c>
       <c r="W29">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.878108906481263</v>
+        <v>7.484825253493939</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09613156393921753</v>
+        <v>0.0960113696305098</v>
       </c>
       <c r="C30">
-        <v>172.552161341249</v>
+        <v>170.7677944237981</v>
       </c>
       <c r="D30">
-        <v>224.3481613412491</v>
+        <v>224.7957944237981</v>
       </c>
       <c r="E30">
-        <v>62.496</v>
+        <v>64.72800000000001</v>
       </c>
       <c r="F30">
-        <v>62.496</v>
+        <v>64.72800000000001</v>
       </c>
       <c r="G30">
         <v>10.7</v>
@@ -3747,28 +3747,28 @@
         <v>25.4</v>
       </c>
       <c r="M30">
-        <v>3.3935328</v>
+        <v>3.5147304</v>
       </c>
       <c r="N30">
-        <v>22.0064672</v>
+        <v>21.8852696</v>
       </c>
       <c r="O30">
-        <v>4.181228768</v>
+        <v>4.158201224</v>
       </c>
       <c r="P30">
-        <v>17.825238432</v>
+        <v>17.727068376</v>
       </c>
       <c r="Q30">
-        <v>31.825238432</v>
+        <v>31.727068376</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.116411561026691</v>
+        <v>0.1172623938457884</v>
       </c>
       <c r="T30">
-        <v>1.190612361004419</v>
+        <v>1.204958624659215</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.484825253493939</v>
+        <v>7.226727830959665</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09601136963050977</v>
+        <v>0.09589117532180198</v>
       </c>
       <c r="C31">
-        <v>170.7677944237982</v>
+        <v>168.9852173670337</v>
       </c>
       <c r="D31">
-        <v>224.7957944237982</v>
+        <v>225.2452173670337</v>
       </c>
       <c r="E31">
-        <v>64.72799999999999</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F31">
-        <v>64.72799999999999</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="G31">
         <v>10.7</v>
@@ -3829,28 +3829,28 @@
         <v>25.4</v>
       </c>
       <c r="M31">
-        <v>3.5147304</v>
+        <v>3.635928</v>
       </c>
       <c r="N31">
-        <v>21.8852696</v>
+        <v>21.764072</v>
       </c>
       <c r="O31">
-        <v>4.158201224</v>
+        <v>4.135173679999999</v>
       </c>
       <c r="P31">
-        <v>17.727068376</v>
+        <v>17.62889832</v>
       </c>
       <c r="Q31">
-        <v>31.727068376</v>
+        <v>31.62889832</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1172623938457884</v>
+        <v>0.1181375361740029</v>
       </c>
       <c r="T31">
-        <v>1.204958624659214</v>
+        <v>1.21971478156129</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.226727830959666</v>
+        <v>6.985836903261011</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09589117532180198</v>
+        <v>0.09577098101309423</v>
       </c>
       <c r="C32">
-        <v>168.9852173670337</v>
+        <v>167.2044409275965</v>
       </c>
       <c r="D32">
-        <v>225.2452173670337</v>
+        <v>225.6964409275965</v>
       </c>
       <c r="E32">
-        <v>66.95999999999999</v>
+        <v>69.19199999999999</v>
       </c>
       <c r="F32">
-        <v>66.95999999999999</v>
+        <v>69.19199999999999</v>
       </c>
       <c r="G32">
         <v>10.7</v>
@@ -3911,28 +3911,28 @@
         <v>25.4</v>
       </c>
       <c r="M32">
-        <v>3.635928</v>
+        <v>3.7571256</v>
       </c>
       <c r="N32">
-        <v>21.764072</v>
+        <v>21.6428744</v>
       </c>
       <c r="O32">
-        <v>4.135173679999999</v>
+        <v>4.112146136</v>
       </c>
       <c r="P32">
-        <v>17.62889832</v>
+        <v>17.530728264</v>
       </c>
       <c r="Q32">
-        <v>31.62889832</v>
+        <v>31.530728264</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1181375361740029</v>
+        <v>0.1190380449465134</v>
       </c>
       <c r="T32">
-        <v>1.21971478156129</v>
+        <v>1.234898653156179</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.985836903261011</v>
+        <v>6.760487325736462</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09577098101309423</v>
+        <v>0.09565078670438648</v>
       </c>
       <c r="C33">
-        <v>167.2044409275965</v>
+        <v>165.4254759484938</v>
       </c>
       <c r="D33">
-        <v>225.6964409275965</v>
+        <v>226.1494759484938</v>
       </c>
       <c r="E33">
-        <v>69.19199999999999</v>
+        <v>71.42399999999999</v>
       </c>
       <c r="F33">
-        <v>69.19199999999999</v>
+        <v>71.42399999999999</v>
       </c>
       <c r="G33">
         <v>10.7</v>
@@ -3993,28 +3993,28 @@
         <v>25.4</v>
       </c>
       <c r="M33">
-        <v>3.7571256</v>
+        <v>3.8783232</v>
       </c>
       <c r="N33">
-        <v>21.6428744</v>
+        <v>21.5216768</v>
       </c>
       <c r="O33">
-        <v>4.112146136</v>
+        <v>4.089118591999999</v>
       </c>
       <c r="P33">
-        <v>17.530728264</v>
+        <v>17.432558208</v>
       </c>
       <c r="Q33">
-        <v>31.530728264</v>
+        <v>31.432558208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1190380449465134</v>
+        <v>0.1199650392711566</v>
       </c>
       <c r="T33">
-        <v>1.234898653156179</v>
+        <v>1.250529109209741</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.760487325736462</v>
+        <v>6.549222096807197</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09565078670438648</v>
+        <v>0.0955305923956787</v>
       </c>
       <c r="C34">
-        <v>165.4254759484938</v>
+        <v>163.6483333599676</v>
       </c>
       <c r="D34">
-        <v>226.1494759484938</v>
+        <v>226.6043333599676</v>
       </c>
       <c r="E34">
-        <v>71.42399999999999</v>
+        <v>73.65600000000001</v>
       </c>
       <c r="F34">
-        <v>71.42399999999999</v>
+        <v>73.65600000000001</v>
       </c>
       <c r="G34">
         <v>10.7</v>
@@ -4075,28 +4075,28 @@
         <v>25.4</v>
       </c>
       <c r="M34">
-        <v>3.8783232</v>
+        <v>3.9995208</v>
       </c>
       <c r="N34">
-        <v>21.5216768</v>
+        <v>21.4004792</v>
       </c>
       <c r="O34">
-        <v>4.089118591999999</v>
+        <v>4.066091048</v>
       </c>
       <c r="P34">
-        <v>17.432558208</v>
+        <v>17.334388152</v>
       </c>
       <c r="Q34">
-        <v>31.432558208</v>
+        <v>31.334388152</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1199650392711566</v>
+        <v>0.1209197050681772</v>
       </c>
       <c r="T34">
-        <v>1.250529109209741</v>
+        <v>1.266626146041021</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.549222096807197</v>
+        <v>6.350760821146372</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0955305923956787</v>
+        <v>0.09541039808697094</v>
       </c>
       <c r="C35">
-        <v>163.6483333599676</v>
+        <v>161.8730241803734</v>
       </c>
       <c r="D35">
-        <v>226.6043333599676</v>
+        <v>227.0610241803734</v>
       </c>
       <c r="E35">
-        <v>73.65600000000001</v>
+        <v>75.88800000000001</v>
       </c>
       <c r="F35">
-        <v>73.65600000000001</v>
+        <v>75.88800000000001</v>
       </c>
       <c r="G35">
         <v>10.7</v>
@@ -4157,28 +4157,28 @@
         <v>25.4</v>
       </c>
       <c r="M35">
-        <v>3.9995208</v>
+        <v>4.1207184</v>
       </c>
       <c r="N35">
-        <v>21.4004792</v>
+        <v>21.2792816</v>
       </c>
       <c r="O35">
-        <v>4.066091048</v>
+        <v>4.043063503999999</v>
       </c>
       <c r="P35">
-        <v>17.334388152</v>
+        <v>17.236218096</v>
       </c>
       <c r="Q35">
-        <v>31.334388152</v>
+        <v>31.236218096</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1209197050681772</v>
+        <v>0.1219033001317742</v>
       </c>
       <c r="T35">
-        <v>1.266626146041021</v>
+        <v>1.283210971867189</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.350760821146372</v>
+        <v>6.163973738171479</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09541039808697094</v>
+        <v>0.09557370377826316</v>
       </c>
       <c r="C36">
-        <v>161.8730241803734</v>
+        <v>159.0209744781796</v>
       </c>
       <c r="D36">
-        <v>227.0610241803734</v>
+        <v>226.4409744781796</v>
       </c>
       <c r="E36">
-        <v>75.88800000000001</v>
+        <v>78.12</v>
       </c>
       <c r="F36">
-        <v>75.88800000000001</v>
+        <v>78.12</v>
       </c>
       <c r="G36">
         <v>10.7</v>
@@ -4239,45 +4239,45 @@
         <v>25.4</v>
       </c>
       <c r="M36">
-        <v>4.1207184</v>
+        <v>4.320036</v>
       </c>
       <c r="N36">
-        <v>21.2792816</v>
+        <v>21.079964</v>
       </c>
       <c r="O36">
-        <v>4.043063503999999</v>
+        <v>4.005193159999999</v>
       </c>
       <c r="P36">
-        <v>17.236218096</v>
+        <v>17.07477084</v>
       </c>
       <c r="Q36">
-        <v>31.236218096</v>
+        <v>31.07477084</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1219033001317742</v>
+        <v>0.1229171596588664</v>
       </c>
       <c r="T36">
-        <v>1.283210971867189</v>
+        <v>1.30030610002647</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.163973738171479</v>
+        <v>5.879580633124353</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09557370377826316</v>
+        <v>0.0954616094695554</v>
       </c>
       <c r="C37">
-        <v>159.0209744781796</v>
+        <v>157.2142163109934</v>
       </c>
       <c r="D37">
-        <v>226.4409744781796</v>
+        <v>226.8662163109934</v>
       </c>
       <c r="E37">
-        <v>78.12</v>
+        <v>80.352</v>
       </c>
       <c r="F37">
-        <v>78.12</v>
+        <v>80.352</v>
       </c>
       <c r="G37">
         <v>10.7</v>
@@ -4321,28 +4321,28 @@
         <v>25.4</v>
       </c>
       <c r="M37">
-        <v>4.320036</v>
+        <v>4.443465600000001</v>
       </c>
       <c r="N37">
-        <v>21.079964</v>
+        <v>20.9565344</v>
       </c>
       <c r="O37">
-        <v>4.005193159999999</v>
+        <v>3.981741536</v>
       </c>
       <c r="P37">
-        <v>17.07477084</v>
+        <v>16.974792864</v>
       </c>
       <c r="Q37">
-        <v>31.07477084</v>
+        <v>30.974792864</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1229171596588664</v>
+        <v>0.1239627022961803</v>
       </c>
       <c r="T37">
-        <v>1.30030610002647</v>
+        <v>1.317935450940728</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.879580633124353</v>
+        <v>5.716258948870898</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0954616094695554</v>
+        <v>0.09534951516084764</v>
       </c>
       <c r="C38">
-        <v>157.2142163109934</v>
+        <v>155.4090583033559</v>
       </c>
       <c r="D38">
-        <v>226.8662163109934</v>
+        <v>227.2930583033559</v>
       </c>
       <c r="E38">
-        <v>80.35199999999999</v>
+        <v>82.58399999999999</v>
       </c>
       <c r="F38">
-        <v>80.35199999999999</v>
+        <v>82.58399999999999</v>
       </c>
       <c r="G38">
         <v>10.7</v>
@@ -4403,28 +4403,28 @@
         <v>25.4</v>
       </c>
       <c r="M38">
-        <v>4.4434656</v>
+        <v>4.566895199999999</v>
       </c>
       <c r="N38">
-        <v>20.9565344</v>
+        <v>20.8331048</v>
       </c>
       <c r="O38">
-        <v>3.981741536</v>
+        <v>3.958289912</v>
       </c>
       <c r="P38">
-        <v>16.974792864</v>
+        <v>16.874814888</v>
       </c>
       <c r="Q38">
-        <v>30.974792864</v>
+        <v>30.874814888</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1239627022961803</v>
+        <v>0.1250414367632502</v>
       </c>
       <c r="T38">
-        <v>1.317935450940728</v>
+        <v>1.336124463788772</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.716258948870899</v>
+        <v>5.561765463766282</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09534951516084764</v>
+        <v>0.09523742085213988</v>
       </c>
       <c r="C39">
-        <v>155.4090583033559</v>
+        <v>153.6055095042493</v>
       </c>
       <c r="D39">
-        <v>227.2930583033559</v>
+        <v>227.7215095042493</v>
       </c>
       <c r="E39">
-        <v>82.58399999999999</v>
+        <v>84.816</v>
       </c>
       <c r="F39">
-        <v>82.58399999999999</v>
+        <v>84.816</v>
       </c>
       <c r="G39">
         <v>10.7</v>
@@ -4485,28 +4485,28 @@
         <v>25.4</v>
       </c>
       <c r="M39">
-        <v>4.566895199999999</v>
+        <v>4.6903248</v>
       </c>
       <c r="N39">
-        <v>20.8331048</v>
+        <v>20.7096752</v>
       </c>
       <c r="O39">
-        <v>3.958289912</v>
+        <v>3.934838288</v>
       </c>
       <c r="P39">
-        <v>16.874814888</v>
+        <v>16.774836912</v>
       </c>
       <c r="Q39">
-        <v>30.874814888</v>
+        <v>30.774836912</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1250414367632502</v>
+        <v>0.1261549691163546</v>
       </c>
       <c r="T39">
-        <v>1.336124463788772</v>
+        <v>1.354900218986753</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.561765463766282</v>
+        <v>5.4154032147198</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09523742085213988</v>
+        <v>0.09512532654343209</v>
       </c>
       <c r="C40">
-        <v>153.6055095042493</v>
+        <v>151.8035790310147</v>
       </c>
       <c r="D40">
-        <v>227.7215095042493</v>
+        <v>228.1515790310147</v>
       </c>
       <c r="E40">
-        <v>84.816</v>
+        <v>87.048</v>
       </c>
       <c r="F40">
-        <v>84.816</v>
+        <v>87.048</v>
       </c>
       <c r="G40">
         <v>10.7</v>
@@ -4567,28 +4567,28 @@
         <v>25.4</v>
       </c>
       <c r="M40">
-        <v>4.6903248</v>
+        <v>4.813754400000001</v>
       </c>
       <c r="N40">
-        <v>20.7096752</v>
+        <v>20.5862456</v>
       </c>
       <c r="O40">
-        <v>3.934838288</v>
+        <v>3.911386664</v>
       </c>
       <c r="P40">
-        <v>16.774836912</v>
+        <v>16.674858936</v>
       </c>
       <c r="Q40">
-        <v>30.774836912</v>
+        <v>30.674858936</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1261549691163546</v>
+        <v>0.1273050107269379</v>
       </c>
       <c r="T40">
-        <v>1.354900218986753</v>
+        <v>1.374291572715816</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.4154032147198</v>
+        <v>5.276546722034675</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09512532654343209</v>
+        <v>0.09501323223472434</v>
       </c>
       <c r="C41">
-        <v>151.8035790310147</v>
+        <v>150.0032760699984</v>
       </c>
       <c r="D41">
-        <v>228.1515790310147</v>
+        <v>228.5832760699984</v>
       </c>
       <c r="E41">
-        <v>87.048</v>
+        <v>89.28</v>
       </c>
       <c r="F41">
-        <v>87.048</v>
+        <v>89.28</v>
       </c>
       <c r="G41">
         <v>10.7</v>
@@ -4649,28 +4649,28 @@
         <v>25.4</v>
       </c>
       <c r="M41">
-        <v>4.813754400000001</v>
+        <v>4.937184</v>
       </c>
       <c r="N41">
-        <v>20.5862456</v>
+        <v>20.462816</v>
       </c>
       <c r="O41">
-        <v>3.911386664</v>
+        <v>3.887935039999999</v>
       </c>
       <c r="P41">
-        <v>16.674858936</v>
+        <v>16.57488096</v>
       </c>
       <c r="Q41">
-        <v>30.674858936</v>
+        <v>30.57488096</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1273050107269379</v>
+        <v>0.1284933870578739</v>
       </c>
       <c r="T41">
-        <v>1.374291572715816</v>
+        <v>1.394329304902513</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.276546722034675</v>
+        <v>5.144633053983808</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09501323223472434</v>
+        <v>0.09490113792601657</v>
       </c>
       <c r="C42">
-        <v>150.0032760699984</v>
+        <v>148.2046098772067</v>
       </c>
       <c r="D42">
-        <v>228.5832760699984</v>
+        <v>229.0166098772067</v>
       </c>
       <c r="E42">
-        <v>89.28</v>
+        <v>91.512</v>
       </c>
       <c r="F42">
-        <v>89.28</v>
+        <v>91.512</v>
       </c>
       <c r="G42">
         <v>10.7</v>
@@ -4731,28 +4731,28 @@
         <v>25.4</v>
       </c>
       <c r="M42">
-        <v>4.937184</v>
+        <v>5.0606136</v>
       </c>
       <c r="N42">
-        <v>20.462816</v>
+        <v>20.3393864</v>
       </c>
       <c r="O42">
-        <v>3.887935039999999</v>
+        <v>3.864483416</v>
       </c>
       <c r="P42">
-        <v>16.57488096</v>
+        <v>16.474902984</v>
       </c>
       <c r="Q42">
-        <v>30.57488096</v>
+        <v>30.474902984</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1284933870578739</v>
+        <v>0.1297220473322315</v>
       </c>
       <c r="T42">
-        <v>1.394329304902513</v>
+        <v>1.415046282248082</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.144633053983808</v>
+        <v>5.019154199008594</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09490113792601657</v>
+        <v>0.09478904361730882</v>
       </c>
       <c r="C43">
-        <v>148.2046098772067</v>
+        <v>146.4075897789666</v>
       </c>
       <c r="D43">
-        <v>229.0166098772067</v>
+        <v>229.4515897789666</v>
       </c>
       <c r="E43">
-        <v>91.512</v>
+        <v>93.744</v>
       </c>
       <c r="F43">
-        <v>91.512</v>
+        <v>93.744</v>
       </c>
       <c r="G43">
         <v>10.7</v>
@@ -4813,28 +4813,28 @@
         <v>25.4</v>
       </c>
       <c r="M43">
-        <v>5.0606136</v>
+        <v>5.184043200000001</v>
       </c>
       <c r="N43">
-        <v>20.3393864</v>
+        <v>20.2159568</v>
       </c>
       <c r="O43">
-        <v>3.864483416</v>
+        <v>3.841031791999999</v>
       </c>
       <c r="P43">
-        <v>16.474902984</v>
+        <v>16.374925008</v>
       </c>
       <c r="Q43">
-        <v>30.474902984</v>
+        <v>30.374925008</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1297220473322315</v>
+        <v>0.1309930752022566</v>
       </c>
       <c r="T43">
-        <v>1.415046282248082</v>
+        <v>1.436477638122809</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.019154199008594</v>
+        <v>4.899650527603627</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09478904361730882</v>
+        <v>0.09467694930860106</v>
       </c>
       <c r="C44">
-        <v>146.4075897789666</v>
+        <v>144.6122251725958</v>
       </c>
       <c r="D44">
-        <v>229.4515897789666</v>
+        <v>229.8882251725958</v>
       </c>
       <c r="E44">
-        <v>93.74399999999999</v>
+        <v>95.976</v>
       </c>
       <c r="F44">
-        <v>93.74399999999999</v>
+        <v>95.976</v>
       </c>
       <c r="G44">
         <v>10.7</v>
@@ -4895,28 +4895,28 @@
         <v>25.4</v>
       </c>
       <c r="M44">
-        <v>5.1840432</v>
+        <v>5.3074728</v>
       </c>
       <c r="N44">
-        <v>20.2159568</v>
+        <v>20.0925272</v>
       </c>
       <c r="O44">
-        <v>3.841031792</v>
+        <v>3.817580168</v>
       </c>
       <c r="P44">
-        <v>16.374925008</v>
+        <v>16.274947032</v>
       </c>
       <c r="Q44">
-        <v>30.374925008</v>
+        <v>30.274947032</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1309930752022566</v>
+        <v>0.1323087005414053</v>
       </c>
       <c r="T44">
-        <v>1.436477638122809</v>
+        <v>1.458660971396649</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.899650527603629</v>
+        <v>4.785705166496566</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09467694930860106</v>
+        <v>0.0945648549998933</v>
       </c>
       <c r="C45">
-        <v>144.6122251725958</v>
+        <v>142.8185255270785</v>
       </c>
       <c r="D45">
-        <v>229.8882251725958</v>
+        <v>230.3265255270785</v>
       </c>
       <c r="E45">
-        <v>95.976</v>
+        <v>98.208</v>
       </c>
       <c r="F45">
-        <v>95.976</v>
+        <v>98.208</v>
       </c>
       <c r="G45">
         <v>10.7</v>
@@ -4977,28 +4977,28 @@
         <v>25.4</v>
       </c>
       <c r="M45">
-        <v>5.3074728</v>
+        <v>5.4309024</v>
       </c>
       <c r="N45">
-        <v>20.0925272</v>
+        <v>19.9690976</v>
       </c>
       <c r="O45">
-        <v>3.817580168</v>
+        <v>3.794128543999999</v>
       </c>
       <c r="P45">
-        <v>16.274947032</v>
+        <v>16.174969056</v>
       </c>
       <c r="Q45">
-        <v>30.274947032</v>
+        <v>30.174969056</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1323087005414053</v>
+        <v>0.1336713124998094</v>
       </c>
       <c r="T45">
-        <v>1.458660971396649</v>
+        <v>1.481636566573125</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.785705166496566</v>
+        <v>4.676939139985281</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0945648549998933</v>
+        <v>0.09445276069118551</v>
       </c>
       <c r="C46">
-        <v>142.8185255270785</v>
+        <v>141.0265003837509</v>
       </c>
       <c r="D46">
-        <v>230.3265255270785</v>
+        <v>230.7665003837509</v>
       </c>
       <c r="E46">
-        <v>98.208</v>
+        <v>100.44</v>
       </c>
       <c r="F46">
-        <v>98.208</v>
+        <v>100.44</v>
       </c>
       <c r="G46">
         <v>10.7</v>
@@ -5059,28 +5059,28 @@
         <v>25.4</v>
       </c>
       <c r="M46">
-        <v>5.4309024</v>
+        <v>5.554332</v>
       </c>
       <c r="N46">
-        <v>19.9690976</v>
+        <v>19.845668</v>
       </c>
       <c r="O46">
-        <v>3.794128543999999</v>
+        <v>3.770676919999999</v>
       </c>
       <c r="P46">
-        <v>16.174969056</v>
+        <v>16.07499108</v>
       </c>
       <c r="Q46">
-        <v>30.174969056</v>
+        <v>30.07499108</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1336713124998094</v>
+        <v>0.1350834739839736</v>
       </c>
       <c r="T46">
-        <v>1.481636566573125</v>
+        <v>1.505447637937838</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.676939139985281</v>
+        <v>4.573007159096719</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09445276069118551</v>
+        <v>0.09527216638247775</v>
       </c>
       <c r="C47">
-        <v>141.0265003837509</v>
+        <v>135.6165311520747</v>
       </c>
       <c r="D47">
-        <v>230.7665003837509</v>
+        <v>227.5885311520747</v>
       </c>
       <c r="E47">
-        <v>100.44</v>
+        <v>102.672</v>
       </c>
       <c r="F47">
-        <v>100.44</v>
+        <v>102.672</v>
       </c>
       <c r="G47">
         <v>10.7</v>
@@ -5141,45 +5141,45 @@
         <v>25.4</v>
       </c>
       <c r="M47">
-        <v>5.554332</v>
+        <v>5.9344416</v>
       </c>
       <c r="N47">
-        <v>19.845668</v>
+        <v>19.4655584</v>
       </c>
       <c r="O47">
-        <v>3.770676919999999</v>
+        <v>3.698456096</v>
       </c>
       <c r="P47">
-        <v>16.07499108</v>
+        <v>15.767102304</v>
       </c>
       <c r="Q47">
-        <v>30.07499108</v>
+        <v>29.767102304</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1350834739839736</v>
+        <v>0.1365479377453291</v>
       </c>
       <c r="T47">
-        <v>1.505447637937838</v>
+        <v>1.530140600834576</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.19</v>
       </c>
       <c r="W47">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.573007159096719</v>
+        <v>4.280099411543623</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09527216638247775</v>
+        <v>0.09518032207376999</v>
       </c>
       <c r="C48">
-        <v>135.6165311520747</v>
+        <v>133.7363762126681</v>
       </c>
       <c r="D48">
-        <v>227.5885311520747</v>
+        <v>227.9403762126681</v>
       </c>
       <c r="E48">
-        <v>102.672</v>
+        <v>104.904</v>
       </c>
       <c r="F48">
-        <v>102.672</v>
+        <v>104.904</v>
       </c>
       <c r="G48">
         <v>10.7</v>
@@ -5223,28 +5223,28 @@
         <v>25.4</v>
       </c>
       <c r="M48">
-        <v>5.9344416</v>
+        <v>6.0634512</v>
       </c>
       <c r="N48">
-        <v>19.4655584</v>
+        <v>19.3365488</v>
       </c>
       <c r="O48">
-        <v>3.698456096</v>
+        <v>3.673944272</v>
       </c>
       <c r="P48">
-        <v>15.767102304</v>
+        <v>15.662604528</v>
       </c>
       <c r="Q48">
-        <v>29.767102304</v>
+        <v>29.662604528</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1365479377453291</v>
+        <v>0.138067664290132</v>
       </c>
       <c r="T48">
-        <v>1.530140600834576</v>
+        <v>1.555765373651947</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.280099411543623</v>
+        <v>4.189033466617163</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09518032207376999</v>
+        <v>0.09508847776506221</v>
       </c>
       <c r="C49">
-        <v>133.7363762126681</v>
+        <v>131.8573108415771</v>
       </c>
       <c r="D49">
-        <v>227.9403762126681</v>
+        <v>228.2933108415772</v>
       </c>
       <c r="E49">
-        <v>104.904</v>
+        <v>107.136</v>
       </c>
       <c r="F49">
-        <v>104.904</v>
+        <v>107.136</v>
       </c>
       <c r="G49">
         <v>10.7</v>
@@ -5305,28 +5305,28 @@
         <v>25.4</v>
       </c>
       <c r="M49">
-        <v>6.0634512</v>
+        <v>6.192460800000001</v>
       </c>
       <c r="N49">
-        <v>19.3365488</v>
+        <v>19.2075392</v>
       </c>
       <c r="O49">
-        <v>3.673944272</v>
+        <v>3.649432448</v>
       </c>
       <c r="P49">
-        <v>15.662604528</v>
+        <v>15.558106752</v>
       </c>
       <c r="Q49">
-        <v>29.662604528</v>
+        <v>29.558106752</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.138067664290132</v>
+        <v>0.1396458418558889</v>
       </c>
       <c r="T49">
-        <v>1.555765373651947</v>
+        <v>1.582375714654601</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.189033466617163</v>
+        <v>4.101761936062639</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09508847776506221</v>
+        <v>0.09499663345635444</v>
       </c>
       <c r="C50">
-        <v>131.8573108415772</v>
+        <v>129.9793401077951</v>
       </c>
       <c r="D50">
-        <v>228.2933108415772</v>
+        <v>228.6473401077951</v>
       </c>
       <c r="E50">
-        <v>107.136</v>
+        <v>109.368</v>
       </c>
       <c r="F50">
-        <v>107.136</v>
+        <v>109.368</v>
       </c>
       <c r="G50">
         <v>10.7</v>
@@ -5387,28 +5387,28 @@
         <v>25.4</v>
       </c>
       <c r="M50">
-        <v>6.1924608</v>
+        <v>6.3214704</v>
       </c>
       <c r="N50">
-        <v>19.2075392</v>
+        <v>19.0785296</v>
       </c>
       <c r="O50">
-        <v>3.649432448</v>
+        <v>3.624920624</v>
       </c>
       <c r="P50">
-        <v>15.558106752</v>
+        <v>15.453608976</v>
       </c>
       <c r="Q50">
-        <v>29.558106752</v>
+        <v>29.453608976</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1396458418558889</v>
+        <v>0.1412859087379499</v>
       </c>
       <c r="T50">
-        <v>1.5823757146546</v>
+        <v>1.610029598441672</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.101761936062639</v>
+        <v>4.018052508796055</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09499663345635444</v>
+        <v>0.09632228914764668</v>
       </c>
       <c r="C51">
-        <v>129.9793401077951</v>
+        <v>122.7415012147319</v>
       </c>
       <c r="D51">
-        <v>228.6473401077951</v>
+        <v>223.6415012147319</v>
       </c>
       <c r="E51">
-        <v>109.368</v>
+        <v>111.6</v>
       </c>
       <c r="F51">
-        <v>109.368</v>
+        <v>111.6</v>
       </c>
       <c r="G51">
         <v>10.7</v>
@@ -5469,45 +5469,45 @@
         <v>25.4</v>
       </c>
       <c r="M51">
-        <v>6.3214704</v>
+        <v>6.84108</v>
       </c>
       <c r="N51">
-        <v>19.0785296</v>
+        <v>18.55892</v>
       </c>
       <c r="O51">
-        <v>3.624920624</v>
+        <v>3.5261948</v>
       </c>
       <c r="P51">
-        <v>15.453608976</v>
+        <v>15.0327252</v>
       </c>
       <c r="Q51">
-        <v>29.453608976</v>
+        <v>29.0327252</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1412859087379499</v>
+        <v>0.1429915782952934</v>
       </c>
       <c r="T51">
-        <v>1.610029598441672</v>
+        <v>1.638789637580227</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.018052508796055</v>
+        <v>3.712864050705444</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09632228914764668</v>
+        <v>0.09625879483893893</v>
       </c>
       <c r="C52">
-        <v>122.7415012147319</v>
+        <v>120.7442605209477</v>
       </c>
       <c r="D52">
-        <v>223.6415012147319</v>
+        <v>223.8762605209477</v>
       </c>
       <c r="E52">
-        <v>111.6</v>
+        <v>113.832</v>
       </c>
       <c r="F52">
-        <v>111.6</v>
+        <v>113.832</v>
       </c>
       <c r="G52">
         <v>10.7</v>
@@ -5551,28 +5551,28 @@
         <v>25.4</v>
       </c>
       <c r="M52">
-        <v>6.84108</v>
+        <v>6.9779016</v>
       </c>
       <c r="N52">
-        <v>18.55892</v>
+        <v>18.4220984</v>
       </c>
       <c r="O52">
-        <v>3.5261948</v>
+        <v>3.500198696</v>
       </c>
       <c r="P52">
-        <v>15.0327252</v>
+        <v>14.921899704</v>
       </c>
       <c r="Q52">
-        <v>29.0327252</v>
+        <v>28.921899704</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1429915782952934</v>
+        <v>0.1447668670182427</v>
       </c>
       <c r="T52">
-        <v>1.638789637580227</v>
+        <v>1.668723555867294</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.712864050705444</v>
+        <v>3.640062794809259</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09625879483893893</v>
+        <v>0.09619530053023115</v>
       </c>
       <c r="C53">
-        <v>120.7442605209477</v>
+        <v>118.7475132046811</v>
       </c>
       <c r="D53">
-        <v>223.8762605209477</v>
+        <v>224.1115132046811</v>
       </c>
       <c r="E53">
-        <v>113.832</v>
+        <v>116.064</v>
       </c>
       <c r="F53">
-        <v>113.832</v>
+        <v>116.064</v>
       </c>
       <c r="G53">
         <v>10.7</v>
@@ -5633,28 +5633,28 @@
         <v>25.4</v>
       </c>
       <c r="M53">
-        <v>6.9779016</v>
+        <v>7.114723199999999</v>
       </c>
       <c r="N53">
-        <v>18.4220984</v>
+        <v>18.2852768</v>
       </c>
       <c r="O53">
-        <v>3.500198696</v>
+        <v>3.474202592</v>
       </c>
       <c r="P53">
-        <v>14.921899704</v>
+        <v>14.811074208</v>
       </c>
       <c r="Q53">
-        <v>28.921899704</v>
+        <v>28.811074208</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1447668670182427</v>
+        <v>0.1466161261046482</v>
       </c>
       <c r="T53">
-        <v>1.668723555867294</v>
+        <v>1.699904720749655</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.640062794809259</v>
+        <v>3.570061587216773</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09619530053023115</v>
+        <v>0.09613180622152337</v>
       </c>
       <c r="C54">
-        <v>118.7475132046811</v>
+        <v>116.7512608229146</v>
       </c>
       <c r="D54">
-        <v>224.1115132046811</v>
+        <v>224.3472608229146</v>
       </c>
       <c r="E54">
-        <v>116.064</v>
+        <v>118.296</v>
       </c>
       <c r="F54">
-        <v>116.064</v>
+        <v>118.296</v>
       </c>
       <c r="G54">
         <v>10.7</v>
@@ -5715,28 +5715,28 @@
         <v>25.4</v>
       </c>
       <c r="M54">
-        <v>7.114723199999999</v>
+        <v>7.2515448</v>
       </c>
       <c r="N54">
-        <v>18.2852768</v>
+        <v>18.1484552</v>
       </c>
       <c r="O54">
-        <v>3.474202592</v>
+        <v>3.448206487999999</v>
       </c>
       <c r="P54">
-        <v>14.811074208</v>
+        <v>14.700248712</v>
       </c>
       <c r="Q54">
-        <v>28.811074208</v>
+        <v>28.700248712</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1466161261046482</v>
+        <v>0.148544077067071</v>
       </c>
       <c r="T54">
-        <v>1.699904720749655</v>
+        <v>1.732412743712117</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.570061587216773</v>
+        <v>3.502701934627777</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09613180622152337</v>
+        <v>0.09729303191281562</v>
       </c>
       <c r="C55">
-        <v>116.7512608229146</v>
+        <v>110.2846836590137</v>
       </c>
       <c r="D55">
-        <v>224.3472608229146</v>
+        <v>220.1126836590137</v>
       </c>
       <c r="E55">
-        <v>118.296</v>
+        <v>120.528</v>
       </c>
       <c r="F55">
-        <v>118.296</v>
+        <v>120.528</v>
       </c>
       <c r="G55">
         <v>10.7</v>
@@ -5797,45 +5797,45 @@
         <v>25.4</v>
       </c>
       <c r="M55">
-        <v>7.2515448</v>
+        <v>7.725844800000001</v>
       </c>
       <c r="N55">
-        <v>18.1484552</v>
+        <v>17.6741552</v>
       </c>
       <c r="O55">
-        <v>3.448206487999999</v>
+        <v>3.358089488</v>
       </c>
       <c r="P55">
-        <v>14.700248712</v>
+        <v>14.316065712</v>
       </c>
       <c r="Q55">
-        <v>28.700248712</v>
+        <v>28.316065712</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.148544077067071</v>
+        <v>0.1505558519843818</v>
       </c>
       <c r="T55">
-        <v>1.732412743712117</v>
+        <v>1.766334158977295</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.502701934627777</v>
+        <v>3.287666353328764</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09729303191281562</v>
+        <v>0.09725221760410785</v>
       </c>
       <c r="C56">
-        <v>110.2846836590137</v>
+        <v>108.1988065886583</v>
       </c>
       <c r="D56">
-        <v>220.1126836590137</v>
+        <v>220.2588065886583</v>
       </c>
       <c r="E56">
-        <v>120.528</v>
+        <v>122.76</v>
       </c>
       <c r="F56">
-        <v>120.528</v>
+        <v>122.76</v>
       </c>
       <c r="G56">
         <v>10.7</v>
@@ -5879,28 +5879,28 @@
         <v>25.4</v>
       </c>
       <c r="M56">
-        <v>7.725844800000001</v>
+        <v>7.868916</v>
       </c>
       <c r="N56">
-        <v>17.6741552</v>
+        <v>17.531084</v>
       </c>
       <c r="O56">
-        <v>3.358089488</v>
+        <v>3.33090596</v>
       </c>
       <c r="P56">
-        <v>14.316065712</v>
+        <v>14.20017804</v>
       </c>
       <c r="Q56">
-        <v>28.316065712</v>
+        <v>28.20017804</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1505558519843818</v>
+        <v>0.1526570391202396</v>
       </c>
       <c r="T56">
-        <v>1.766334158977295</v>
+        <v>1.801763192698703</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.287666353328764</v>
+        <v>3.22789060145006</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09725221760410785</v>
+        <v>0.09721140329540008</v>
       </c>
       <c r="C57">
-        <v>108.1988065886583</v>
+        <v>106.113123656089</v>
       </c>
       <c r="D57">
-        <v>220.2588065886583</v>
+        <v>220.405123656089</v>
       </c>
       <c r="E57">
-        <v>122.76</v>
+        <v>124.992</v>
       </c>
       <c r="F57">
-        <v>122.76</v>
+        <v>124.992</v>
       </c>
       <c r="G57">
         <v>10.7</v>
@@ -5961,28 +5961,28 @@
         <v>25.4</v>
       </c>
       <c r="M57">
-        <v>7.868916</v>
+        <v>8.0119872</v>
       </c>
       <c r="N57">
-        <v>17.531084</v>
+        <v>17.3880128</v>
       </c>
       <c r="O57">
-        <v>3.33090596</v>
+        <v>3.303722432</v>
       </c>
       <c r="P57">
-        <v>14.20017804</v>
+        <v>14.084290368</v>
       </c>
       <c r="Q57">
-        <v>28.20017804</v>
+        <v>28.084290368</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1526570391202396</v>
+        <v>0.1548537347622729</v>
       </c>
       <c r="T57">
-        <v>1.801763192698703</v>
+        <v>1.838802637043811</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.22789060145006</v>
+        <v>3.170249697852737</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09721140329540008</v>
+        <v>0.0971705889866923</v>
       </c>
       <c r="C58">
-        <v>106.113123656089</v>
+        <v>104.0276352484581</v>
       </c>
       <c r="D58">
-        <v>220.405123656089</v>
+        <v>220.5516352484581</v>
       </c>
       <c r="E58">
-        <v>124.992</v>
+        <v>127.224</v>
       </c>
       <c r="F58">
-        <v>124.992</v>
+        <v>127.224</v>
       </c>
       <c r="G58">
         <v>10.7</v>
@@ -6043,28 +6043,28 @@
         <v>25.4</v>
       </c>
       <c r="M58">
-        <v>8.0119872</v>
+        <v>8.155058400000001</v>
       </c>
       <c r="N58">
-        <v>17.3880128</v>
+        <v>17.2449416</v>
       </c>
       <c r="O58">
-        <v>3.303722432</v>
+        <v>3.276538904</v>
       </c>
       <c r="P58">
-        <v>14.084290368</v>
+        <v>13.968402696</v>
       </c>
       <c r="Q58">
-        <v>28.084290368</v>
+        <v>27.968402696</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1548537347622729</v>
+        <v>0.1571526022946333</v>
       </c>
       <c r="T58">
-        <v>1.838802637043811</v>
+        <v>1.877564846242179</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.170249697852737</v>
+        <v>3.114631282100934</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0971705889866923</v>
+        <v>0.09712977467798455</v>
       </c>
       <c r="C59">
-        <v>104.0276352484581</v>
+        <v>101.9423417539476</v>
       </c>
       <c r="D59">
-        <v>220.5516352484581</v>
+        <v>220.6983417539476</v>
       </c>
       <c r="E59">
-        <v>127.224</v>
+        <v>129.456</v>
       </c>
       <c r="F59">
-        <v>127.224</v>
+        <v>129.456</v>
       </c>
       <c r="G59">
         <v>10.7</v>
@@ -6125,28 +6125,28 @@
         <v>25.4</v>
       </c>
       <c r="M59">
-        <v>8.155058400000001</v>
+        <v>8.298129600000001</v>
       </c>
       <c r="N59">
-        <v>17.2449416</v>
+        <v>17.1018704</v>
       </c>
       <c r="O59">
-        <v>3.276538904</v>
+        <v>3.249355375999999</v>
       </c>
       <c r="P59">
-        <v>13.968402696</v>
+        <v>13.852515024</v>
       </c>
       <c r="Q59">
-        <v>27.968402696</v>
+        <v>27.852515024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1571526022946333</v>
+        <v>0.159560939709487</v>
       </c>
       <c r="T59">
-        <v>1.877564846242179</v>
+        <v>1.918172874926185</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.114631282100934</v>
+        <v>3.060930742754366</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09712977467798455</v>
+        <v>0.09708896036927678</v>
       </c>
       <c r="C60">
-        <v>101.9423417539476</v>
+        <v>99.85724356177346</v>
       </c>
       <c r="D60">
-        <v>220.6983417539476</v>
+        <v>220.8452435617735</v>
       </c>
       <c r="E60">
-        <v>129.456</v>
+        <v>131.688</v>
       </c>
       <c r="F60">
-        <v>129.456</v>
+        <v>131.688</v>
       </c>
       <c r="G60">
         <v>10.7</v>
@@ -6207,28 +6207,28 @@
         <v>25.4</v>
       </c>
       <c r="M60">
-        <v>8.298129599999999</v>
+        <v>8.441200799999999</v>
       </c>
       <c r="N60">
-        <v>17.1018704</v>
+        <v>16.9587992</v>
       </c>
       <c r="O60">
-        <v>3.249355376</v>
+        <v>3.222171848</v>
       </c>
       <c r="P60">
-        <v>13.852515024</v>
+        <v>13.736627352</v>
       </c>
       <c r="Q60">
-        <v>27.852515024</v>
+        <v>27.736627352</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.159560939709487</v>
+        <v>0.162086756998236</v>
       </c>
       <c r="T60">
-        <v>1.918172874926185</v>
+        <v>1.960761783058191</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.060930742754367</v>
+        <v>3.009050560673785</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09708896036927678</v>
+        <v>0.100838946060569</v>
       </c>
       <c r="C61">
-        <v>99.85724356177346</v>
+        <v>84.8974331739883</v>
       </c>
       <c r="D61">
-        <v>220.8452435617735</v>
+        <v>208.1174331739883</v>
       </c>
       <c r="E61">
-        <v>131.688</v>
+        <v>133.92</v>
       </c>
       <c r="F61">
-        <v>131.688</v>
+        <v>133.92</v>
       </c>
       <c r="G61">
         <v>10.7</v>
@@ -6289,45 +6289,45 @@
         <v>25.4</v>
       </c>
       <c r="M61">
-        <v>8.441200799999999</v>
+        <v>9.628848</v>
       </c>
       <c r="N61">
-        <v>16.9587992</v>
+        <v>15.771152</v>
       </c>
       <c r="O61">
-        <v>3.222171848</v>
+        <v>2.99651888</v>
       </c>
       <c r="P61">
-        <v>13.736627352</v>
+        <v>12.77463312</v>
       </c>
       <c r="Q61">
-        <v>27.736627352</v>
+        <v>26.77463312</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.162086756998236</v>
+        <v>0.1647388651514225</v>
       </c>
       <c r="T61">
-        <v>1.960761783058191</v>
+        <v>2.005480136596797</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.19</v>
       </c>
       <c r="W61">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.009050560673785</v>
+        <v>2.637906424527628</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.100838946060569</v>
+        <v>0.1008613117518612</v>
       </c>
       <c r="C62">
-        <v>84.8974331739883</v>
+        <v>82.59392139725082</v>
       </c>
       <c r="D62">
-        <v>208.1174331739883</v>
+        <v>208.0459213972508</v>
       </c>
       <c r="E62">
-        <v>133.92</v>
+        <v>136.152</v>
       </c>
       <c r="F62">
-        <v>133.92</v>
+        <v>136.152</v>
       </c>
       <c r="G62">
         <v>10.7</v>
@@ -6371,28 +6371,28 @@
         <v>25.4</v>
       </c>
       <c r="M62">
-        <v>9.628848</v>
+        <v>9.7893288</v>
       </c>
       <c r="N62">
-        <v>15.771152</v>
+        <v>15.6106712</v>
       </c>
       <c r="O62">
-        <v>2.99651888</v>
+        <v>2.966027528</v>
       </c>
       <c r="P62">
-        <v>12.77463312</v>
+        <v>12.644643672</v>
       </c>
       <c r="Q62">
-        <v>26.77463312</v>
+        <v>26.644643672</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1647388651514225</v>
+        <v>0.1675269788509263</v>
       </c>
       <c r="T62">
-        <v>2.005480136596797</v>
+        <v>2.052491739034819</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.637906424527628</v>
+        <v>2.594662056912421</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1008613117518612</v>
+        <v>0.1008836774431535</v>
       </c>
       <c r="C63">
-        <v>82.59392139725082</v>
+        <v>80.29045874833051</v>
       </c>
       <c r="D63">
-        <v>208.0459213972508</v>
+        <v>207.9744587483305</v>
       </c>
       <c r="E63">
-        <v>136.152</v>
+        <v>138.384</v>
       </c>
       <c r="F63">
-        <v>136.152</v>
+        <v>138.384</v>
       </c>
       <c r="G63">
         <v>10.7</v>
@@ -6453,28 +6453,28 @@
         <v>25.4</v>
       </c>
       <c r="M63">
-        <v>9.7893288</v>
+        <v>9.9498096</v>
       </c>
       <c r="N63">
-        <v>15.6106712</v>
+        <v>15.4501904</v>
       </c>
       <c r="O63">
-        <v>2.966027528</v>
+        <v>2.935536176</v>
       </c>
       <c r="P63">
-        <v>12.644643672</v>
+        <v>12.514654224</v>
       </c>
       <c r="Q63">
-        <v>26.644643672</v>
+        <v>26.514654224</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1675269788509263</v>
+        <v>0.1704618353767197</v>
       </c>
       <c r="T63">
-        <v>2.052491739034819</v>
+        <v>2.101977636338</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.594662056912421</v>
+        <v>2.552812668897704</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1008836774431535</v>
+        <v>0.1009060431344457</v>
       </c>
       <c r="C64">
-        <v>80.29045874833051</v>
+        <v>77.98704517661938</v>
       </c>
       <c r="D64">
-        <v>207.9744587483305</v>
+        <v>207.9030451766194</v>
       </c>
       <c r="E64">
-        <v>138.384</v>
+        <v>140.616</v>
       </c>
       <c r="F64">
-        <v>138.384</v>
+        <v>140.616</v>
       </c>
       <c r="G64">
         <v>10.7</v>
@@ -6535,28 +6535,28 @@
         <v>25.4</v>
       </c>
       <c r="M64">
-        <v>9.9498096</v>
+        <v>10.1102904</v>
       </c>
       <c r="N64">
-        <v>15.4501904</v>
+        <v>15.2897096</v>
       </c>
       <c r="O64">
-        <v>2.935536176</v>
+        <v>2.905044824</v>
       </c>
       <c r="P64">
-        <v>12.514654224</v>
+        <v>12.384664776</v>
       </c>
       <c r="Q64">
-        <v>26.514654224</v>
+        <v>26.384664776</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1704618353767197</v>
+        <v>0.1735553327957992</v>
       </c>
       <c r="T64">
-        <v>2.101977636338</v>
+        <v>2.15413844700892</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.552812668897704</v>
+        <v>2.512291832883455</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1009060431344457</v>
+        <v>0.102950168825738</v>
       </c>
       <c r="C65">
-        <v>77.98704517661938</v>
+        <v>69.42893346902895</v>
       </c>
       <c r="D65">
-        <v>207.9030451766194</v>
+        <v>201.5769334690289</v>
       </c>
       <c r="E65">
-        <v>140.616</v>
+        <v>142.848</v>
       </c>
       <c r="F65">
-        <v>140.616</v>
+        <v>142.848</v>
       </c>
       <c r="G65">
         <v>10.7</v>
@@ -6617,45 +6617,45 @@
         <v>25.4</v>
       </c>
       <c r="M65">
-        <v>10.1102904</v>
+        <v>10.8278784</v>
       </c>
       <c r="N65">
-        <v>15.2897096</v>
+        <v>14.5721216</v>
       </c>
       <c r="O65">
-        <v>2.905044824</v>
+        <v>2.768703104</v>
       </c>
       <c r="P65">
-        <v>12.384664776</v>
+        <v>11.803418496</v>
       </c>
       <c r="Q65">
-        <v>26.384664776</v>
+        <v>25.803418496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1735553327957992</v>
+        <v>0.1768206911826054</v>
       </c>
       <c r="T65">
-        <v>2.15413844700892</v>
+        <v>2.209197080494892</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.512291832883455</v>
+        <v>2.345796568975137</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.102950168825738</v>
+        <v>0.1030041245170302</v>
       </c>
       <c r="C66">
-        <v>69.42893346902895</v>
+        <v>67.0351635255337</v>
       </c>
       <c r="D66">
-        <v>201.5769334690289</v>
+        <v>201.4151635255337</v>
       </c>
       <c r="E66">
-        <v>142.848</v>
+        <v>145.08</v>
       </c>
       <c r="F66">
-        <v>142.848</v>
+        <v>145.08</v>
       </c>
       <c r="G66">
         <v>10.7</v>
@@ -6699,28 +6699,28 @@
         <v>25.4</v>
       </c>
       <c r="M66">
-        <v>10.8278784</v>
+        <v>10.997064</v>
       </c>
       <c r="N66">
-        <v>14.5721216</v>
+        <v>14.402936</v>
       </c>
       <c r="O66">
-        <v>2.768703104</v>
+        <v>2.73655784</v>
       </c>
       <c r="P66">
-        <v>11.803418496</v>
+        <v>11.66637816</v>
       </c>
       <c r="Q66">
-        <v>25.803418496</v>
+        <v>25.66637816</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1768206911826054</v>
+        <v>0.1802726414772291</v>
       </c>
       <c r="T66">
-        <v>2.209197080494892</v>
+        <v>2.267401921608633</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.345796568975137</v>
+        <v>2.309707390990904</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1030041245170302</v>
+        <v>0.1030580802083224</v>
       </c>
       <c r="C67">
-        <v>67.0351635255337</v>
+        <v>64.64165302174109</v>
       </c>
       <c r="D67">
-        <v>201.4151635255337</v>
+        <v>201.2536530217411</v>
       </c>
       <c r="E67">
-        <v>145.08</v>
+        <v>147.312</v>
       </c>
       <c r="F67">
-        <v>145.08</v>
+        <v>147.312</v>
       </c>
       <c r="G67">
         <v>10.7</v>
@@ -6781,28 +6781,28 @@
         <v>25.4</v>
       </c>
       <c r="M67">
-        <v>10.997064</v>
+        <v>11.1662496</v>
       </c>
       <c r="N67">
-        <v>14.402936</v>
+        <v>14.2337504</v>
       </c>
       <c r="O67">
-        <v>2.73655784</v>
+        <v>2.704412575999999</v>
       </c>
       <c r="P67">
-        <v>11.66637816</v>
+        <v>11.529337824</v>
       </c>
       <c r="Q67">
-        <v>25.66637816</v>
+        <v>25.529337824</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1802726414772291</v>
+        <v>0.1839276476715365</v>
       </c>
       <c r="T67">
-        <v>2.267401921608633</v>
+        <v>2.329030576905535</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.309707390990904</v>
+        <v>2.274711824460739</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1030580802083224</v>
+        <v>0.1031120358996147</v>
       </c>
       <c r="C68">
-        <v>64.64165302174109</v>
+        <v>62.24840133403387</v>
       </c>
       <c r="D68">
-        <v>201.2536530217411</v>
+        <v>201.0924013340339</v>
       </c>
       <c r="E68">
-        <v>147.312</v>
+        <v>149.544</v>
       </c>
       <c r="F68">
-        <v>147.312</v>
+        <v>149.544</v>
       </c>
       <c r="G68">
         <v>10.7</v>
@@ -6863,28 +6863,28 @@
         <v>25.4</v>
       </c>
       <c r="M68">
-        <v>11.1662496</v>
+        <v>11.3354352</v>
       </c>
       <c r="N68">
-        <v>14.2337504</v>
+        <v>14.0645648</v>
       </c>
       <c r="O68">
-        <v>2.704412575999999</v>
+        <v>2.672267312</v>
       </c>
       <c r="P68">
-        <v>11.529337824</v>
+        <v>11.392297488</v>
       </c>
       <c r="Q68">
-        <v>25.529337824</v>
+        <v>25.392297488</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1839276476715365</v>
+        <v>0.1878041693927717</v>
       </c>
       <c r="T68">
-        <v>2.329030576905535</v>
+        <v>2.394394302220432</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.274711824460739</v>
+        <v>2.240760901707594</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1031120358996147</v>
+        <v>0.1031659915909069</v>
       </c>
       <c r="C69">
-        <v>62.24840133403387</v>
+        <v>59.85540784079168</v>
       </c>
       <c r="D69">
-        <v>201.0924013340339</v>
+        <v>200.9314078407917</v>
       </c>
       <c r="E69">
-        <v>149.544</v>
+        <v>151.776</v>
       </c>
       <c r="F69">
-        <v>149.544</v>
+        <v>151.776</v>
       </c>
       <c r="G69">
         <v>10.7</v>
@@ -6945,28 +6945,28 @@
         <v>25.4</v>
       </c>
       <c r="M69">
-        <v>11.3354352</v>
+        <v>11.5046208</v>
       </c>
       <c r="N69">
-        <v>14.0645648</v>
+        <v>13.8953792</v>
       </c>
       <c r="O69">
-        <v>2.672267312</v>
+        <v>2.640122047999999</v>
       </c>
       <c r="P69">
-        <v>11.392297488</v>
+        <v>11.255257152</v>
       </c>
       <c r="Q69">
-        <v>25.392297488</v>
+        <v>25.255257152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1878041693927717</v>
+        <v>0.191922973721584</v>
       </c>
       <c r="T69">
-        <v>2.394394302220432</v>
+        <v>2.46384326036751</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.240760901707594</v>
+        <v>2.207808535506011</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1031659915909069</v>
+        <v>0.1032199472821991</v>
       </c>
       <c r="C70">
-        <v>59.85540784079168</v>
+        <v>57.46267192238341</v>
       </c>
       <c r="D70">
-        <v>200.9314078407917</v>
+        <v>200.7706719223834</v>
       </c>
       <c r="E70">
-        <v>151.776</v>
+        <v>154.008</v>
       </c>
       <c r="F70">
-        <v>151.776</v>
+        <v>154.008</v>
       </c>
       <c r="G70">
         <v>10.7</v>
@@ -7027,28 +7027,28 @@
         <v>25.4</v>
       </c>
       <c r="M70">
-        <v>11.5046208</v>
+        <v>11.6738064</v>
       </c>
       <c r="N70">
-        <v>13.8953792</v>
+        <v>13.7261936</v>
       </c>
       <c r="O70">
-        <v>2.640122047999999</v>
+        <v>2.607976783999999</v>
       </c>
       <c r="P70">
-        <v>11.255257152</v>
+        <v>11.118216816</v>
       </c>
       <c r="Q70">
-        <v>25.255257152</v>
+        <v>25.118216816</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.191922973721584</v>
+        <v>0.1963075073619326</v>
       </c>
       <c r="T70">
-        <v>2.46384326036751</v>
+        <v>2.53777279645956</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.207808535506011</v>
+        <v>2.17581131035375</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1032199472821991</v>
+        <v>0.1032739029734914</v>
       </c>
       <c r="C71">
-        <v>57.46267192238341</v>
+        <v>55.0701929611588</v>
       </c>
       <c r="D71">
-        <v>200.7706719223834</v>
+        <v>200.6101929611588</v>
       </c>
       <c r="E71">
-        <v>154.008</v>
+        <v>156.24</v>
       </c>
       <c r="F71">
-        <v>154.008</v>
+        <v>156.24</v>
       </c>
       <c r="G71">
         <v>10.7</v>
@@ -7109,28 +7109,28 @@
         <v>25.4</v>
       </c>
       <c r="M71">
-        <v>11.6738064</v>
+        <v>11.842992</v>
       </c>
       <c r="N71">
-        <v>13.7261936</v>
+        <v>13.557008</v>
       </c>
       <c r="O71">
-        <v>2.607976783999999</v>
+        <v>2.575831519999999</v>
       </c>
       <c r="P71">
-        <v>11.118216816</v>
+        <v>10.98117648</v>
       </c>
       <c r="Q71">
-        <v>25.118216816</v>
+        <v>24.98117647999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1963075073619326</v>
+        <v>0.2009843432449712</v>
       </c>
       <c r="T71">
-        <v>2.53777279645956</v>
+        <v>2.616630968291081</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.17581131035375</v>
+        <v>2.144728291634411</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1032739029734914</v>
+        <v>0.1033278586647836</v>
       </c>
       <c r="C72">
-        <v>55.0701929611588</v>
+        <v>52.6779703414411</v>
       </c>
       <c r="D72">
-        <v>200.6101929611588</v>
+        <v>200.4499703414411</v>
       </c>
       <c r="E72">
-        <v>156.24</v>
+        <v>158.472</v>
       </c>
       <c r="F72">
-        <v>156.24</v>
+        <v>158.472</v>
       </c>
       <c r="G72">
         <v>10.7</v>
@@ -7191,28 +7191,28 @@
         <v>25.4</v>
       </c>
       <c r="M72">
-        <v>11.842992</v>
+        <v>12.0121776</v>
       </c>
       <c r="N72">
-        <v>13.557008</v>
+        <v>13.3878224</v>
       </c>
       <c r="O72">
-        <v>2.575831519999999</v>
+        <v>2.543686256</v>
       </c>
       <c r="P72">
-        <v>10.98117648</v>
+        <v>10.844136144</v>
       </c>
       <c r="Q72">
-        <v>24.98117647999999</v>
+        <v>24.844136144</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2009843432449712</v>
+        <v>0.2059837195337365</v>
       </c>
       <c r="T72">
-        <v>2.616630968291081</v>
+        <v>2.700927634731672</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.144728291634411</v>
+        <v>2.114520850907166</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1033278586647836</v>
+        <v>0.1033818143560758</v>
       </c>
       <c r="C73">
-        <v>52.67797034144112</v>
+        <v>50.28600344951869</v>
       </c>
       <c r="D73">
-        <v>200.4499703414411</v>
+        <v>200.2900034495187</v>
       </c>
       <c r="E73">
-        <v>158.472</v>
+        <v>160.704</v>
       </c>
       <c r="F73">
-        <v>158.472</v>
+        <v>160.704</v>
       </c>
       <c r="G73">
         <v>10.7</v>
@@ -7273,28 +7273,28 @@
         <v>25.4</v>
       </c>
       <c r="M73">
-        <v>12.0121776</v>
+        <v>12.1813632</v>
       </c>
       <c r="N73">
-        <v>13.3878224</v>
+        <v>13.2186368</v>
       </c>
       <c r="O73">
-        <v>2.543686256</v>
+        <v>2.511540992</v>
       </c>
       <c r="P73">
-        <v>10.844136144</v>
+        <v>10.707095808</v>
       </c>
       <c r="Q73">
-        <v>24.844136144</v>
+        <v>24.707095808</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2059837195337365</v>
+        <v>0.2113401941288422</v>
       </c>
       <c r="T73">
-        <v>2.700927634731671</v>
+        <v>2.791245491632304</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.114520850907166</v>
+        <v>2.085152505755678</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1033818143560758</v>
+        <v>0.1034357700473681</v>
       </c>
       <c r="C74">
-        <v>50.28600344951869</v>
+        <v>47.89429167363753</v>
       </c>
       <c r="D74">
-        <v>200.2900034495187</v>
+        <v>200.1302916736375</v>
       </c>
       <c r="E74">
-        <v>160.704</v>
+        <v>162.936</v>
       </c>
       <c r="F74">
-        <v>160.704</v>
+        <v>162.936</v>
       </c>
       <c r="G74">
         <v>10.7</v>
@@ -7355,28 +7355,28 @@
         <v>25.4</v>
       </c>
       <c r="M74">
-        <v>12.1813632</v>
+        <v>12.3505488</v>
       </c>
       <c r="N74">
-        <v>13.2186368</v>
+        <v>13.0494512</v>
       </c>
       <c r="O74">
-        <v>2.511540992</v>
+        <v>2.479395728</v>
       </c>
       <c r="P74">
-        <v>10.707095808</v>
+        <v>10.570055472</v>
       </c>
       <c r="Q74">
-        <v>24.707095808</v>
+        <v>24.570055472</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2113401941288422</v>
+        <v>0.2170934446198816</v>
       </c>
       <c r="T74">
-        <v>2.791245491632304</v>
+        <v>2.888253560155206</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.085152505755678</v>
+        <v>2.05658877280012</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1034357700473681</v>
+        <v>0.1034897257386603</v>
       </c>
       <c r="C75">
-        <v>47.89429167363753</v>
+        <v>45.50283440399326</v>
       </c>
       <c r="D75">
-        <v>200.1302916736375</v>
+        <v>199.9708344039933</v>
       </c>
       <c r="E75">
-        <v>162.936</v>
+        <v>165.168</v>
       </c>
       <c r="F75">
-        <v>162.936</v>
+        <v>165.168</v>
       </c>
       <c r="G75">
         <v>10.7</v>
@@ -7437,28 +7437,28 @@
         <v>25.4</v>
       </c>
       <c r="M75">
-        <v>12.3505488</v>
+        <v>12.5197344</v>
       </c>
       <c r="N75">
-        <v>13.0494512</v>
+        <v>12.8802656</v>
       </c>
       <c r="O75">
-        <v>2.479395728</v>
+        <v>2.447250464</v>
       </c>
       <c r="P75">
-        <v>10.570055472</v>
+        <v>10.433015136</v>
       </c>
       <c r="Q75">
-        <v>24.570055472</v>
+        <v>24.433015136</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2170934446198816</v>
+        <v>0.2232892528410011</v>
       </c>
       <c r="T75">
-        <v>2.888253560155206</v>
+        <v>2.992723787795255</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.05658877280012</v>
+        <v>2.028797032627146</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1034897257386603</v>
+        <v>0.1035436814299525</v>
       </c>
       <c r="C76">
-        <v>45.50283440399326</v>
+        <v>43.11163103272347</v>
       </c>
       <c r="D76">
-        <v>199.9708344039933</v>
+        <v>199.8116310327235</v>
       </c>
       <c r="E76">
-        <v>165.168</v>
+        <v>167.4</v>
       </c>
       <c r="F76">
-        <v>165.168</v>
+        <v>167.4</v>
       </c>
       <c r="G76">
         <v>10.7</v>
@@ -7519,28 +7519,28 @@
         <v>25.4</v>
       </c>
       <c r="M76">
-        <v>12.5197344</v>
+        <v>12.68892</v>
       </c>
       <c r="N76">
-        <v>12.8802656</v>
+        <v>12.71108</v>
       </c>
       <c r="O76">
-        <v>2.447250464</v>
+        <v>2.4151052</v>
       </c>
       <c r="P76">
-        <v>10.433015136</v>
+        <v>10.2959748</v>
       </c>
       <c r="Q76">
-        <v>24.433015136</v>
+        <v>24.2959748</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2232892528410011</v>
+        <v>0.2299807257198101</v>
       </c>
       <c r="T76">
-        <v>2.992723787795255</v>
+        <v>3.105551633646507</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.028797032627146</v>
+        <v>2.00174640552545</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1035436814299525</v>
+        <v>0.1123391571212448</v>
       </c>
       <c r="C77">
-        <v>43.11163103272347</v>
+        <v>17.9268894847215</v>
       </c>
       <c r="D77">
-        <v>199.8116310327235</v>
+        <v>176.8588894847215</v>
       </c>
       <c r="E77">
-        <v>167.4</v>
+        <v>169.632</v>
       </c>
       <c r="F77">
-        <v>167.4</v>
+        <v>169.632</v>
       </c>
       <c r="G77">
         <v>10.7</v>
@@ -7601,45 +7601,45 @@
         <v>25.4</v>
       </c>
       <c r="M77">
-        <v>12.68892</v>
+        <v>15.26688</v>
       </c>
       <c r="N77">
-        <v>12.71108</v>
+        <v>10.13312</v>
       </c>
       <c r="O77">
-        <v>2.4151052</v>
+        <v>1.9252928</v>
       </c>
       <c r="P77">
-        <v>10.2959748</v>
+        <v>8.207827199999999</v>
       </c>
       <c r="Q77">
-        <v>24.2959748</v>
+        <v>22.2078272</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2299807257198101</v>
+        <v>0.2372298213385198</v>
       </c>
       <c r="T77">
-        <v>3.105551633646507</v>
+        <v>3.227781799985364</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.19</v>
       </c>
       <c r="W77">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.00174640552545</v>
+        <v>1.663732209855583</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1123391571212448</v>
+        <v>0.112508132812537</v>
       </c>
       <c r="C78">
-        <v>17.9268894847215</v>
+        <v>15.30544261742139</v>
       </c>
       <c r="D78">
-        <v>176.8588894847215</v>
+        <v>176.4694426174214</v>
       </c>
       <c r="E78">
-        <v>169.632</v>
+        <v>171.864</v>
       </c>
       <c r="F78">
-        <v>169.632</v>
+        <v>171.864</v>
       </c>
       <c r="G78">
         <v>10.7</v>
@@ -7683,28 +7683,28 @@
         <v>25.4</v>
       </c>
       <c r="M78">
-        <v>15.26688</v>
+        <v>15.46776</v>
       </c>
       <c r="N78">
-        <v>10.13312</v>
+        <v>9.932239999999998</v>
       </c>
       <c r="O78">
-        <v>1.9252928</v>
+        <v>1.8871256</v>
       </c>
       <c r="P78">
-        <v>8.207827199999999</v>
+        <v>8.045114399999999</v>
       </c>
       <c r="Q78">
-        <v>22.2078272</v>
+        <v>22.0451144</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2372298213385198</v>
+        <v>0.2451092730979869</v>
       </c>
       <c r="T78">
-        <v>3.227781799985364</v>
+        <v>3.360640676440643</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.663732209855583</v>
+        <v>1.642125298039276</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.112508132812537</v>
+        <v>0.1126771085038292</v>
       </c>
       <c r="C79">
-        <v>15.30544261742139</v>
+        <v>12.68570712147257</v>
       </c>
       <c r="D79">
-        <v>176.4694426174214</v>
+        <v>176.0817071214726</v>
       </c>
       <c r="E79">
-        <v>171.864</v>
+        <v>174.096</v>
       </c>
       <c r="F79">
-        <v>171.864</v>
+        <v>174.096</v>
       </c>
       <c r="G79">
         <v>10.7</v>
@@ -7765,28 +7765,28 @@
         <v>25.4</v>
       </c>
       <c r="M79">
-        <v>15.46776</v>
+        <v>15.66864</v>
       </c>
       <c r="N79">
-        <v>9.932239999999998</v>
+        <v>9.731359999999999</v>
       </c>
       <c r="O79">
-        <v>1.8871256</v>
+        <v>1.8489584</v>
       </c>
       <c r="P79">
-        <v>8.045114399999999</v>
+        <v>7.882401599999999</v>
       </c>
       <c r="Q79">
-        <v>22.0451144</v>
+        <v>21.8824016</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2451092730979869</v>
+        <v>0.2537050386537691</v>
       </c>
       <c r="T79">
-        <v>3.360640676440643</v>
+        <v>3.505577632573675</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.642125298039276</v>
+        <v>1.621072409602875</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1126771085038292</v>
+        <v>0.1128460841951215</v>
       </c>
       <c r="C80">
-        <v>12.68570712147257</v>
+        <v>10.06767174102282</v>
       </c>
       <c r="D80">
-        <v>176.0817071214726</v>
+        <v>175.6956717410228</v>
       </c>
       <c r="E80">
-        <v>174.096</v>
+        <v>176.328</v>
       </c>
       <c r="F80">
-        <v>174.096</v>
+        <v>176.328</v>
       </c>
       <c r="G80">
         <v>10.7</v>
@@ -7847,28 +7847,28 @@
         <v>25.4</v>
       </c>
       <c r="M80">
-        <v>15.66864</v>
+        <v>15.86952</v>
       </c>
       <c r="N80">
-        <v>9.731359999999999</v>
+        <v>9.530479999999999</v>
       </c>
       <c r="O80">
-        <v>1.8489584</v>
+        <v>1.8107912</v>
       </c>
       <c r="P80">
-        <v>7.882401599999999</v>
+        <v>7.719688799999999</v>
       </c>
       <c r="Q80">
-        <v>21.8824016</v>
+        <v>21.7196888</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2537050386537691</v>
+        <v>0.2631194485481974</v>
       </c>
       <c r="T80">
-        <v>3.505577632573675</v>
+        <v>3.664318108338424</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.621072409602875</v>
+        <v>1.600552505683852</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1128460841951215</v>
+        <v>0.1130150598864137</v>
       </c>
       <c r="C81">
-        <v>10.06767174102282</v>
+        <v>7.45132531871181</v>
       </c>
       <c r="D81">
-        <v>175.6956717410228</v>
+        <v>175.3113253187118</v>
       </c>
       <c r="E81">
-        <v>176.328</v>
+        <v>178.56</v>
       </c>
       <c r="F81">
-        <v>176.328</v>
+        <v>178.56</v>
       </c>
       <c r="G81">
         <v>10.7</v>
@@ -7929,28 +7929,28 @@
         <v>25.4</v>
       </c>
       <c r="M81">
-        <v>15.86952</v>
+        <v>16.0704</v>
       </c>
       <c r="N81">
-        <v>9.530479999999999</v>
+        <v>9.329599999999999</v>
       </c>
       <c r="O81">
-        <v>1.8107912</v>
+        <v>1.772624</v>
       </c>
       <c r="P81">
-        <v>7.719688799999999</v>
+        <v>7.556975999999999</v>
       </c>
       <c r="Q81">
-        <v>21.7196888</v>
+        <v>21.556976</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2631194485481974</v>
+        <v>0.2734752994320684</v>
       </c>
       <c r="T81">
-        <v>3.664318108338424</v>
+        <v>3.838932631679648</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.600552505683852</v>
+        <v>1.580545599362804</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1130150598864137</v>
+        <v>0.1131840355777059</v>
       </c>
       <c r="C82">
-        <v>7.45132531871181</v>
+        <v>4.836656794595967</v>
       </c>
       <c r="D82">
-        <v>175.3113253187118</v>
+        <v>174.928656794596</v>
       </c>
       <c r="E82">
-        <v>178.56</v>
+        <v>180.792</v>
       </c>
       <c r="F82">
-        <v>178.56</v>
+        <v>180.792</v>
       </c>
       <c r="G82">
         <v>10.7</v>
@@ -8011,28 +8011,28 @@
         <v>25.4</v>
       </c>
       <c r="M82">
-        <v>16.0704</v>
+        <v>16.27128</v>
       </c>
       <c r="N82">
-        <v>9.329599999999999</v>
+        <v>9.128719999999998</v>
       </c>
       <c r="O82">
-        <v>1.772624</v>
+        <v>1.7344568</v>
       </c>
       <c r="P82">
-        <v>7.556975999999999</v>
+        <v>7.394263199999998</v>
       </c>
       <c r="Q82">
-        <v>21.556976</v>
+        <v>21.3942632</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2734752994320684</v>
+        <v>0.2849212398826628</v>
       </c>
       <c r="T82">
-        <v>3.838932631679648</v>
+        <v>4.031927631162054</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.580545599362804</v>
+        <v>1.561032690728695</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1131840355777059</v>
+        <v>0.1133530112689981</v>
       </c>
       <c r="C83">
-        <v>4.836656794595967</v>
+        <v>2.22365520508788</v>
       </c>
       <c r="D83">
-        <v>174.928656794596</v>
+        <v>174.5476552050879</v>
       </c>
       <c r="E83">
-        <v>180.792</v>
+        <v>183.024</v>
       </c>
       <c r="F83">
-        <v>180.792</v>
+        <v>183.024</v>
       </c>
       <c r="G83">
         <v>10.7</v>
@@ -8093,28 +8093,28 @@
         <v>25.4</v>
       </c>
       <c r="M83">
-        <v>16.27128</v>
+        <v>16.47216</v>
       </c>
       <c r="N83">
-        <v>9.128719999999998</v>
+        <v>8.92784</v>
       </c>
       <c r="O83">
-        <v>1.7344568</v>
+        <v>1.6962896</v>
       </c>
       <c r="P83">
-        <v>7.394263199999998</v>
+        <v>7.2315504</v>
       </c>
       <c r="Q83">
-        <v>21.3942632</v>
+        <v>21.2315504</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2849212398826628</v>
+        <v>0.2976389514944342</v>
       </c>
       <c r="T83">
-        <v>4.031927631162054</v>
+        <v>4.246366519475838</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.561032690728695</v>
+        <v>1.541995706695418</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1133530112689981</v>
+        <v>0.1135219869602904</v>
       </c>
       <c r="C84">
-        <v>2.22365520508788</v>
+        <v>-0.3876903180911881</v>
       </c>
       <c r="D84">
-        <v>174.5476552050879</v>
+        <v>174.1683096819088</v>
       </c>
       <c r="E84">
-        <v>183.024</v>
+        <v>185.256</v>
       </c>
       <c r="F84">
-        <v>183.024</v>
+        <v>185.256</v>
       </c>
       <c r="G84">
         <v>10.7</v>
@@ -8175,28 +8175,28 @@
         <v>25.4</v>
       </c>
       <c r="M84">
-        <v>16.47216</v>
+        <v>16.67304</v>
       </c>
       <c r="N84">
-        <v>8.92784</v>
+        <v>8.726959999999998</v>
       </c>
       <c r="O84">
-        <v>1.6962896</v>
+        <v>1.6581224</v>
       </c>
       <c r="P84">
-        <v>7.2315504</v>
+        <v>7.068837599999998</v>
       </c>
       <c r="Q84">
-        <v>21.2315504</v>
+        <v>21.0688376</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2976389514944342</v>
+        <v>0.3118528644722964</v>
       </c>
       <c r="T84">
-        <v>4.246366519475838</v>
+        <v>4.486033512297126</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.541995706695418</v>
+        <v>1.523417445168967</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1135219869602904</v>
+        <v>0.1136909626515826</v>
       </c>
       <c r="C85">
-        <v>-0.3876903180911881</v>
+        <v>-2.997390548944225</v>
       </c>
       <c r="D85">
-        <v>174.1683096819088</v>
+        <v>173.7906094510558</v>
       </c>
       <c r="E85">
-        <v>185.256</v>
+        <v>187.488</v>
       </c>
       <c r="F85">
-        <v>185.256</v>
+        <v>187.488</v>
       </c>
       <c r="G85">
         <v>10.7</v>
@@ -8257,28 +8257,28 @@
         <v>25.4</v>
       </c>
       <c r="M85">
-        <v>16.67304</v>
+        <v>16.87392</v>
       </c>
       <c r="N85">
-        <v>8.726959999999998</v>
+        <v>8.52608</v>
       </c>
       <c r="O85">
-        <v>1.6581224</v>
+        <v>1.6199552</v>
       </c>
       <c r="P85">
-        <v>7.068837599999998</v>
+        <v>6.906124800000001</v>
       </c>
       <c r="Q85">
-        <v>21.0688376</v>
+        <v>20.9061248</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3118528644722964</v>
+        <v>0.3278435165723915</v>
       </c>
       <c r="T85">
-        <v>4.486033512297126</v>
+        <v>4.755658879221075</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.523417445168967</v>
+        <v>1.50528152320267</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1136909626515826</v>
+        <v>0.1558162217134258</v>
       </c>
       <c r="C86">
-        <v>-2.997390548944196</v>
+        <v>-66.21476737002844</v>
       </c>
       <c r="D86">
-        <v>173.7906094510558</v>
+        <v>112.8052326299716</v>
       </c>
       <c r="E86">
-        <v>187.488</v>
+        <v>189.72</v>
       </c>
       <c r="F86">
-        <v>187.488</v>
+        <v>189.72</v>
       </c>
       <c r="G86">
         <v>10.7</v>
@@ -8339,45 +8339,45 @@
         <v>25.4</v>
       </c>
       <c r="M86">
-        <v>16.87392</v>
+        <v>27.850896</v>
       </c>
       <c r="N86">
-        <v>8.52608</v>
+        <v>-2.450896000000004</v>
       </c>
       <c r="O86">
-        <v>1.6199552</v>
+        <v>-0.4656702400000007</v>
       </c>
       <c r="P86">
-        <v>6.906124800000001</v>
+        <v>-1.985225760000003</v>
       </c>
       <c r="Q86">
-        <v>20.9061248</v>
+        <v>12.01477424</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3278435165723913</v>
+        <v>0.3510539034180596</v>
       </c>
       <c r="T86">
-        <v>4.755658879221072</v>
+        <v>5.147019345982332</v>
       </c>
       <c r="U86">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.19</v>
+        <v>0.1732798829883246</v>
       </c>
       <c r="W86">
-        <v>0.07290000000000001</v>
+        <v>0.121362513177314</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.50528152320267</v>
+        <v>0.9119993841490772</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1558162217134258</v>
+        <v>0.1568262217134258</v>
       </c>
       <c r="C87">
-        <v>-66.21476737002844</v>
+        <v>-69.38793888892287</v>
       </c>
       <c r="D87">
-        <v>112.8052326299716</v>
+        <v>111.8640611110771</v>
       </c>
       <c r="E87">
-        <v>189.72</v>
+        <v>191.952</v>
       </c>
       <c r="F87">
-        <v>189.72</v>
+        <v>191.952</v>
       </c>
       <c r="G87">
         <v>10.7</v>
@@ -8421,37 +8421,37 @@
         <v>25.4</v>
       </c>
       <c r="M87">
-        <v>27.850896</v>
+        <v>28.1785536</v>
       </c>
       <c r="N87">
-        <v>-2.450896000000004</v>
+        <v>-2.778553600000002</v>
       </c>
       <c r="O87">
-        <v>-0.4656702400000007</v>
+        <v>-0.5279251840000004</v>
       </c>
       <c r="P87">
-        <v>-1.985225760000003</v>
+        <v>-2.250628416000002</v>
       </c>
       <c r="Q87">
-        <v>12.01477424</v>
+        <v>11.749371584</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3510539034180596</v>
+        <v>0.3728577536622066</v>
       </c>
       <c r="T87">
-        <v>5.147019345982332</v>
+        <v>5.514663584981069</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1732798829883246</v>
+        <v>0.1712650006279953</v>
       </c>
       <c r="W87">
-        <v>0.121362513177314</v>
+        <v>0.1216582979078103</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.9119993841490772</v>
+        <v>0.9013947401473438</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1568262217134258</v>
+        <v>0.1578362217134258</v>
       </c>
       <c r="C88">
-        <v>-69.38793888892287</v>
+        <v>-72.54553534266067</v>
       </c>
       <c r="D88">
-        <v>111.8640611110771</v>
+        <v>110.9384646573393</v>
       </c>
       <c r="E88">
-        <v>191.952</v>
+        <v>194.184</v>
       </c>
       <c r="F88">
-        <v>191.952</v>
+        <v>194.184</v>
       </c>
       <c r="G88">
         <v>10.7</v>
@@ -8503,37 +8503,37 @@
         <v>25.4</v>
       </c>
       <c r="M88">
-        <v>28.1785536</v>
+        <v>28.5062112</v>
       </c>
       <c r="N88">
-        <v>-2.778553600000002</v>
+        <v>-3.106211200000004</v>
       </c>
       <c r="O88">
-        <v>-0.5279251840000004</v>
+        <v>-0.5901801280000007</v>
       </c>
       <c r="P88">
-        <v>-2.250628416000002</v>
+        <v>-2.516031072000003</v>
       </c>
       <c r="Q88">
-        <v>11.749371584</v>
+        <v>11.483968928</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3728577536622066</v>
+        <v>0.3980160424054534</v>
       </c>
       <c r="T88">
-        <v>5.514663584981069</v>
+        <v>5.93886847613346</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1712650006279953</v>
+        <v>0.1692964374023862</v>
       </c>
       <c r="W88">
-        <v>0.1216582979078103</v>
+        <v>0.1219472829893297</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9013947401473438</v>
+        <v>0.8910338810651903</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1578362217134258</v>
+        <v>0.1588462217134258</v>
       </c>
       <c r="C89">
-        <v>-72.54553534266067</v>
+        <v>-75.68794017664058</v>
       </c>
       <c r="D89">
-        <v>110.9384646573393</v>
+        <v>110.0280598233594</v>
       </c>
       <c r="E89">
-        <v>194.184</v>
+        <v>196.416</v>
       </c>
       <c r="F89">
-        <v>194.184</v>
+        <v>196.416</v>
       </c>
       <c r="G89">
         <v>10.7</v>
@@ -8585,37 +8585,37 @@
         <v>25.4</v>
       </c>
       <c r="M89">
-        <v>28.5062112</v>
+        <v>28.8338688</v>
       </c>
       <c r="N89">
-        <v>-3.106211200000004</v>
+        <v>-3.433868800000003</v>
       </c>
       <c r="O89">
-        <v>-0.5901801280000007</v>
+        <v>-0.6524350720000005</v>
       </c>
       <c r="P89">
-        <v>-2.516031072000003</v>
+        <v>-2.781433728000002</v>
       </c>
       <c r="Q89">
-        <v>11.483968928</v>
+        <v>11.218566272</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3980160424054534</v>
+        <v>0.4273673792725745</v>
       </c>
       <c r="T89">
-        <v>5.93886847613346</v>
+        <v>6.433774182477915</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1692964374023862</v>
+        <v>0.1673726142500863</v>
       </c>
       <c r="W89">
-        <v>0.1219472829893297</v>
+        <v>0.1222297002280873</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8910338810651903</v>
+        <v>0.880908496053086</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1588462217134258</v>
+        <v>0.1598562217134258</v>
       </c>
       <c r="C90">
-        <v>-75.68794017664058</v>
+        <v>-78.81552435189587</v>
       </c>
       <c r="D90">
-        <v>110.0280598233594</v>
+        <v>109.1324756481041</v>
       </c>
       <c r="E90">
-        <v>196.416</v>
+        <v>198.648</v>
       </c>
       <c r="F90">
-        <v>196.416</v>
+        <v>198.648</v>
       </c>
       <c r="G90">
         <v>10.7</v>
@@ -8667,37 +8667,37 @@
         <v>25.4</v>
       </c>
       <c r="M90">
-        <v>28.8338688</v>
+        <v>29.1615264</v>
       </c>
       <c r="N90">
-        <v>-3.433868800000003</v>
+        <v>-3.761526400000005</v>
       </c>
       <c r="O90">
-        <v>-0.6524350720000005</v>
+        <v>-0.7146900160000009</v>
       </c>
       <c r="P90">
-        <v>-2.781433728000002</v>
+        <v>-3.046836384000004</v>
       </c>
       <c r="Q90">
-        <v>11.218566272</v>
+        <v>10.953163616</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4273673792725745</v>
+        <v>0.4620553228428085</v>
       </c>
       <c r="T90">
-        <v>6.433774182477915</v>
+        <v>7.018662744521363</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1673726142500863</v>
+        <v>0.165492023078737</v>
       </c>
       <c r="W90">
-        <v>0.1222297002280873</v>
+        <v>0.1225057710120414</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.880908496053086</v>
+        <v>0.8710106477828264</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1598562217134258</v>
+        <v>0.1608662217134258</v>
       </c>
       <c r="C91">
-        <v>-78.81552435189587</v>
+        <v>-81.92864684908047</v>
       </c>
       <c r="D91">
-        <v>109.1324756481041</v>
+        <v>108.2513531509195</v>
       </c>
       <c r="E91">
-        <v>198.648</v>
+        <v>200.88</v>
       </c>
       <c r="F91">
-        <v>198.648</v>
+        <v>200.88</v>
       </c>
       <c r="G91">
         <v>10.7</v>
@@ -8749,37 +8749,37 @@
         <v>25.4</v>
       </c>
       <c r="M91">
-        <v>29.1615264</v>
+        <v>29.489184</v>
       </c>
       <c r="N91">
-        <v>-3.761526400000005</v>
+        <v>-4.089184000000003</v>
       </c>
       <c r="O91">
-        <v>-0.7146900160000009</v>
+        <v>-0.7769449600000006</v>
       </c>
       <c r="P91">
-        <v>-3.046836384000004</v>
+        <v>-3.312239040000002</v>
       </c>
       <c r="Q91">
-        <v>10.953163616</v>
+        <v>10.68776096</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4620553228428085</v>
+        <v>0.5036808551270894</v>
       </c>
       <c r="T91">
-        <v>7.018662744521363</v>
+        <v>7.720529018973498</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.165492023078737</v>
+        <v>0.1636532228223066</v>
       </c>
       <c r="W91">
-        <v>0.1225057710120414</v>
+        <v>0.1227757068896854</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8710106477828264</v>
+        <v>0.8613327516963507</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1608662217134258</v>
+        <v>0.1618762217134258</v>
       </c>
       <c r="C92">
-        <v>-81.92864684908047</v>
+        <v>-85.02765514823621</v>
       </c>
       <c r="D92">
-        <v>108.2513531509195</v>
+        <v>107.3843448517638</v>
       </c>
       <c r="E92">
-        <v>200.88</v>
+        <v>203.112</v>
       </c>
       <c r="F92">
-        <v>200.88</v>
+        <v>203.112</v>
       </c>
       <c r="G92">
         <v>10.7</v>
@@ -8831,37 +8831,37 @@
         <v>25.4</v>
       </c>
       <c r="M92">
-        <v>29.489184</v>
+        <v>29.8168416</v>
       </c>
       <c r="N92">
-        <v>-4.089184000000003</v>
+        <v>-4.416841600000005</v>
       </c>
       <c r="O92">
-        <v>-0.7769449600000006</v>
+        <v>-0.839199904000001</v>
       </c>
       <c r="P92">
-        <v>-3.312239040000002</v>
+        <v>-3.577641696000004</v>
       </c>
       <c r="Q92">
-        <v>10.68776096</v>
+        <v>10.422358304</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5036808551270894</v>
+        <v>0.554556505696766</v>
       </c>
       <c r="T92">
-        <v>7.720529018973498</v>
+        <v>8.578365576637221</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1636532228223066</v>
+        <v>0.1618548357583252</v>
       </c>
       <c r="W92">
-        <v>0.1227757068896854</v>
+        <v>0.1230397101106779</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8613327516963507</v>
+        <v>0.8518675566227644</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1618762217134258</v>
+        <v>0.1628862217134258</v>
       </c>
       <c r="C93">
-        <v>-85.02765514823621</v>
+        <v>-88.11288568568776</v>
       </c>
       <c r="D93">
-        <v>107.3843448517638</v>
+        <v>106.5311143143122</v>
       </c>
       <c r="E93">
-        <v>203.112</v>
+        <v>205.344</v>
       </c>
       <c r="F93">
-        <v>203.112</v>
+        <v>205.344</v>
       </c>
       <c r="G93">
         <v>10.7</v>
@@ -8913,37 +8913,37 @@
         <v>25.4</v>
       </c>
       <c r="M93">
-        <v>29.8168416</v>
+        <v>30.1444992</v>
       </c>
       <c r="N93">
-        <v>-4.416841600000005</v>
+        <v>-4.744499200000003</v>
       </c>
       <c r="O93">
-        <v>-0.839199904000001</v>
+        <v>-0.9014548480000006</v>
       </c>
       <c r="P93">
-        <v>-3.577641696000004</v>
+        <v>-3.843044352000003</v>
       </c>
       <c r="Q93">
-        <v>10.422358304</v>
+        <v>10.156955648</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.554556505696766</v>
+        <v>0.6181510689088618</v>
       </c>
       <c r="T93">
-        <v>8.578365576637221</v>
+        <v>9.650661273716876</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1618548357583252</v>
+        <v>0.1600955440653</v>
       </c>
       <c r="W93">
-        <v>0.1230397101106779</v>
+        <v>0.123297974131214</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8518675566227644</v>
+        <v>0.8426081266594735</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1628862217134258</v>
+        <v>0.1638962217134258</v>
       </c>
       <c r="C94">
-        <v>-88.11288568568776</v>
+        <v>-91.18466428932759</v>
       </c>
       <c r="D94">
-        <v>106.5311143143122</v>
+        <v>105.6913357106724</v>
       </c>
       <c r="E94">
-        <v>205.344</v>
+        <v>207.576</v>
       </c>
       <c r="F94">
-        <v>205.344</v>
+        <v>207.576</v>
       </c>
       <c r="G94">
         <v>10.7</v>
@@ -8995,37 +8995,37 @@
         <v>25.4</v>
       </c>
       <c r="M94">
-        <v>30.1444992</v>
+        <v>30.4721568</v>
       </c>
       <c r="N94">
-        <v>-4.744499200000003</v>
+        <v>-5.072156800000002</v>
       </c>
       <c r="O94">
-        <v>-0.9014548480000006</v>
+        <v>-0.9637097920000004</v>
       </c>
       <c r="P94">
-        <v>-3.843044352000003</v>
+        <v>-4.108447008000002</v>
       </c>
       <c r="Q94">
-        <v>10.156955648</v>
+        <v>9.891552991999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6181510689088618</v>
+        <v>0.6999155073244138</v>
       </c>
       <c r="T94">
-        <v>9.650661273716876</v>
+        <v>11.02932716996215</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1600955440653</v>
+        <v>0.1583740866022322</v>
       </c>
       <c r="W94">
-        <v>0.123297974131214</v>
+        <v>0.1235506840867923</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8426081266594735</v>
+        <v>0.8335478242222749</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1638962217134258</v>
+        <v>0.1649062217134258</v>
       </c>
       <c r="C95">
-        <v>-91.18466428932759</v>
+        <v>-94.24330659347383</v>
       </c>
       <c r="D95">
-        <v>105.6913357106724</v>
+        <v>104.8646934065262</v>
       </c>
       <c r="E95">
-        <v>207.576</v>
+        <v>209.808</v>
       </c>
       <c r="F95">
-        <v>207.576</v>
+        <v>209.808</v>
       </c>
       <c r="G95">
         <v>10.7</v>
@@ -9077,37 +9077,37 @@
         <v>25.4</v>
       </c>
       <c r="M95">
-        <v>30.4721568</v>
+        <v>30.7998144</v>
       </c>
       <c r="N95">
-        <v>-5.072156800000002</v>
+        <v>-5.399814400000004</v>
       </c>
       <c r="O95">
-        <v>-0.9637097920000004</v>
+        <v>-1.025964736000001</v>
       </c>
       <c r="P95">
-        <v>-4.108447008000002</v>
+        <v>-4.373849664000003</v>
       </c>
       <c r="Q95">
-        <v>9.891552991999998</v>
+        <v>9.626150335999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6999155073244138</v>
+        <v>0.8089347585451496</v>
       </c>
       <c r="T95">
-        <v>11.02932716996215</v>
+        <v>12.86754836495584</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1583740866022322</v>
+        <v>0.1566892558936978</v>
       </c>
       <c r="W95">
-        <v>0.1235506840867923</v>
+        <v>0.1237980172348052</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8335478242222749</v>
+        <v>0.824680294177357</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1649062217134258</v>
+        <v>0.1659162217134258</v>
       </c>
       <c r="C96">
-        <v>-94.24330659347383</v>
+        <v>-97.28911843441109</v>
       </c>
       <c r="D96">
-        <v>104.8646934065262</v>
+        <v>104.0508815655889</v>
       </c>
       <c r="E96">
-        <v>209.808</v>
+        <v>212.04</v>
       </c>
       <c r="F96">
-        <v>209.808</v>
+        <v>212.04</v>
       </c>
       <c r="G96">
         <v>10.7</v>
@@ -9159,37 +9159,37 @@
         <v>25.4</v>
       </c>
       <c r="M96">
-        <v>30.7998144</v>
+        <v>31.127472</v>
       </c>
       <c r="N96">
-        <v>-5.399814400000004</v>
+        <v>-5.727472000000002</v>
       </c>
       <c r="O96">
-        <v>-1.025964736000001</v>
+        <v>-1.08821968</v>
       </c>
       <c r="P96">
-        <v>-4.373849664000003</v>
+        <v>-4.639252320000002</v>
       </c>
       <c r="Q96">
-        <v>9.626150335999997</v>
+        <v>9.360747679999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8089347585451496</v>
+        <v>0.96156171025418</v>
       </c>
       <c r="T96">
-        <v>12.86754836495584</v>
+        <v>15.44105803794702</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1566892558936978</v>
+        <v>0.1550398953053431</v>
       </c>
       <c r="W96">
-        <v>0.1237980172348052</v>
+        <v>0.1240401433691756</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.824680294177357</v>
+        <v>0.8159994489754901</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1659162217134258</v>
+        <v>0.1669262217134258</v>
       </c>
       <c r="C97">
-        <v>-97.28911843441109</v>
+        <v>-100.3223962276555</v>
       </c>
       <c r="D97">
-        <v>104.0508815655889</v>
+        <v>103.2496037723446</v>
       </c>
       <c r="E97">
-        <v>212.04</v>
+        <v>214.272</v>
       </c>
       <c r="F97">
-        <v>212.04</v>
+        <v>214.272</v>
       </c>
       <c r="G97">
         <v>10.7</v>
@@ -9241,37 +9241,37 @@
         <v>25.4</v>
       </c>
       <c r="M97">
-        <v>31.127472</v>
+        <v>31.45512960000001</v>
       </c>
       <c r="N97">
-        <v>-5.727472000000002</v>
+        <v>-6.055129600000008</v>
       </c>
       <c r="O97">
-        <v>-1.08821968</v>
+        <v>-1.150474624000001</v>
       </c>
       <c r="P97">
-        <v>-4.639252320000002</v>
+        <v>-4.904654976000007</v>
       </c>
       <c r="Q97">
-        <v>9.360747679999998</v>
+        <v>9.095345023999993</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.96156171025418</v>
+        <v>1.190502137817726</v>
       </c>
       <c r="T97">
-        <v>15.44105803794702</v>
+        <v>19.30132254743378</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1550398953053431</v>
+        <v>0.1534248963959124</v>
       </c>
       <c r="W97">
-        <v>0.1240401433691756</v>
+        <v>0.1242772252090801</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8159994489754901</v>
+        <v>0.8074994547153287</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1669262217134258</v>
+        <v>0.2224431222602266</v>
       </c>
       <c r="C98">
-        <v>-100.3223962276554</v>
+        <v>-133.2612437919443</v>
       </c>
       <c r="D98">
-        <v>103.2496037723446</v>
+        <v>72.54275620805566</v>
       </c>
       <c r="E98">
-        <v>214.272</v>
+        <v>216.504</v>
       </c>
       <c r="F98">
-        <v>214.272</v>
+        <v>216.504</v>
       </c>
       <c r="G98">
         <v>10.7</v>
@@ -9323,45 +9323,45 @@
         <v>25.4</v>
       </c>
       <c r="M98">
-        <v>31.4551296</v>
+        <v>43.4740032</v>
       </c>
       <c r="N98">
-        <v>-6.055129600000004</v>
+        <v>-18.0740032</v>
       </c>
       <c r="O98">
-        <v>-1.150474624000001</v>
+        <v>-3.434060608</v>
       </c>
       <c r="P98">
-        <v>-4.904654976000003</v>
+        <v>-14.639942592</v>
       </c>
       <c r="Q98">
-        <v>9.095345023999997</v>
+        <v>-0.6399425920000006</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.190502137817723</v>
+        <v>1.642966201983658</v>
       </c>
       <c r="T98">
-        <v>19.30132254743373</v>
+        <v>26.93051668892323</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1534248963959124</v>
+        <v>0.1110088706990756</v>
       </c>
       <c r="W98">
-        <v>0.1242772252090801</v>
+        <v>0.1785094187636256</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8074994547153287</v>
+        <v>0.5842572142056612</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2224431222602266</v>
+        <v>0.2239931222602266</v>
       </c>
       <c r="C99">
-        <v>-133.2612437919443</v>
+        <v>-136.0906313427799</v>
       </c>
       <c r="D99">
-        <v>72.54275620805566</v>
+        <v>71.94536865722009</v>
       </c>
       <c r="E99">
-        <v>216.504</v>
+        <v>218.736</v>
       </c>
       <c r="F99">
-        <v>216.504</v>
+        <v>218.736</v>
       </c>
       <c r="G99">
         <v>10.7</v>
@@ -9405,37 +9405,37 @@
         <v>25.4</v>
       </c>
       <c r="M99">
-        <v>43.4740032</v>
+        <v>43.9221888</v>
       </c>
       <c r="N99">
-        <v>-18.0740032</v>
+        <v>-18.5221888</v>
       </c>
       <c r="O99">
-        <v>-3.434060608</v>
+        <v>-3.519215872000001</v>
       </c>
       <c r="P99">
-        <v>-14.639942592</v>
+        <v>-15.002972928</v>
       </c>
       <c r="Q99">
-        <v>-0.6399425920000006</v>
+        <v>-1.002972928000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.642966201983658</v>
+        <v>2.441549302975486</v>
       </c>
       <c r="T99">
-        <v>26.93051668892323</v>
+        <v>40.39577503338483</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1110088706990756</v>
+        <v>0.1098761271205136</v>
       </c>
       <c r="W99">
-        <v>0.1785094187636256</v>
+        <v>0.1787368736742009</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5842572142056612</v>
+        <v>0.5782954058974401</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2239931222602266</v>
+        <v>0.2255431222602266</v>
       </c>
       <c r="C100">
-        <v>-136.0906313427799</v>
+        <v>-138.9102603159712</v>
       </c>
       <c r="D100">
-        <v>71.94536865722009</v>
+        <v>71.3577396840288</v>
       </c>
       <c r="E100">
-        <v>218.736</v>
+        <v>220.968</v>
       </c>
       <c r="F100">
-        <v>218.736</v>
+        <v>220.968</v>
       </c>
       <c r="G100">
         <v>10.7</v>
@@ -9487,37 +9487,37 @@
         <v>25.4</v>
       </c>
       <c r="M100">
-        <v>43.9221888</v>
+        <v>44.3703744</v>
       </c>
       <c r="N100">
-        <v>-18.5221888</v>
+        <v>-18.9703744</v>
       </c>
       <c r="O100">
-        <v>-3.519215872000001</v>
+        <v>-3.604371136</v>
       </c>
       <c r="P100">
-        <v>-15.002972928</v>
+        <v>-15.366003264</v>
       </c>
       <c r="Q100">
-        <v>-1.002972928000002</v>
+        <v>-1.366003263999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.441549302975486</v>
+        <v>4.837298605950972</v>
       </c>
       <c r="T100">
-        <v>40.39577503338483</v>
+        <v>80.79155006676966</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1098761271205136</v>
+        <v>0.1087662672506095</v>
       </c>
       <c r="W100">
-        <v>0.1787368736742009</v>
+        <v>0.1789597335360776</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5782954058974401</v>
+        <v>0.5724540381611024</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2255431222602266</v>
-      </c>
-      <c r="C101">
-        <v>-138.9102603159712</v>
-      </c>
-      <c r="D101">
-        <v>71.3577396840288</v>
-      </c>
-      <c r="E101">
-        <v>220.968</v>
-      </c>
-      <c r="F101">
-        <v>220.968</v>
-      </c>
-      <c r="G101">
-        <v>10.7</v>
-      </c>
-      <c r="H101">
-        <v>223.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>39.4</v>
-      </c>
-      <c r="K101">
-        <v>14</v>
-      </c>
-      <c r="L101">
-        <v>25.4</v>
-      </c>
-      <c r="M101">
-        <v>44.3703744</v>
-      </c>
-      <c r="N101">
-        <v>-18.9703744</v>
-      </c>
-      <c r="O101">
-        <v>-3.604371136</v>
-      </c>
-      <c r="P101">
-        <v>-15.366003264</v>
-      </c>
-      <c r="Q101">
-        <v>-1.366003263999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.837298605950972</v>
-      </c>
-      <c r="T101">
-        <v>80.79155006676966</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1087662672506095</v>
-      </c>
-      <c r="W101">
-        <v>0.1789597335360776</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5724540381611024</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
